--- a/Salidas/data_B_completa.xlsx
+++ b/Salidas/data_B_completa.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE66"/>
+  <dimension ref="A1:AF66"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -367,145 +367,150 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Grupo de evento.x</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Evento</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Grupo de evento</t>
-        </is>
-      </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Grupo de evento.y</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Clasificación manual del caso</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Apellido Ciudadano</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Nombre Ciudadano</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Calle Domicilio</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Numero Domicilio</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Localidad Residencia</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Tipo Cobertura Social</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Edad Diagnostico</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Sexo Legal</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Tipo de doc</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Establecimiento de Carga</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Fecha Apertura</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Fecha recolección en papel</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Fecha consulta</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Fecha de inicio de síntomas</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Internado</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Sintomático</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Tratamiento...21</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Resultado tratamiento</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Fallecido</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Clasificación</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Co-infección</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Tratamiento...26</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Transplante</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Hepatocarcinoma</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Cirrosis</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Pérdida de seguimiento</t>
         </is>
@@ -522,76 +527,81 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>Hepatitis virales</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>Hepatitis B</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Hepatitis virales</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Hepatitis virales</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
         <is>
           <t>ROMERO QUIROGA</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>CINTHIA SOLEDAD</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>USHUAIA</t>
         </is>
       </c>
-      <c r="L2">
+      <c r="M2">
         <v>21</v>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="P2">
+      <c r="Q2">
         <v>43472</v>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="Y2" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>Crónica</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>sin datos</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>sin dato</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>sin dato</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>sin dato</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>sin dato</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
@@ -608,76 +618,81 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>Hepatitis virales</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>Hepatitis B</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Hepatitis virales</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Hepatitis virales</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
         <is>
           <t>CAJAL</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>CAROLINA</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>USHUAIA</t>
         </is>
       </c>
-      <c r="L3">
+      <c r="M3">
         <v>36</v>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="P3">
+      <c r="Q3">
         <v>43297</v>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="Y3" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>Crónica</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>sin datos</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>sin dato</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>sin dato</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>sin dato</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>sin dato</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
@@ -694,76 +709,81 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>Hepatitis virales</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>Hepatitis B</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Hepatitis virales</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Hepatitis virales</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
         <is>
           <t>NUÑEZ</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>JOSE JESUS</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>USHUAIA</t>
         </is>
       </c>
-      <c r="L4">
+      <c r="M4">
         <v>51</v>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="P4">
+      <c r="Q4">
         <v>43508</v>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="Y4" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>Crónica</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>sin datos</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>sin dato</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>sin dato</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>sin dato</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>sin dato</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
@@ -780,55 +800,55 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>Hepatitis virales</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>Hepatitis B</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Hepatitis virales</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Hepatitis virales</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
         <is>
           <t>LAMA</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>MIGUEL ANGEL</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>USHUAIA</t>
         </is>
       </c>
-      <c r="L5">
+      <c r="M5">
         <v>52</v>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="P5">
+      <c r="Q5">
         <v>43249</v>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="Y5" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>Crónica</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>NO</t>
@@ -850,6 +870,11 @@
         </is>
       </c>
       <c r="AE5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
@@ -866,76 +891,81 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>Hepatitis virales</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
           <t>Hepatitis B</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Hepatitis virales</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Hepatitis virales</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>SALAS</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>EVARISTO SILVANO</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>USHUAIA</t>
         </is>
       </c>
-      <c r="L6">
+      <c r="M6">
         <v>56</v>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="P6">
+      <c r="Q6">
         <v>43179</v>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="Y6" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>Crónica</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>sin datos</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>sin dato</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>sin dato</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>sin dato</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>sin dato</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
@@ -952,55 +982,55 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>Hepatitis virales</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
           <t>Hepatitis B</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Hepatitis virales</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Hepatitis virales</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>MERUVIA ROBLES</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>HERLINDA</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>USHUAIA</t>
         </is>
       </c>
-      <c r="L7">
+      <c r="M7">
         <v>33</v>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="P7">
+      <c r="Q7">
         <v>43472</v>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="Y7" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>Crónica</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>NO</t>
@@ -1022,6 +1052,11 @@
         </is>
       </c>
       <c r="AE7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
@@ -1038,75 +1073,75 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>Hepatitis virales</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
           <t>Hepatitis B</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Hepatitis virales</t>
-        </is>
-      </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>Hepatitis virales</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>07. Hepatitis B Resuelta - Infección Pasada</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>FLEITAS</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>CARLOS FELIPE</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>LOTE 12, MACIZO 624</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>TOLHUIN</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>S/D</t>
         </is>
       </c>
-      <c r="L8">
+      <c r="M8">
         <v>44</v>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>DNI</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>CENTRO ASISTENCIAL TOLHUIN</t>
         </is>
       </c>
-      <c r="P8">
+      <c r="Q8">
         <v>45122</v>
       </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>*sin dato*</t>
-        </is>
-      </c>
       <c r="R8" t="inlineStr">
         <is>
           <t>*sin dato*</t>
@@ -1139,19 +1174,19 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>*sin dato*</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>Crónica</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>NO</t>
@@ -1173,6 +1208,11 @@
         </is>
       </c>
       <c r="AE8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
@@ -1189,88 +1229,88 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>Hepatitis virales</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
           <t>Hepatitis B</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Hepatitis virales</t>
-        </is>
-      </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>Hepatitis virales</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>RUSCH</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>GERMAN ALFREDO</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>CERRO JEUJEPEN</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>473</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>TOLHUIN</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>S/D</t>
         </is>
       </c>
-      <c r="L9">
+      <c r="M9">
         <v>64</v>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>DNI</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>CENTRO ASISTENCIAL TOLHUIN</t>
         </is>
       </c>
-      <c r="P9">
+      <c r="Q9">
         <v>45295</v>
       </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>*sin dato*</t>
-        </is>
-      </c>
       <c r="R9" t="inlineStr">
         <is>
+          <t>*sin dato*</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
           <t>45247</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>*sin dato*</t>
-        </is>
-      </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>*sin dato*</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1280,7 +1320,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>*sin dato*</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -1290,40 +1330,45 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>*sin dato*</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>Crónica</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>sin datos</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>sin dato</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>sin dato</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>sin dato</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>sin dato</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
@@ -1340,88 +1385,88 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>Hepatitis virales</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
           <t>Hepatitis B</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Hepatitis virales</t>
-        </is>
-      </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>Hepatitis virales</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>GONZALEZ</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>EDGARDO RUBEN</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>JOSE IGNACIO RUCCI</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>530</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>TOLHUIN</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>S/D</t>
         </is>
       </c>
-      <c r="L10">
+      <c r="M10">
         <v>68</v>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>DNI</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>CENTRO ASISTENCIAL TOLHUIN</t>
         </is>
       </c>
-      <c r="P10">
+      <c r="Q10">
         <v>44365</v>
       </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>*sin dato*</t>
-        </is>
-      </c>
       <c r="R10" t="inlineStr">
         <is>
+          <t>*sin dato*</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
           <t>44376</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>*sin dato*</t>
-        </is>
-      </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>*sin dato*</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1431,39 +1476,39 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
           <t>Tenofovir alafenamida (TAF)</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>En tratamiento con carga negativa</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="Y10" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>Crónica</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
           <t>NO</t>
@@ -1475,6 +1520,11 @@
         </is>
       </c>
       <c r="AE10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
@@ -1491,80 +1541,80 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>Hepatitis virales</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
           <t>Hepatitis B</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Hepatitis virales</t>
-        </is>
-      </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t>Hepatitis virales</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t>12. Virus Hepatitis B</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>PEREZ LUNA RAFAJLOVSKI</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>PARASHKEVA</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>B° THORNE</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>RIO GRANDE</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>S/D</t>
         </is>
       </c>
-      <c r="L11">
+      <c r="M11">
         <v>35</v>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>DNI</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>CLINICA DE ESPECIALIDADES MEDICAS PRIVADA (CEMEP)</t>
         </is>
       </c>
-      <c r="P11">
+      <c r="Q11">
         <v>45183</v>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>45169</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>*sin dato*</t>
-        </is>
-      </c>
       <c r="S11" t="inlineStr">
         <is>
           <t>*sin dato*</t>
@@ -1592,40 +1642,45 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>*sin dato*</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>Crónica</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>sin datos</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>sin dato</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>sin dato</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AD11" t="inlineStr">
         <is>
           <t>sin dato</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AE11" t="inlineStr">
         <is>
           <t>sin dato</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
+      <c r="AF11" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
@@ -1642,80 +1697,80 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>Hepatitis virales</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
           <t>Hepatitis B</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Hepatitis virales</t>
-        </is>
-      </c>
       <c r="E12" t="inlineStr">
         <is>
+          <t>Hepatitis virales</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t>12. Virus Hepatitis B</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>HEREDIA</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>SERGIO OSCAR</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>VICENTE L. CANGA</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>1891</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>USHUAIA</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>S/D</t>
         </is>
       </c>
-      <c r="L12">
+      <c r="M12">
         <v>54</v>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>DNI</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>CLINICA SAN JORGE</t>
         </is>
       </c>
-      <c r="P12">
+      <c r="Q12">
         <v>43892</v>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>43872</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>*sin dato*</t>
-        </is>
-      </c>
       <c r="S12" t="inlineStr">
         <is>
           <t>*sin dato*</t>
@@ -1743,10 +1798,15 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>*sin dato*</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
         <is>
           <t>Sin datos</t>
         </is>
@@ -1763,88 +1823,88 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>Hepatitis virales</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
           <t>Hepatitis B</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Hepatitis virales</t>
-        </is>
-      </c>
       <c r="E13" t="inlineStr">
         <is>
+          <t>Hepatitis virales</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t>Paciente en seguimiento</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>GONZALEZ MOLINA</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>LOURDES MARIANELA</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>CATRIEL</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>1166</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>USHUAIA</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>S/D</t>
         </is>
       </c>
-      <c r="L13">
+      <c r="M13">
         <v>20</v>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>DNI</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>CONSULTORIO MEDICO MUNICIPALIDAD DE USHUAIA</t>
         </is>
       </c>
-      <c r="P13">
+      <c r="Q13">
         <v>43689</v>
       </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>*sin dato*</t>
-        </is>
-      </c>
       <c r="R13" t="inlineStr">
         <is>
+          <t>*sin dato*</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
           <t>43677</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>*sin dato*</t>
-        </is>
-      </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>*sin dato*</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1854,7 +1914,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>*sin dato*</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -1864,10 +1924,15 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>*sin dato*</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
         <is>
           <t>Sin datos</t>
         </is>
@@ -1884,98 +1949,98 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
+          <t>Hepatitis virales</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
           <t>Hepatitis B</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Hepatitis virales</t>
-        </is>
-      </c>
       <c r="E14" t="inlineStr">
         <is>
+          <t>Hepatitis virales</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t>Paciente en seguimiento</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>NAVIA CASTELLON</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>GUSTAVO ENZO</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>INDIOS YAMANAS</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>1176</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>USHUAIA</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>S/D</t>
         </is>
       </c>
-      <c r="L14">
+      <c r="M14">
         <v>22</v>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>DNI</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>CONSULTORIO MEDICO MUNICIPALIDAD DE USHUAIA</t>
         </is>
       </c>
-      <c r="P14">
+      <c r="Q14">
         <v>43689</v>
       </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>*sin dato*</t>
-        </is>
-      </c>
       <c r="R14" t="inlineStr">
         <is>
+          <t>*sin dato*</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
           <t>43677</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>*sin dato*</t>
-        </is>
-      </c>
       <c r="T14" t="inlineStr">
         <is>
+          <t>*sin dato*</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
           <t>ND</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>*sin dato*</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -1985,10 +2050,15 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>*sin dato*</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
         <is>
           <t>descartado</t>
         </is>
@@ -2005,75 +2075,75 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
+          <t>Hepatitis virales</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
           <t>Hepatitis B</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Hepatitis virales</t>
-        </is>
-      </c>
       <c r="E15" t="inlineStr">
         <is>
+          <t>Hepatitis virales</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t>11. En estudio para hepatitis B</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>CABRERA</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>MARIO ADRIAN</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>FINOCCHIO</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>784</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>RIO GRANDE</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>S/D</t>
         </is>
       </c>
-      <c r="L15">
+      <c r="M15">
         <v>49</v>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>DNI</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>DEPARTAMENTO DE EPIDEMIOLOGIA E INFORMACION DE LA SALUD ZONA NORTE</t>
         </is>
       </c>
-      <c r="P15">
+      <c r="Q15">
         <v>44182</v>
       </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>*sin dato*</t>
-        </is>
-      </c>
       <c r="R15" t="inlineStr">
         <is>
           <t>*sin dato*</t>
@@ -2106,15 +2176,20 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>*sin dato*</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>Sin datos</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
+      <c r="AA15" t="inlineStr">
         <is>
           <t>HIV</t>
         </is>
@@ -2131,88 +2206,88 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
+          <t>Hepatitis virales</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
           <t>Hepatitis B</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Hepatitis virales</t>
-        </is>
-      </c>
       <c r="E16" t="inlineStr">
         <is>
+          <t>Hepatitis virales</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t>03. Caso PROBABLE de Infección por VHB</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>BAZAN</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>ANA MARIA</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>ESTRADA</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>1861</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>RIO GRANDE</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>S/D</t>
         </is>
       </c>
-      <c r="L16">
+      <c r="M16">
         <v>63</v>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>DNI</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>DEPARTAMENTO DE EPIDEMIOLOGIA E INFORMACION DE LA SALUD ZONA NORTE</t>
         </is>
       </c>
-      <c r="P16">
+      <c r="Q16">
         <v>44176</v>
       </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>*sin dato*</t>
-        </is>
-      </c>
       <c r="R16" t="inlineStr">
         <is>
+          <t>*sin dato*</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
           <t>44032</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>*sin dato*</t>
-        </is>
-      </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>*sin dato*</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2222,7 +2297,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>*sin dato*</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
@@ -2232,40 +2307,45 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>*sin dato*</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>Crónica</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
+      <c r="AA16" t="inlineStr">
         <is>
           <t>sin datos</t>
         </is>
       </c>
-      <c r="AA16" t="inlineStr">
+      <c r="AB16" t="inlineStr">
         <is>
           <t>sin dato</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
+      <c r="AC16" t="inlineStr">
         <is>
           <t>sin dato</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
+      <c r="AD16" t="inlineStr">
         <is>
           <t>sin dato</t>
         </is>
       </c>
-      <c r="AD16" t="inlineStr">
+      <c r="AE16" t="inlineStr">
         <is>
           <t>sin dato</t>
         </is>
       </c>
-      <c r="AE16" t="inlineStr">
+      <c r="AF16" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
@@ -2282,88 +2362,88 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
+          <t>Hepatitis virales</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
           <t>Hepatitis B</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Hepatitis virales</t>
-        </is>
-      </c>
       <c r="E17" t="inlineStr">
         <is>
+          <t>Hepatitis virales</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t>06. Caso CONFIRMADO de Infección Aguda por VHB</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>GODOY</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>DANIEL ALBERTO</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>FORGACS</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>1031</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>RIO GRANDE</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>S/D</t>
         </is>
       </c>
-      <c r="L17">
+      <c r="M17">
         <v>25</v>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>DNI</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>DEPARTAMENTO DE EPIDEMIOLOGIA E INFORMACION DE LA SALUD ZONA NORTE</t>
         </is>
       </c>
-      <c r="P17">
+      <c r="Q17">
         <v>43714</v>
       </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>*sin dato*</t>
-        </is>
-      </c>
       <c r="R17" t="inlineStr">
         <is>
+          <t>*sin dato*</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
           <t>43697</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>*sin dato*</t>
-        </is>
-      </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>*sin dato*</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2373,7 +2453,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>*sin dato*</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -2383,40 +2463,45 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>*sin dato*</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>Aguda</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
+      <c r="AA17" t="inlineStr">
         <is>
           <t>sin datos</t>
         </is>
       </c>
-      <c r="AA17" t="inlineStr">
+      <c r="AB17" t="inlineStr">
         <is>
           <t>sin dato</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
+      <c r="AC17" t="inlineStr">
         <is>
           <t>sin dato</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
+      <c r="AD17" t="inlineStr">
         <is>
           <t>sin dato</t>
         </is>
       </c>
-      <c r="AD17" t="inlineStr">
+      <c r="AE17" t="inlineStr">
         <is>
           <t>sin dato</t>
         </is>
       </c>
-      <c r="AE17" t="inlineStr">
+      <c r="AF17" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
@@ -2433,88 +2518,88 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
+          <t>Hepatitis virales</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
           <t>Hepatitis B</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Hepatitis virales</t>
-        </is>
-      </c>
       <c r="E18" t="inlineStr">
         <is>
+          <t>Hepatitis virales</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>LLAMPA</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>ROSALIA SABINA</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>HERNANDO DE MAGALLANES</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>2441</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>USHUAIA</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>S/D</t>
         </is>
       </c>
-      <c r="L18">
+      <c r="M18">
         <v>53</v>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>DNI</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>DIRECCION DE EPIDEMIOLOGIA E INFORMACION DE LA SALUD</t>
         </is>
       </c>
-      <c r="P18">
+      <c r="Q18">
         <v>44932</v>
       </c>
-      <c r="Q18" t="inlineStr">
+      <c r="R18" t="inlineStr">
         <is>
           <t>44873</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>44873</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>*sin dato*</t>
-        </is>
-      </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>*sin dato*</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2524,7 +2609,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>*sin dato*</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
@@ -2534,19 +2619,19 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>*sin dato*</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>Crónica</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>NO</t>
@@ -2568,6 +2653,11 @@
         </is>
       </c>
       <c r="AE18" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
@@ -2584,55 +2674,55 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
+          <t>Hepatitis virales</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
           <t>Hepatitis B</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>CALISAYA</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>ILDA</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>USHUAIA</t>
         </is>
       </c>
-      <c r="L19">
+      <c r="M19">
         <v>62</v>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>HOSPITAL SALTA</t>
         </is>
       </c>
-      <c r="P19">
+      <c r="Q19">
         <v>44805</v>
       </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="Y19" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>Crónica</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>NO</t>
@@ -2654,6 +2744,11 @@
         </is>
       </c>
       <c r="AE19" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
@@ -2670,80 +2765,80 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
+          <t>Banco de Sangre</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
           <t>Hepatitis B</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>Banco de Sangre</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>02. Caso sospechoso en banco de sangre</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>CASTRO</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>SILVIO ALFREDO</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>Kau</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>534</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>RIO GRANDE</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>S/D</t>
         </is>
       </c>
-      <c r="L20">
+      <c r="M20">
         <v>40</v>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>DNI</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>HOSPITAL REGIONAL NUESTRA SEÑORA DE LA CANDELARIA.</t>
         </is>
       </c>
-      <c r="P20">
+      <c r="Q20">
         <v>43598</v>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="R20" t="inlineStr">
         <is>
           <t>43556</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>*sin dato*</t>
-        </is>
-      </c>
       <c r="S20" t="inlineStr">
         <is>
           <t>*sin dato*</t>
@@ -2771,10 +2866,15 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>*sin dato*</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
         <is>
           <t>Sin datos</t>
         </is>
@@ -2791,88 +2891,88 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
+          <t>Hepatitis virales</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
           <t>Hepatitis B</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Hepatitis virales</t>
-        </is>
-      </c>
       <c r="E21" t="inlineStr">
         <is>
+          <t>Hepatitis virales</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
           <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>PELLEGRINI</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>EDGARDO ENZO</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>JOSE MENENDEZ</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>952</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>*sin dato*</t>
-        </is>
-      </c>
       <c r="K21" t="inlineStr">
         <is>
+          <t>*sin dato*</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
           <t>S/D</t>
         </is>
       </c>
-      <c r="L21">
+      <c r="M21">
         <v>63</v>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>DNI</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>HOSPITAL REGIONAL NUESTRA SEÑORA DE LA CANDELARIA.</t>
         </is>
       </c>
-      <c r="P21">
+      <c r="Q21">
         <v>44928</v>
       </c>
-      <c r="Q21" t="inlineStr">
+      <c r="R21" t="inlineStr">
         <is>
           <t>44917</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>44917</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>*sin dato*</t>
-        </is>
-      </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>*sin dato*</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2882,7 +2982,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>*sin dato*</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
@@ -2892,40 +2992,45 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>*sin dato*</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
           <t>Crónica</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
           <t>sin dato</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
+      <c r="AC21" t="inlineStr">
         <is>
           <t>sin dato</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
+      <c r="AD21" t="inlineStr">
         <is>
           <t>sin dato</t>
         </is>
       </c>
-      <c r="AD21" t="inlineStr">
+      <c r="AE21" t="inlineStr">
         <is>
           <t>sin dato</t>
         </is>
       </c>
-      <c r="AE21" t="inlineStr">
+      <c r="AF21" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
@@ -2942,80 +3047,80 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
+          <t>Banco de Sangre</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
           <t>Hepatitis B</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>Banco de Sangre</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>01. Caso probable en banco de sangre</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>ALCOBA</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>LUISA AUDELINA</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>SARMIENTO</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>2879</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>RIO GRANDE</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>S/D</t>
         </is>
       </c>
-      <c r="L22">
+      <c r="M22">
         <v>39</v>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>DNI</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>HOSPITAL REGIONAL NUESTRA SEÑORA DE LA CANDELARIA.</t>
         </is>
       </c>
-      <c r="P22">
+      <c r="Q22">
         <v>43851</v>
       </c>
-      <c r="Q22" t="inlineStr">
+      <c r="R22" t="inlineStr">
         <is>
           <t>43804</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>*sin dato*</t>
-        </is>
-      </c>
       <c r="S22" t="inlineStr">
         <is>
           <t>*sin dato*</t>
@@ -3043,10 +3148,15 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>*sin dato*</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
         <is>
           <t>Sin datos</t>
         </is>
@@ -3063,80 +3173,80 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
+          <t>Banco de Sangre</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
           <t>Hepatitis B</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>Banco de Sangre</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>01. Caso probable en banco de sangre</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>VARGAS</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>ALDO WALTER</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>ANGELELLI</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>366</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>RIO GRANDE</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>S/D</t>
         </is>
       </c>
-      <c r="L23">
+      <c r="M23">
         <v>56</v>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t>DNI</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="P23" t="inlineStr">
         <is>
           <t>HOSPITAL REGIONAL NUESTRA SEÑORA DE LA CANDELARIA.</t>
         </is>
       </c>
-      <c r="P23">
+      <c r="Q23">
         <v>43675</v>
       </c>
-      <c r="Q23" t="inlineStr">
+      <c r="R23" t="inlineStr">
         <is>
           <t>43672</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>*sin dato*</t>
-        </is>
-      </c>
       <c r="S23" t="inlineStr">
         <is>
           <t>*sin dato*</t>
@@ -3164,10 +3274,15 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>*sin dato*</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
         <is>
           <t>Sin datos</t>
         </is>
@@ -3184,88 +3299,88 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
+          <t>Hepatitis virales</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
           <t>Hepatitis B</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Hepatitis virales</t>
-        </is>
-      </c>
       <c r="E24" t="inlineStr">
         <is>
+          <t>Hepatitis virales</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
           <t>07. Hepatitis B Resuelta - Infección Pasada</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>GUANDARILLO</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>ABEL MARCELO</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>PUERTO EGMONT</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>273</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>RIO GRANDE</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>S/D</t>
         </is>
       </c>
-      <c r="L24">
+      <c r="M24">
         <v>42</v>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>DNI</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="P24" t="inlineStr">
         <is>
           <t>HOSPITAL REGIONAL NUESTRA SEÑORA DE LA CANDELARIA.</t>
         </is>
       </c>
-      <c r="P24">
+      <c r="Q24">
         <v>45441</v>
       </c>
-      <c r="Q24" t="inlineStr">
+      <c r="R24" t="inlineStr">
         <is>
           <t>45407</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr">
+      <c r="S24" t="inlineStr">
         <is>
           <t>45407</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>*sin dato*</t>
-        </is>
-      </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>*sin dato*</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3275,7 +3390,7 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>*sin dato*</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
@@ -3285,19 +3400,19 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>*sin dato*</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
           <t>Resuelta</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>NO</t>
@@ -3319,6 +3434,11 @@
         </is>
       </c>
       <c r="AE24" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
@@ -3335,80 +3455,80 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
+          <t>Banco de Sangre</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
           <t>Hepatitis B</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>Banco de Sangre</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>02. Caso sospechoso en banco de sangre</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>YURQUINA</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>NECTOR OSCAR</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>CALLE S/NOMBRE 335 CASA</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>3214</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>RIO GRANDE</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>S/D</t>
         </is>
       </c>
-      <c r="L25">
+      <c r="M25">
         <v>39</v>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>DNI</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>HOSPITAL REGIONAL NUESTRA SEÑORA DE LA CANDELARIA.</t>
         </is>
       </c>
-      <c r="P25">
+      <c r="Q25">
         <v>43851</v>
       </c>
-      <c r="Q25" t="inlineStr">
+      <c r="R25" t="inlineStr">
         <is>
           <t>43812</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>*sin dato*</t>
-        </is>
-      </c>
       <c r="S25" t="inlineStr">
         <is>
           <t>*sin dato*</t>
@@ -3436,10 +3556,15 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>*sin dato*</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
         <is>
           <t>Sin datos</t>
         </is>
@@ -3456,88 +3581,88 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
+          <t>Banco de Sangre</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
           <t>Hepatitis B</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>Banco de Sangre</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>09. Caso CONFIRMADO de Infección OCULTA por VHB</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>VILLALOBOS</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>EVA MARIA</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>KAU</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>RIO GRANDE</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>S/D</t>
         </is>
       </c>
-      <c r="L26">
+      <c r="M26">
         <v>41</v>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>DNI</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="P26" t="inlineStr">
         <is>
           <t>HOSPITAL REGIONAL NUESTRA SEÑORA DE LA CANDELARIA.</t>
         </is>
       </c>
-      <c r="P26">
+      <c r="Q26">
         <v>45936</v>
       </c>
-      <c r="Q26" t="inlineStr">
+      <c r="R26" t="inlineStr">
         <is>
           <t>45918</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr">
+      <c r="S26" t="inlineStr">
         <is>
           <t>45918</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>*sin dato*</t>
-        </is>
-      </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>*sin dato*</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3547,7 +3672,7 @@
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>*sin dato*</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
@@ -3557,10 +3682,15 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>*sin dato*</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
         <is>
           <t>Sin datos</t>
         </is>
@@ -3577,80 +3707,80 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
+          <t>Banco de Sangre</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
           <t>Hepatitis B</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>Banco de Sangre</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>11. En estudio para hepatitis B</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>FIGEROA</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>VICTORIA ELENA</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>SHELK'NAM</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>692</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>RIO GRANDE</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t>S/D</t>
         </is>
       </c>
-      <c r="L27">
+      <c r="M27">
         <v>38</v>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>DNI</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="P27" t="inlineStr">
         <is>
           <t>HOSPITAL REGIONAL NUESTRA SEÑORA DE LA CANDELARIA.</t>
         </is>
       </c>
-      <c r="P27">
+      <c r="Q27">
         <v>43668</v>
       </c>
-      <c r="Q27" t="inlineStr">
+      <c r="R27" t="inlineStr">
         <is>
           <t>43658</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>*sin dato*</t>
-        </is>
-      </c>
       <c r="S27" t="inlineStr">
         <is>
           <t>*sin dato*</t>
@@ -3678,40 +3808,45 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>*sin dato*</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
           <t>Resuelta</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
+      <c r="AA27" t="inlineStr">
         <is>
           <t>sin datos</t>
         </is>
       </c>
-      <c r="AA27" t="inlineStr">
+      <c r="AB27" t="inlineStr">
         <is>
           <t>sin dato</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
+      <c r="AC27" t="inlineStr">
         <is>
           <t>sin dato</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
+      <c r="AD27" t="inlineStr">
         <is>
           <t>sin dato</t>
         </is>
       </c>
-      <c r="AD27" t="inlineStr">
+      <c r="AE27" t="inlineStr">
         <is>
           <t>sin dato</t>
         </is>
       </c>
-      <c r="AE27" t="inlineStr">
+      <c r="AF27" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
@@ -3728,130 +3863,130 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
+          <t>Hepatitis virales</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
           <t>Hepatitis B</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Hepatitis virales</t>
-        </is>
-      </c>
       <c r="E28" t="inlineStr">
         <is>
+          <t>Hepatitis virales</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
           <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>CAYO</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>RAMONA ANDREA</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>LASERRE</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>82</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>RIO GRANDE</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t>S/D</t>
         </is>
       </c>
-      <c r="L28">
+      <c r="M28">
         <v>69</v>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t>DNI</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="P28" t="inlineStr">
         <is>
           <t>HOSPITAL REGIONAL NUESTRA SEÑORA DE LA CANDELARIA.</t>
         </is>
       </c>
-      <c r="P28">
+      <c r="Q28">
         <v>44928</v>
       </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>*sin dato*</t>
-        </is>
-      </c>
       <c r="R28" t="inlineStr">
         <is>
+          <t>*sin dato*</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
           <t>42873</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
+      <c r="T28" t="inlineStr">
         <is>
           <t>40079</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="U28" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr">
+      <c r="W28" t="inlineStr">
         <is>
           <t>Entecavir</t>
         </is>
       </c>
-      <c r="W28" t="inlineStr">
+      <c r="X28" t="inlineStr">
         <is>
           <t>En tratamiento con carga negativa</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="Y28" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
           <t>Crónica</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="AC28" t="inlineStr">
         <is>
           <t>NO</t>
@@ -3859,10 +3994,15 @@
       </c>
       <c r="AD28" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="AE28" t="inlineStr">
+      <c r="AF28" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
@@ -3879,88 +4019,88 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
+          <t>Banco de Sangre</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
           <t>Hepatitis B</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>Banco de Sangre</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>09. Caso CONFIRMADO de Infección OCULTA por VHB</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>ORTIZ</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>NATALIA ALEJANDRA</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>TRANSPORTE SANTA MICAELA</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>2761</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>RIO GRANDE</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>S/D</t>
         </is>
       </c>
-      <c r="L29">
+      <c r="M29">
         <v>32</v>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>DNI</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
+      <c r="P29" t="inlineStr">
         <is>
           <t>HOSPITAL REGIONAL NUESTRA SEÑORA DE LA CANDELARIA.</t>
         </is>
       </c>
-      <c r="P29">
+      <c r="Q29">
         <v>45733</v>
       </c>
-      <c r="Q29" t="inlineStr">
+      <c r="R29" t="inlineStr">
         <is>
           <t>45677</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr">
+      <c r="S29" t="inlineStr">
         <is>
           <t>45684</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>*sin dato*</t>
-        </is>
-      </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>*sin dato*</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3970,7 +4110,7 @@
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>*sin dato*</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
@@ -3980,10 +4120,15 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>*sin dato*</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
         <is>
           <t>Sin datos</t>
         </is>
@@ -4000,88 +4145,88 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
+          <t>Hepatitis virales</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
           <t>Hepatitis B</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Hepatitis virales</t>
-        </is>
-      </c>
       <c r="E30" t="inlineStr">
         <is>
+          <t>Hepatitis virales</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
           <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>OCAMPO</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>ELIO JAVIER</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>HERNANDO DE MAGALLANES</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>2442</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>USHUAIA</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>S/D</t>
         </is>
       </c>
-      <c r="L30">
+      <c r="M30">
         <v>77</v>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>DNI</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="P30" t="inlineStr">
         <is>
           <t>HOSPITAL REGIONAL USHUAIA GOBERNADOR ERNESTO M. CAMPOS</t>
         </is>
       </c>
-      <c r="P30">
+      <c r="Q30">
         <v>45565</v>
       </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>*sin dato*</t>
-        </is>
-      </c>
       <c r="R30" t="inlineStr">
         <is>
+          <t>*sin dato*</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
           <t>45537</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>*sin dato*</t>
-        </is>
-      </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>*sin dato*</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -4091,39 +4236,39 @@
       </c>
       <c r="V30" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
           <t>Tenofovir alafenamida (TAF)</t>
         </is>
       </c>
-      <c r="W30" t="inlineStr">
+      <c r="X30" t="inlineStr">
         <is>
           <t>Desconocido</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="Y30" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
           <t>Crónica</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="AC30" t="inlineStr">
         <is>
           <t>NO</t>
@@ -4135,6 +4280,11 @@
         </is>
       </c>
       <c r="AE30" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
@@ -4151,88 +4301,88 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
+          <t>Hepatitis virales</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
           <t>Hepatitis B</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Hepatitis virales</t>
-        </is>
-      </c>
       <c r="E31" t="inlineStr">
         <is>
+          <t>Hepatitis virales</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
           <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>PORTAL</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>HUGO CESAR</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>FRANCISCO RAMIREZ</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>575</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>USHUAIA</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>S/D</t>
         </is>
       </c>
-      <c r="L31">
+      <c r="M31">
         <v>50</v>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>DNI</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="P31" t="inlineStr">
         <is>
           <t>HOSPITAL REGIONAL USHUAIA GOBERNADOR ERNESTO M. CAMPOS</t>
         </is>
       </c>
-      <c r="P31">
+      <c r="Q31">
         <v>45244</v>
       </c>
-      <c r="Q31" t="inlineStr">
+      <c r="R31" t="inlineStr">
         <is>
           <t>44991</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr">
+      <c r="S31" t="inlineStr">
         <is>
           <t>44991</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>*sin dato*</t>
-        </is>
-      </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>*sin dato*</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -4242,7 +4392,7 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>*sin dato*</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
@@ -4252,19 +4402,19 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>*sin dato*</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
           <t>Crónica</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>NO</t>
@@ -4286,6 +4436,11 @@
         </is>
       </c>
       <c r="AE31" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
@@ -4302,100 +4457,100 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
+          <t>Hepatitis virales</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
           <t>Hepatitis B</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Hepatitis virales</t>
-        </is>
-      </c>
       <c r="E32" t="inlineStr">
         <is>
+          <t>Hepatitis virales</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
           <t>07. Hepatitis B Resuelta - Infección Pasada</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>FERRARESE</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>DALMACIO ESTEBAN</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>LAS AGUILAS</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>1441</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>USHUAIA</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>S/D</t>
         </is>
       </c>
-      <c r="L32">
+      <c r="M32">
         <v>70</v>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>DNI</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
+      <c r="P32" t="inlineStr">
         <is>
           <t>HOSPITAL REGIONAL USHUAIA GOBERNADOR ERNESTO M. CAMPOS</t>
         </is>
       </c>
-      <c r="P32">
+      <c r="Q32">
         <v>44701</v>
       </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>*sin dato*</t>
-        </is>
-      </c>
       <c r="R32" t="inlineStr">
         <is>
+          <t>*sin dato*</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
           <t>44581</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr">
+      <c r="T32" t="inlineStr">
         <is>
           <t>44565</t>
         </is>
       </c>
-      <c r="T32" t="inlineStr">
+      <c r="U32" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="U32" t="inlineStr">
+      <c r="V32" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>*sin dato*</t>
-        </is>
-      </c>
       <c r="W32" t="inlineStr">
         <is>
           <t>*sin dato*</t>
@@ -4403,19 +4558,19 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>*sin dato*</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
           <t>aguda y resuelta</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>NO</t>
@@ -4437,6 +4592,11 @@
         </is>
       </c>
       <c r="AE32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
         <is>
           <t>no corresponde</t>
         </is>
@@ -4453,80 +4613,80 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
+          <t>Banco de Sangre</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
           <t>Hepatitis B</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>Banco de Sangre</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>03. Caso PROBABLE de Infección por VHB</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>GRAMAJO</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>NORMANDO</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>VITO DUMAS CASA</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>USHUAIA</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t>S/D</t>
         </is>
       </c>
-      <c r="L33">
+      <c r="M33">
         <v>62</v>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t>DNI</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
+      <c r="P33" t="inlineStr">
         <is>
           <t>HOSPITAL REGIONAL USHUAIA GOBERNADOR ERNESTO M. CAMPOS</t>
         </is>
       </c>
-      <c r="P33">
+      <c r="Q33">
         <v>45414</v>
       </c>
-      <c r="Q33" t="inlineStr">
+      <c r="R33" t="inlineStr">
         <is>
           <t>45315</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>*sin dato*</t>
-        </is>
-      </c>
       <c r="S33" t="inlineStr">
         <is>
           <t>*sin dato*</t>
@@ -4554,10 +4714,15 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>*sin dato*</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
         <is>
           <t>descartado</t>
         </is>
@@ -4574,100 +4739,100 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
+          <t>Hepatitis virales</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
           <t>Hepatitis B</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Hepatitis virales</t>
-        </is>
-      </c>
       <c r="E34" t="inlineStr">
         <is>
+          <t>Hepatitis virales</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
           <t>06. Caso CONFIRMADO de Infección Aguda por VHB</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>GONZALEZ</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>OSVALDO CRISTIAN</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>INTENDENTE TORELLI</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>1046</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>USHUAIA</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t>S/D</t>
         </is>
       </c>
-      <c r="L34">
+      <c r="M34">
         <v>43</v>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t>DNI</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
+      <c r="P34" t="inlineStr">
         <is>
           <t>HOSPITAL REGIONAL USHUAIA GOBERNADOR ERNESTO M. CAMPOS</t>
         </is>
       </c>
-      <c r="P34">
+      <c r="Q34">
         <v>43707</v>
       </c>
-      <c r="Q34" t="inlineStr">
+      <c r="R34" t="inlineStr">
         <is>
           <t>43703</t>
         </is>
       </c>
-      <c r="R34" t="inlineStr">
+      <c r="S34" t="inlineStr">
         <is>
           <t>43712</t>
         </is>
       </c>
-      <c r="S34" t="inlineStr">
+      <c r="T34" t="inlineStr">
         <is>
           <t>43696</t>
         </is>
       </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="U34" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>*sin dato*</t>
-        </is>
-      </c>
       <c r="W34" t="inlineStr">
         <is>
           <t>*sin dato*</t>
@@ -4675,40 +4840,45 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>*sin dato*</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
           <t>Aguda</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
           <t>sin dato</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
+      <c r="AC34" t="inlineStr">
         <is>
           <t>sin dato</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
+      <c r="AD34" t="inlineStr">
         <is>
           <t>sin dato</t>
         </is>
       </c>
-      <c r="AD34" t="inlineStr">
+      <c r="AE34" t="inlineStr">
         <is>
           <t>sin dato</t>
         </is>
       </c>
-      <c r="AE34" t="inlineStr">
+      <c r="AF34" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
@@ -4725,100 +4895,100 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
+          <t>Hepatitis virales</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
           <t>Hepatitis B</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Hepatitis virales</t>
-        </is>
-      </c>
       <c r="E35" t="inlineStr">
         <is>
+          <t>Hepatitis virales</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
           <t>07. Hepatitis B Resuelta - Infección Pasada</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>DAVIDSON</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>ANDRES SILVIO DE LA CRUZ</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>HALCON PEREGRINO</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>421</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>USHUAIA</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t>S/D</t>
         </is>
       </c>
-      <c r="L35">
+      <c r="M35">
         <v>41</v>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
+      <c r="O35" t="inlineStr">
         <is>
           <t>DNI</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
+      <c r="P35" t="inlineStr">
         <is>
           <t>HOSPITAL REGIONAL USHUAIA GOBERNADOR ERNESTO M. CAMPOS</t>
         </is>
       </c>
-      <c r="P35">
+      <c r="Q35">
         <v>45595</v>
       </c>
-      <c r="Q35" t="inlineStr">
+      <c r="R35" t="inlineStr">
         <is>
           <t>45593</t>
         </is>
       </c>
-      <c r="R35" t="inlineStr">
+      <c r="S35" t="inlineStr">
         <is>
           <t>45593</t>
         </is>
       </c>
-      <c r="S35" t="inlineStr">
+      <c r="T35" t="inlineStr">
         <is>
           <t>45530</t>
         </is>
       </c>
-      <c r="T35" t="inlineStr">
+      <c r="U35" t="inlineStr">
         <is>
           <t>ND</t>
         </is>
       </c>
-      <c r="U35" t="inlineStr">
+      <c r="V35" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>*sin dato*</t>
-        </is>
-      </c>
       <c r="W35" t="inlineStr">
         <is>
           <t>*sin dato*</t>
@@ -4826,19 +4996,19 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>*sin dato*</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
           <t>aguda y resuelta</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>NO</t>
@@ -4860,6 +5030,11 @@
         </is>
       </c>
       <c r="AE35" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
         <is>
           <t>no corresponde</t>
         </is>
@@ -4876,75 +5051,75 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
+          <t>Banco de Sangre</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
           <t>Hepatitis B</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>Banco de Sangre</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>01. Caso probable en banco de sangre</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>AVALO</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>MARCELA MARIA ITATI</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>VICENTE CANGA</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>1918</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t>USHUAIA</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="L36" t="inlineStr">
         <is>
           <t>S/D</t>
         </is>
       </c>
-      <c r="L36">
+      <c r="M36">
         <v>43</v>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
+      <c r="O36" t="inlineStr">
         <is>
           <t>DNI</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr">
+      <c r="P36" t="inlineStr">
         <is>
           <t>HOSPITAL REGIONAL USHUAIA GOBERNADOR ERNESTO M. CAMPOS</t>
         </is>
       </c>
-      <c r="P36">
+      <c r="Q36">
         <v>44916</v>
       </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>*sin dato*</t>
-        </is>
-      </c>
       <c r="R36" t="inlineStr">
         <is>
           <t>*sin dato*</t>
@@ -4977,19 +5152,19 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>*sin dato*</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
           <t>Resuelta</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>NO</t>
@@ -5011,6 +5186,11 @@
         </is>
       </c>
       <c r="AE36" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
@@ -5027,75 +5207,75 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
+          <t>Banco de Sangre</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
           <t>Hepatitis B</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>Banco de Sangre</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>02. Caso sospechoso en banco de sangre</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>ANACHURI</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>PASCUAL</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>B OBRERO CASA</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t>USHUAIA</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="L37" t="inlineStr">
         <is>
           <t>S/D</t>
         </is>
       </c>
-      <c r="L37">
+      <c r="M37">
         <v>47</v>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
+      <c r="O37" t="inlineStr">
         <is>
           <t>DNI</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr">
+      <c r="P37" t="inlineStr">
         <is>
           <t>HOSPITAL REGIONAL USHUAIA GOBERNADOR ERNESTO M. CAMPOS</t>
         </is>
       </c>
-      <c r="P37">
+      <c r="Q37">
         <v>43739</v>
       </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>*sin dato*</t>
-        </is>
-      </c>
       <c r="R37" t="inlineStr">
         <is>
           <t>*sin dato*</t>
@@ -5128,10 +5308,15 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>*sin dato*</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
         <is>
           <t>Sin datos</t>
         </is>
@@ -5148,88 +5333,88 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
+          <t>Hepatitis virales</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
           <t>Hepatitis B</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Hepatitis virales</t>
-        </is>
-      </c>
       <c r="E38" t="inlineStr">
         <is>
+          <t>Hepatitis virales</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
           <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>FERREYRA</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>ARSENIA ISABEL</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>TIRA 16</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="K38" t="inlineStr">
         <is>
           <t>USHUAIA</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
+      <c r="L38" t="inlineStr">
         <is>
           <t>S/D</t>
         </is>
       </c>
-      <c r="L38">
+      <c r="M38">
         <v>70</v>
       </c>
-      <c r="M38" t="inlineStr">
+      <c r="N38" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr">
+      <c r="O38" t="inlineStr">
         <is>
           <t>DNI</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr">
+      <c r="P38" t="inlineStr">
         <is>
           <t>HOSPITAL REGIONAL USHUAIA GOBERNADOR ERNESTO M. CAMPOS</t>
         </is>
       </c>
-      <c r="P38">
+      <c r="Q38">
         <v>45244</v>
       </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>*sin dato*</t>
-        </is>
-      </c>
       <c r="R38" t="inlineStr">
         <is>
+          <t>*sin dato*</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
           <t>44445</t>
         </is>
       </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>*sin dato*</t>
-        </is>
-      </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>*sin dato*</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -5239,39 +5424,39 @@
       </c>
       <c r="V38" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
           <t>Entecavir</t>
         </is>
       </c>
-      <c r="W38" t="inlineStr">
+      <c r="X38" t="inlineStr">
         <is>
           <t>En tratamiento con carga negativa</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="Y38" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
           <t>Crónica</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="AC38" t="inlineStr">
         <is>
           <t>NO</t>
@@ -5283,6 +5468,11 @@
         </is>
       </c>
       <c r="AE38" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
@@ -5299,88 +5489,88 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
+          <t>Hepatitis virales</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
           <t>Hepatitis B</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Hepatitis virales</t>
-        </is>
-      </c>
       <c r="E39" t="inlineStr">
         <is>
+          <t>Hepatitis virales</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
           <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>YECGUANCHUY CHAVEZ</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>RAUL ANTONY</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>12 de Octubre y Maipu</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>*sin dato*</t>
-        </is>
-      </c>
       <c r="J39" t="inlineStr">
         <is>
+          <t>*sin dato*</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
           <t>USHUAIA</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
+      <c r="L39" t="inlineStr">
         <is>
           <t>S/D</t>
         </is>
       </c>
-      <c r="L39">
+      <c r="M39">
         <v>41</v>
       </c>
-      <c r="M39" t="inlineStr">
+      <c r="N39" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
+      <c r="O39" t="inlineStr">
         <is>
           <t>DNI</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr">
+      <c r="P39" t="inlineStr">
         <is>
           <t>HOSPITAL REGIONAL USHUAIA GOBERNADOR ERNESTO M. CAMPOS</t>
         </is>
       </c>
-      <c r="P39">
+      <c r="Q39">
         <v>45246</v>
       </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>*sin dato*</t>
-        </is>
-      </c>
       <c r="R39" t="inlineStr">
         <is>
+          <t>*sin dato*</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
           <t>45246</t>
         </is>
       </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>*sin dato*</t>
-        </is>
-      </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>*sin dato*</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -5390,39 +5580,39 @@
       </c>
       <c r="V39" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
           <t>Lamivudina/Tenofovir</t>
         </is>
       </c>
-      <c r="W39" t="inlineStr">
+      <c r="X39" t="inlineStr">
         <is>
           <t>En tratamiento con carga negativa</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="Y39" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
           <t>Crónica</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
+      <c r="AA39" t="inlineStr">
         <is>
           <t>HIV/HCV</t>
         </is>
       </c>
-      <c r="AA39" t="inlineStr">
+      <c r="AB39" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="AC39" t="inlineStr">
         <is>
           <t>NO</t>
@@ -5434,6 +5624,11 @@
         </is>
       </c>
       <c r="AE39" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
@@ -5450,80 +5645,80 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
+          <t>Hepatitis virales</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
           <t>Hepatitis B</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Hepatitis virales</t>
-        </is>
-      </c>
       <c r="E40" t="inlineStr">
         <is>
+          <t>Hepatitis virales</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
           <t>03. Caso PROBABLE de Infección por VHB</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>QUIROZ</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>LILIANA ROXANA</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>SECCION K MACIZO E LOTE</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>69</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="K40" t="inlineStr">
         <is>
           <t>USHUAIA</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
+      <c r="L40" t="inlineStr">
         <is>
           <t>S/D</t>
         </is>
       </c>
-      <c r="L40">
+      <c r="M40">
         <v>43</v>
       </c>
-      <c r="M40" t="inlineStr">
+      <c r="N40" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr">
+      <c r="O40" t="inlineStr">
         <is>
           <t>DNI</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr">
+      <c r="P40" t="inlineStr">
         <is>
           <t>HOSPITAL REGIONAL USHUAIA GOBERNADOR ERNESTO M. CAMPOS</t>
         </is>
       </c>
-      <c r="P40">
+      <c r="Q40">
         <v>44708</v>
       </c>
-      <c r="Q40" t="inlineStr">
+      <c r="R40" t="inlineStr">
         <is>
           <t>44705</t>
         </is>
       </c>
-      <c r="R40" t="inlineStr">
-        <is>
-          <t>*sin dato*</t>
-        </is>
-      </c>
       <c r="S40" t="inlineStr">
         <is>
           <t>*sin dato*</t>
@@ -5551,40 +5746,45 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>*sin dato*</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
           <t>Crónica</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
+      <c r="AA40" t="inlineStr">
         <is>
           <t>sin datos</t>
         </is>
       </c>
-      <c r="AA40" t="inlineStr">
+      <c r="AB40" t="inlineStr">
         <is>
           <t>sin dato</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
+      <c r="AC40" t="inlineStr">
         <is>
           <t>sin dato</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
+      <c r="AD40" t="inlineStr">
         <is>
           <t>sin dato</t>
         </is>
       </c>
-      <c r="AD40" t="inlineStr">
+      <c r="AE40" t="inlineStr">
         <is>
           <t>sin dato</t>
         </is>
       </c>
-      <c r="AE40" t="inlineStr">
+      <c r="AF40" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
@@ -5601,75 +5801,75 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
+          <t>Banco de Sangre</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
           <t>Hepatitis B</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>Banco de Sangre</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>02. Caso sospechoso en banco de sangre</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>CARI</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>EMANUEL BRIAN</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>B 640 VDAS. TIRA 19 PISO 1 DTO. C</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="K41" t="inlineStr">
         <is>
           <t>USHUAIA</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="L41" t="inlineStr">
         <is>
           <t>S/D</t>
         </is>
       </c>
-      <c r="L41">
+      <c r="M41">
         <v>23</v>
       </c>
-      <c r="M41" t="inlineStr">
+      <c r="N41" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr">
+      <c r="O41" t="inlineStr">
         <is>
           <t>DNI</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr">
+      <c r="P41" t="inlineStr">
         <is>
           <t>HOSPITAL REGIONAL USHUAIA GOBERNADOR ERNESTO M. CAMPOS</t>
         </is>
       </c>
-      <c r="P41">
+      <c r="Q41">
         <v>43739</v>
       </c>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>*sin dato*</t>
-        </is>
-      </c>
       <c r="R41" t="inlineStr">
         <is>
           <t>*sin dato*</t>
@@ -5702,19 +5902,19 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>*sin dato*</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
           <t>Resuelta</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>NO</t>
@@ -5736,6 +5936,11 @@
         </is>
       </c>
       <c r="AE41" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
@@ -5752,75 +5957,75 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
+          <t>Banco de Sangre</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
           <t>Hepatitis B</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>Banco de Sangre</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>01. Caso probable en banco de sangre</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>LAREO</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>MARINA PAULA</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>BAHIA GRANDE</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>3014</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="K42" t="inlineStr">
         <is>
           <t>USHUAIA</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t>S/D</t>
         </is>
       </c>
-      <c r="L42">
+      <c r="M42">
         <v>36</v>
       </c>
-      <c r="M42" t="inlineStr">
+      <c r="N42" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
+      <c r="O42" t="inlineStr">
         <is>
           <t>DNI</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr">
+      <c r="P42" t="inlineStr">
         <is>
           <t>HOSPITAL REGIONAL USHUAIA GOBERNADOR ERNESTO M. CAMPOS</t>
         </is>
       </c>
-      <c r="P42">
+      <c r="Q42">
         <v>44082</v>
       </c>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t>*sin dato*</t>
-        </is>
-      </c>
       <c r="R42" t="inlineStr">
         <is>
           <t>*sin dato*</t>
@@ -5853,10 +6058,15 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>*sin dato*</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
         <is>
           <t>Sin datos</t>
         </is>
@@ -5873,80 +6083,80 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
+          <t>Hepatitis virales</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
           <t>Hepatitis B</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Hepatitis virales</t>
-        </is>
-      </c>
       <c r="E43" t="inlineStr">
         <is>
+          <t>Hepatitis virales</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
           <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>VERA OYARZO</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>RUBEN MARCELO</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>BÂ° 640 VIVIENDAS TIRA</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="K43" t="inlineStr">
         <is>
           <t>USHUAIA</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="L43" t="inlineStr">
         <is>
           <t>S/D</t>
         </is>
       </c>
-      <c r="L43">
+      <c r="M43">
         <v>48</v>
       </c>
-      <c r="M43" t="inlineStr">
+      <c r="N43" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr">
+      <c r="O43" t="inlineStr">
         <is>
           <t>DNI</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr">
+      <c r="P43" t="inlineStr">
         <is>
           <t>HOSPITAL REGIONAL USHUAIA GOBERNADOR ERNESTO M. CAMPOS</t>
         </is>
       </c>
-      <c r="P43">
+      <c r="Q43">
         <v>46001</v>
       </c>
-      <c r="Q43" t="inlineStr">
+      <c r="R43" t="inlineStr">
         <is>
           <t>46001</t>
         </is>
       </c>
-      <c r="R43" t="inlineStr">
-        <is>
-          <t>*sin dato*</t>
-        </is>
-      </c>
       <c r="S43" t="inlineStr">
         <is>
           <t>*sin dato*</t>
@@ -5974,19 +6184,19 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>*sin dato*</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
           <t>Crónica</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>NO</t>
@@ -6008,6 +6218,11 @@
         </is>
       </c>
       <c r="AE43" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AF43" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
@@ -6024,98 +6239,98 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
+          <t>Hepatitis virales</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
           <t>Hepatitis B</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Hepatitis virales</t>
-        </is>
-      </c>
       <c r="E44" t="inlineStr">
         <is>
+          <t>Hepatitis virales</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
           <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>PEREZ</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>VILMA</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>LEUM</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t>1992</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="K44" t="inlineStr">
         <is>
           <t>USHUAIA</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="L44" t="inlineStr">
         <is>
           <t>S/D</t>
         </is>
       </c>
-      <c r="L44">
+      <c r="M44">
         <v>62</v>
       </c>
-      <c r="M44" t="inlineStr">
+      <c r="N44" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr">
+      <c r="O44" t="inlineStr">
         <is>
           <t>DNI</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr">
+      <c r="P44" t="inlineStr">
         <is>
           <t>HOSPITAL REGIONAL USHUAIA GOBERNADOR ERNESTO M. CAMPOS</t>
         </is>
       </c>
-      <c r="P44">
+      <c r="Q44">
         <v>45565</v>
       </c>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>*sin dato*</t>
-        </is>
-      </c>
       <c r="R44" t="inlineStr">
         <is>
+          <t>*sin dato*</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
           <t>45565</t>
         </is>
       </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>*sin dato*</t>
-        </is>
-      </c>
       <c r="T44" t="inlineStr">
         <is>
+          <t>*sin dato*</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
           <t>ND</t>
         </is>
       </c>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>*sin dato*</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="W44" t="inlineStr">
@@ -6125,19 +6340,19 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>*sin dato*</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
           <t>Crónica</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>NO</t>
@@ -6159,6 +6374,11 @@
         </is>
       </c>
       <c r="AE44" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AF44" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
@@ -6175,88 +6395,88 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
+          <t>Hepatitis virales</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
           <t>Hepatitis B</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Hepatitis virales</t>
-        </is>
-      </c>
       <c r="E45" t="inlineStr">
         <is>
+          <t>Hepatitis virales</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
           <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>BAZAN</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>JUAN FRANCO SANTIAGO</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>TEKENIKA</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t>238</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="K45" t="inlineStr">
         <is>
           <t>USHUAIA</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="L45" t="inlineStr">
         <is>
           <t>S/D</t>
         </is>
       </c>
-      <c r="L45">
+      <c r="M45">
         <v>43</v>
       </c>
-      <c r="M45" t="inlineStr">
+      <c r="N45" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr">
+      <c r="O45" t="inlineStr">
         <is>
           <t>DNI</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr">
+      <c r="P45" t="inlineStr">
         <is>
           <t>HOSPITAL REGIONAL USHUAIA GOBERNADOR ERNESTO M. CAMPOS</t>
         </is>
       </c>
-      <c r="P45">
+      <c r="Q45">
         <v>45244</v>
       </c>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>*sin dato*</t>
-        </is>
-      </c>
       <c r="R45" t="inlineStr">
         <is>
+          <t>*sin dato*</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
           <t>45239</t>
         </is>
       </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>*sin dato*</t>
-        </is>
-      </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>*sin dato*</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -6266,7 +6486,7 @@
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>*sin dato*</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="W45" t="inlineStr">
@@ -6276,19 +6496,19 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>*sin dato*</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
           <t>Crónica</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>NO</t>
@@ -6310,6 +6530,11 @@
         </is>
       </c>
       <c r="AE45" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AF45" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
@@ -6326,88 +6551,88 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
+          <t>Hepatitis virales</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
           <t>Hepatitis B</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Hepatitis virales</t>
-        </is>
-      </c>
       <c r="E46" t="inlineStr">
         <is>
+          <t>Hepatitis virales</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
           <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>MUÑOZ BUSTAMANTE</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>ELITA</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t>BÂ LAS RAICES CASA</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t>183</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="K46" t="inlineStr">
         <is>
           <t>USHUAIA</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="L46" t="inlineStr">
         <is>
           <t>S/D</t>
         </is>
       </c>
-      <c r="L46">
+      <c r="M46">
         <v>34</v>
       </c>
-      <c r="M46" t="inlineStr">
+      <c r="N46" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr">
+      <c r="O46" t="inlineStr">
         <is>
           <t>DNI</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr">
+      <c r="P46" t="inlineStr">
         <is>
           <t>HOSPITAL REGIONAL USHUAIA GOBERNADOR ERNESTO M. CAMPOS</t>
         </is>
       </c>
-      <c r="P46">
+      <c r="Q46">
         <v>45744</v>
       </c>
-      <c r="Q46" t="inlineStr">
+      <c r="R46" t="inlineStr">
         <is>
           <t>45686</t>
         </is>
       </c>
-      <c r="R46" t="inlineStr">
+      <c r="S46" t="inlineStr">
         <is>
           <t>45811</t>
         </is>
       </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>*sin dato*</t>
-        </is>
-      </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>*sin dato*</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -6417,7 +6642,7 @@
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>*sin dato*</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="W46" t="inlineStr">
@@ -6427,19 +6652,19 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>*sin dato*</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
           <t>Crónica</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>NO</t>
@@ -6461,6 +6686,11 @@
         </is>
       </c>
       <c r="AE46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AF46" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
@@ -6477,80 +6707,80 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
+          <t>Banco de Sangre</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
           <t>Hepatitis B</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>Banco de Sangre</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>03. Caso PROBABLE de Infección por VHB</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>MORAN</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>LAURA MABEL</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t>SOLDADO HECTOR H. AGUIRRE</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t>2464</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="K47" t="inlineStr">
         <is>
           <t>USHUAIA</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="L47" t="inlineStr">
         <is>
           <t>S/D</t>
         </is>
       </c>
-      <c r="L47">
+      <c r="M47">
         <v>53</v>
       </c>
-      <c r="M47" t="inlineStr">
+      <c r="N47" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr">
+      <c r="O47" t="inlineStr">
         <is>
           <t>DNI</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr">
+      <c r="P47" t="inlineStr">
         <is>
           <t>HOSPITAL REGIONAL USHUAIA GOBERNADOR ERNESTO M. CAMPOS</t>
         </is>
       </c>
-      <c r="P47">
+      <c r="Q47">
         <v>45876</v>
       </c>
-      <c r="Q47" t="inlineStr">
+      <c r="R47" t="inlineStr">
         <is>
           <t>45846</t>
         </is>
       </c>
-      <c r="R47" t="inlineStr">
-        <is>
-          <t>*sin dato*</t>
-        </is>
-      </c>
       <c r="S47" t="inlineStr">
         <is>
           <t>*sin dato*</t>
@@ -6578,19 +6808,19 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>*sin dato*</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
           <t>Resuelta</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>NO</t>
@@ -6612,6 +6842,11 @@
         </is>
       </c>
       <c r="AE47" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AF47" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
@@ -6628,80 +6863,80 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
+          <t>Hepatitis virales</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
           <t>Hepatitis B</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Hepatitis virales</t>
-        </is>
-      </c>
       <c r="E48" t="inlineStr">
         <is>
+          <t>Hepatitis virales</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
           <t>07. Hepatitis B Resuelta - Infección Pasada</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>AYALA</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>CARLA PATRICIA</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t>CEFERINO NAMUNCURá</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
+      <c r="K48" t="inlineStr">
         <is>
           <t>USHUAIA</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
+      <c r="L48" t="inlineStr">
         <is>
           <t>S/D</t>
         </is>
       </c>
-      <c r="L48">
+      <c r="M48">
         <v>57</v>
       </c>
-      <c r="M48" t="inlineStr">
+      <c r="N48" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr">
+      <c r="O48" t="inlineStr">
         <is>
           <t>DNI</t>
         </is>
       </c>
-      <c r="O48" t="inlineStr">
+      <c r="P48" t="inlineStr">
         <is>
           <t>HOSPITAL REGIONAL USHUAIA GOBERNADOR ERNESTO M. CAMPOS</t>
         </is>
       </c>
-      <c r="P48">
+      <c r="Q48">
         <v>45876</v>
       </c>
-      <c r="Q48" t="inlineStr">
+      <c r="R48" t="inlineStr">
         <is>
           <t>45670</t>
         </is>
       </c>
-      <c r="R48" t="inlineStr">
-        <is>
-          <t>*sin dato*</t>
-        </is>
-      </c>
       <c r="S48" t="inlineStr">
         <is>
           <t>*sin dato*</t>
@@ -6729,10 +6964,15 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>*sin dato*</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
         <is>
           <t>descartado</t>
         </is>
@@ -6749,80 +6989,80 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
+          <t>Hepatitis virales</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
           <t>Hepatitis B</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Hepatitis virales</t>
-        </is>
-      </c>
       <c r="E49" t="inlineStr">
         <is>
+          <t>Hepatitis virales</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
           <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>SOSA</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>SANDRA VIVIANA</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t>ERNESTO KRUND</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t>649</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="K49" t="inlineStr">
         <is>
           <t>TOLHUIN</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="L49" t="inlineStr">
         <is>
           <t>S/D</t>
         </is>
       </c>
-      <c r="L49">
+      <c r="M49">
         <v>37</v>
       </c>
-      <c r="M49" t="inlineStr">
+      <c r="N49" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr">
+      <c r="O49" t="inlineStr">
         <is>
           <t>DNI</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr">
+      <c r="P49" t="inlineStr">
         <is>
           <t>HOSPITAL REGIONAL USHUAIA GOBERNADOR ERNESTO M. CAMPOS</t>
         </is>
       </c>
-      <c r="P49">
+      <c r="Q49">
         <v>45169</v>
       </c>
-      <c r="Q49" t="inlineStr">
+      <c r="R49" t="inlineStr">
         <is>
           <t>45169</t>
         </is>
       </c>
-      <c r="R49" t="inlineStr">
-        <is>
-          <t>*sin dato*</t>
-        </is>
-      </c>
       <c r="S49" t="inlineStr">
         <is>
           <t>*sin dato*</t>
@@ -6850,40 +7090,45 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>*sin dato*</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
           <t>Crónica</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
+      <c r="AA49" t="inlineStr">
         <is>
           <t>sin datos</t>
         </is>
       </c>
-      <c r="AA49" t="inlineStr">
+      <c r="AB49" t="inlineStr">
         <is>
           <t>sin dato</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
+      <c r="AC49" t="inlineStr">
         <is>
           <t>sin dato</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
+      <c r="AD49" t="inlineStr">
         <is>
           <t>sin dato</t>
         </is>
       </c>
-      <c r="AD49" t="inlineStr">
+      <c r="AE49" t="inlineStr">
         <is>
           <t>sin dato</t>
         </is>
       </c>
-      <c r="AE49" t="inlineStr">
+      <c r="AF49" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
@@ -6900,80 +7145,80 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
+          <t>Banco de Sangre</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
           <t>Hepatitis B</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>Banco de Sangre</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>02. Caso sospechoso en banco de sangre</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>PEREA</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t>MARTIN ALFREDO</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t>CAMINO DEL VALLE</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t>2600</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
+      <c r="K50" t="inlineStr">
         <is>
           <t>USHUAIA</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
+      <c r="L50" t="inlineStr">
         <is>
           <t>S/D</t>
         </is>
       </c>
-      <c r="L50">
+      <c r="M50">
         <v>37</v>
       </c>
-      <c r="M50" t="inlineStr">
+      <c r="N50" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr">
+      <c r="O50" t="inlineStr">
         <is>
           <t>DNI</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr">
+      <c r="P50" t="inlineStr">
         <is>
           <t>HOSPITAL REGIONAL USHUAIA GOBERNADOR ERNESTO M. CAMPOS</t>
         </is>
       </c>
-      <c r="P50">
+      <c r="Q50">
         <v>43739</v>
       </c>
-      <c r="Q50" t="inlineStr">
+      <c r="R50" t="inlineStr">
         <is>
           <t>43626</t>
         </is>
       </c>
-      <c r="R50" t="inlineStr">
-        <is>
-          <t>*sin dato*</t>
-        </is>
-      </c>
       <c r="S50" t="inlineStr">
         <is>
           <t>*sin dato*</t>
@@ -7001,10 +7246,15 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>*sin dato*</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
         <is>
           <t>Sin datos</t>
         </is>
@@ -7021,98 +7271,98 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
+          <t>Hepatitis virales</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
           <t>Hepatitis B</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Hepatitis virales</t>
-        </is>
-      </c>
       <c r="E51" t="inlineStr">
         <is>
+          <t>Hepatitis virales</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
           <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>SENILLIANI MELCHIOR</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t>CECILIA</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t>AVDA. LEANDRO N. ALEM</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="J51" t="inlineStr">
         <is>
           <t>4595</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="K51" t="inlineStr">
         <is>
           <t>USHUAIA</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="L51" t="inlineStr">
         <is>
           <t>S/D</t>
         </is>
       </c>
-      <c r="L51">
+      <c r="M51">
         <v>38</v>
       </c>
-      <c r="M51" t="inlineStr">
+      <c r="N51" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr">
+      <c r="O51" t="inlineStr">
         <is>
           <t>DNI</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr">
+      <c r="P51" t="inlineStr">
         <is>
           <t>HOSPITAL REGIONAL USHUAIA GOBERNADOR ERNESTO M. CAMPOS</t>
         </is>
       </c>
-      <c r="P51">
+      <c r="Q51">
         <v>43692</v>
       </c>
-      <c r="Q51" t="inlineStr">
-        <is>
-          <t>*sin dato*</t>
-        </is>
-      </c>
       <c r="R51" t="inlineStr">
         <is>
+          <t>*sin dato*</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
           <t>43692</t>
         </is>
       </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>*sin dato*</t>
-        </is>
-      </c>
       <c r="T51" t="inlineStr">
         <is>
+          <t>*sin dato*</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
           <t>ND</t>
         </is>
       </c>
-      <c r="U51" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>*sin dato*</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="W51" t="inlineStr">
@@ -7122,19 +7372,19 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>*sin dato*</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
           <t>Crónica</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>NO</t>
@@ -7156,6 +7406,11 @@
         </is>
       </c>
       <c r="AE51" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AF51" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
@@ -7172,98 +7427,98 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
+          <t>Hepatitis virales</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
           <t>Hepatitis B</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Hepatitis virales</t>
-        </is>
-      </c>
       <c r="E52" t="inlineStr">
         <is>
+          <t>Hepatitis virales</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
           <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t>PAVLOV</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="H52" t="inlineStr">
         <is>
           <t>VANINA LORENA</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t>ERCILIA PEREZ</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="J52" t="inlineStr">
         <is>
           <t>1940</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
+      <c r="K52" t="inlineStr">
         <is>
           <t>USHUAIA</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
+      <c r="L52" t="inlineStr">
         <is>
           <t>S/D</t>
         </is>
       </c>
-      <c r="L52">
+      <c r="M52">
         <v>42</v>
       </c>
-      <c r="M52" t="inlineStr">
+      <c r="N52" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr">
+      <c r="O52" t="inlineStr">
         <is>
           <t>DNI</t>
         </is>
       </c>
-      <c r="O52" t="inlineStr">
+      <c r="P52" t="inlineStr">
         <is>
           <t>HOSPITAL REGIONAL USHUAIA GOBERNADOR ERNESTO M. CAMPOS</t>
         </is>
       </c>
-      <c r="P52">
+      <c r="Q52">
         <v>43692</v>
       </c>
-      <c r="Q52" t="inlineStr">
+      <c r="R52" t="inlineStr">
         <is>
           <t>42950</t>
         </is>
       </c>
-      <c r="R52" t="inlineStr">
+      <c r="S52" t="inlineStr">
         <is>
           <t>43692</t>
         </is>
       </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>*sin dato*</t>
-        </is>
-      </c>
       <c r="T52" t="inlineStr">
         <is>
+          <t>*sin dato*</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
           <t>ND</t>
         </is>
       </c>
-      <c r="U52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>*sin dato*</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="W52" t="inlineStr">
@@ -7273,19 +7528,19 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>*sin dato*</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
           <t>Crónica</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>NO</t>
@@ -7307,6 +7562,11 @@
         </is>
       </c>
       <c r="AE52" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AF52" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
@@ -7323,56 +7583,61 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
+          <t>Hepatitis virales</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
           <t>Hepatitis B</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Hepatitis virales</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Hepatitis virales</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
         <is>
           <t>NIEVA</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="H53" t="inlineStr">
         <is>
           <t>ENRIQUE ALBERTO</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="K53" t="inlineStr">
         <is>
           <t>USHUAIA</t>
         </is>
       </c>
-      <c r="L53">
+      <c r="M53">
         <v>51</v>
       </c>
-      <c r="M53" t="inlineStr">
+      <c r="N53" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="O53" t="inlineStr">
+      <c r="P53" t="inlineStr">
         <is>
           <t>HOSPITAL REGIONAL USHUAIA GOBERNADOR ERNESTO M. CAMPOS</t>
         </is>
       </c>
-      <c r="P53">
+      <c r="Q53">
         <v>44770</v>
       </c>
-      <c r="X53" t="inlineStr">
+      <c r="Y53" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="Y53" t="inlineStr">
+      <c r="Z53" t="inlineStr">
         <is>
           <t>Aguda</t>
         </is>
       </c>
-      <c r="AE53" t="inlineStr">
+      <c r="AF53" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
@@ -7389,100 +7654,100 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
+          <t>Hepatitis virales</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
           <t>Hepatitis B</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Hepatitis virales</t>
-        </is>
-      </c>
       <c r="E54" t="inlineStr">
         <is>
+          <t>Hepatitis virales</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
           <t>06. Caso CONFIRMADO de Infección Aguda por VHB</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t>VILLARREAL</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="H54" t="inlineStr">
         <is>
           <t>DANIEL EDUARDO</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t>FELIPE ROMERO TIRA 1</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="J54" t="inlineStr">
         <is>
           <t>325</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
+      <c r="K54" t="inlineStr">
         <is>
           <t>USHUAIA</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
+      <c r="L54" t="inlineStr">
         <is>
           <t>S/D</t>
         </is>
       </c>
-      <c r="L54">
+      <c r="M54">
         <v>57</v>
       </c>
-      <c r="M54" t="inlineStr">
+      <c r="N54" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr">
+      <c r="O54" t="inlineStr">
         <is>
           <t>DNI</t>
         </is>
       </c>
-      <c r="O54" t="inlineStr">
+      <c r="P54" t="inlineStr">
         <is>
           <t>HOSPITAL REGIONAL USHUAIA GOBERNADOR ERNESTO M. CAMPOS</t>
         </is>
       </c>
-      <c r="P54">
+      <c r="Q54">
         <v>45257</v>
       </c>
-      <c r="Q54" t="inlineStr">
+      <c r="R54" t="inlineStr">
         <is>
           <t>45257</t>
         </is>
       </c>
-      <c r="R54" t="inlineStr">
+      <c r="S54" t="inlineStr">
         <is>
           <t>45257</t>
         </is>
       </c>
-      <c r="S54" t="inlineStr">
+      <c r="T54" t="inlineStr">
         <is>
           <t>45253</t>
         </is>
       </c>
-      <c r="T54" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="U54" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="V54" t="inlineStr">
-        <is>
-          <t>*sin dato*</t>
-        </is>
-      </c>
       <c r="W54" t="inlineStr">
         <is>
           <t>*sin dato*</t>
@@ -7490,19 +7755,19 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>*sin dato*</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
           <t>Crónica</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>NO</t>
@@ -7520,10 +7785,15 @@
       </c>
       <c r="AD54" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AE54" t="inlineStr">
+        <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="AE54" t="inlineStr">
+      <c r="AF54" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
@@ -7540,130 +7810,130 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
+          <t>Hepatitis virales</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
           <t>Hepatitis B</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>Hepatitis virales</t>
-        </is>
-      </c>
       <c r="E55" t="inlineStr">
         <is>
+          <t>Hepatitis virales</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
           <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t>MOTTER</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="H55" t="inlineStr">
         <is>
           <t>DIEGO IGNACIO</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="I55" t="inlineStr">
         <is>
           <t>12 DE OCTUBRE</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
+      <c r="J55" t="inlineStr">
         <is>
           <t>178</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
+      <c r="K55" t="inlineStr">
         <is>
           <t>USHUAIA</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
+      <c r="L55" t="inlineStr">
         <is>
           <t>S/D</t>
         </is>
       </c>
-      <c r="L55">
+      <c r="M55">
         <v>44</v>
       </c>
-      <c r="M55" t="inlineStr">
+      <c r="N55" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr">
+      <c r="O55" t="inlineStr">
         <is>
           <t>DNI</t>
         </is>
       </c>
-      <c r="O55" t="inlineStr">
+      <c r="P55" t="inlineStr">
         <is>
           <t>HOSPITAL REGIONAL USHUAIA GOBERNADOR ERNESTO M. CAMPOS</t>
         </is>
       </c>
-      <c r="P55">
+      <c r="Q55">
         <v>44221</v>
       </c>
-      <c r="Q55" t="inlineStr">
+      <c r="R55" t="inlineStr">
         <is>
           <t>44140</t>
         </is>
       </c>
-      <c r="R55" t="inlineStr">
+      <c r="S55" t="inlineStr">
         <is>
           <t>44140</t>
         </is>
       </c>
-      <c r="S55" t="inlineStr">
+      <c r="T55" t="inlineStr">
         <is>
           <t>44124</t>
         </is>
       </c>
-      <c r="T55" t="inlineStr">
+      <c r="U55" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="U55" t="inlineStr">
+      <c r="V55" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="V55" t="inlineStr">
+      <c r="W55" t="inlineStr">
         <is>
           <t>Tenofovir</t>
         </is>
       </c>
-      <c r="W55" t="inlineStr">
+      <c r="X55" t="inlineStr">
         <is>
           <t>En tratamiento con carga negativa</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="Y55" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
           <t>Crónica</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
+      <c r="AA55" t="inlineStr">
         <is>
           <t>sin datos</t>
         </is>
       </c>
-      <c r="AA55" t="inlineStr">
+      <c r="AB55" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="AC55" t="inlineStr">
         <is>
           <t>NO</t>
@@ -7675,6 +7945,11 @@
         </is>
       </c>
       <c r="AE55" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AF55" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
@@ -7691,88 +7966,88 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
+          <t>Hepatitis virales</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
           <t>Hepatitis B</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Hepatitis virales</t>
-        </is>
-      </c>
       <c r="E56" t="inlineStr">
         <is>
+          <t>Hepatitis virales</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
           <t>12. Virus Hepatitis B</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t>CAMERA</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="H56" t="inlineStr">
         <is>
           <t>OMAR MIGUEL</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t>ALSINA</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
+      <c r="J56" t="inlineStr">
         <is>
           <t>2106</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
+      <c r="K56" t="inlineStr">
         <is>
           <t>CIUDAD DE BUENOS AIRES</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
+      <c r="L56" t="inlineStr">
         <is>
           <t>S/D</t>
         </is>
       </c>
-      <c r="L56">
+      <c r="M56">
         <v>62</v>
       </c>
-      <c r="M56" t="inlineStr">
+      <c r="N56" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr">
+      <c r="O56" t="inlineStr">
         <is>
           <t>DNI</t>
         </is>
       </c>
-      <c r="O56" t="inlineStr">
+      <c r="P56" t="inlineStr">
         <is>
           <t>HOSPITAL REGIONAL USHUAIA GOBERNADOR ERNESTO M. CAMPOS</t>
         </is>
       </c>
-      <c r="P56">
+      <c r="Q56">
         <v>44701</v>
       </c>
-      <c r="Q56" t="inlineStr">
-        <is>
-          <t>*sin dato*</t>
-        </is>
-      </c>
       <c r="R56" t="inlineStr">
         <is>
+          <t>*sin dato*</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
           <t>44410</t>
         </is>
       </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>*sin dato*</t>
-        </is>
-      </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>*sin dato*</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -7782,7 +8057,7 @@
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>*sin dato*</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="W56" t="inlineStr">
@@ -7792,29 +8067,29 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>*sin dato*</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
           <t>Crónica</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
+      <c r="AA56" t="inlineStr">
         <is>
           <t>HIV</t>
         </is>
       </c>
-      <c r="AA56" t="inlineStr">
+      <c r="AB56" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="AC56" t="inlineStr">
         <is>
           <t>NO</t>
@@ -7822,10 +8097,15 @@
       </c>
       <c r="AD56" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AE56" t="inlineStr">
+        <is>
           <t>sin dato</t>
         </is>
       </c>
-      <c r="AE56" t="inlineStr">
+      <c r="AF56" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
@@ -7842,80 +8122,80 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
+          <t>Hepatitis virales</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
           <t>Hepatitis B</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>Hepatitis virales</t>
-        </is>
-      </c>
       <c r="E57" t="inlineStr">
         <is>
+          <t>Hepatitis virales</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
           <t>03. Caso PROBABLE de Infección por VHB</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>ESTIGARRIBIA ACOSTA</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="H57" t="inlineStr">
         <is>
           <t>CLAUDIO</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t>METET</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="J57" t="inlineStr">
         <is>
           <t>361</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
+      <c r="K57" t="inlineStr">
         <is>
           <t>TOLHUIN</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
+      <c r="L57" t="inlineStr">
         <is>
           <t>S/D</t>
         </is>
       </c>
-      <c r="L57">
+      <c r="M57">
         <v>63</v>
       </c>
-      <c r="M57" t="inlineStr">
+      <c r="N57" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr">
+      <c r="O57" t="inlineStr">
         <is>
           <t>DNI</t>
         </is>
       </c>
-      <c r="O57" t="inlineStr">
+      <c r="P57" t="inlineStr">
         <is>
           <t>HOSPITAL REGIONAL USHUAIA GOBERNADOR ERNESTO M. CAMPOS</t>
         </is>
       </c>
-      <c r="P57">
+      <c r="Q57">
         <v>45777</v>
       </c>
-      <c r="Q57" t="inlineStr">
+      <c r="R57" t="inlineStr">
         <is>
           <t>45777</t>
         </is>
       </c>
-      <c r="R57" t="inlineStr">
-        <is>
-          <t>*sin dato*</t>
-        </is>
-      </c>
       <c r="S57" t="inlineStr">
         <is>
           <t>*sin dato*</t>
@@ -7943,19 +8223,19 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>*sin dato*</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
           <t>Crónica</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>NO</t>
@@ -7977,6 +8257,11 @@
         </is>
       </c>
       <c r="AE57" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AF57" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
@@ -7993,65 +8278,65 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
+          <t>Hepatitis virales</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
           <t>Hepatitis B</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>Hepatitis virales</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Hepatitis virales</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
         <is>
           <t>GONZALEZ</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="H58" t="inlineStr">
         <is>
           <t>GUILLERMO OSCAR</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
+      <c r="K58" t="inlineStr">
         <is>
           <t>USHUAIA</t>
         </is>
       </c>
-      <c r="L58">
+      <c r="M58">
         <v>33</v>
       </c>
-      <c r="M58" t="inlineStr">
+      <c r="N58" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="P58">
+      <c r="Q58">
         <v>43875</v>
       </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="Y58" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
           <t>Crónica</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
+      <c r="AA58" t="inlineStr">
         <is>
           <t>HIV</t>
         </is>
       </c>
-      <c r="AA58" t="inlineStr">
+      <c r="AB58" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="AC58" t="inlineStr">
         <is>
           <t>NO</t>
@@ -8059,10 +8344,15 @@
       </c>
       <c r="AD58" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AE58" t="inlineStr">
+        <is>
           <t>sin dato</t>
         </is>
       </c>
-      <c r="AE58" t="inlineStr">
+      <c r="AF58" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
@@ -8079,100 +8369,100 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
+          <t>Hepatitis virales</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
           <t>Hepatitis B</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>Hepatitis virales</t>
-        </is>
-      </c>
       <c r="E59" t="inlineStr">
         <is>
+          <t>Hepatitis virales</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
           <t>06. Caso CONFIRMADO de Infección Aguda por VHB</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t>SEQUEIRA</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="H59" t="inlineStr">
         <is>
           <t>SILVANO JOAQUIN</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t>PASAJE AYELEN</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
+      <c r="J59" t="inlineStr">
         <is>
           <t>185</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
+      <c r="K59" t="inlineStr">
         <is>
           <t>USHUAIA</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
+      <c r="L59" t="inlineStr">
         <is>
           <t>S/D</t>
         </is>
       </c>
-      <c r="L59">
+      <c r="M59">
         <v>36</v>
       </c>
-      <c r="M59" t="inlineStr">
+      <c r="N59" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="N59" t="inlineStr">
+      <c r="O59" t="inlineStr">
         <is>
           <t>DNI</t>
         </is>
       </c>
-      <c r="O59" t="inlineStr">
+      <c r="P59" t="inlineStr">
         <is>
           <t>HOSPITAL REGIONAL USHUAIA GOBERNADOR ERNESTO M. CAMPOS</t>
         </is>
       </c>
-      <c r="P59">
+      <c r="Q59">
         <v>43846</v>
       </c>
-      <c r="Q59" t="inlineStr">
+      <c r="R59" t="inlineStr">
         <is>
           <t>43846</t>
         </is>
       </c>
-      <c r="R59" t="inlineStr">
+      <c r="S59" t="inlineStr">
         <is>
           <t>44140</t>
         </is>
       </c>
-      <c r="S59" t="inlineStr">
+      <c r="T59" t="inlineStr">
         <is>
           <t>44133</t>
         </is>
       </c>
-      <c r="T59" t="inlineStr">
+      <c r="U59" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="U59" t="inlineStr">
+      <c r="V59" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="V59" t="inlineStr">
-        <is>
-          <t>*sin dato*</t>
-        </is>
-      </c>
       <c r="W59" t="inlineStr">
         <is>
           <t>*sin dato*</t>
@@ -8180,19 +8470,19 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>*sin dato*</t>
         </is>
       </c>
       <c r="Y59" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
           <t>aguda y resuelta</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>NO</t>
@@ -8214,6 +8504,11 @@
         </is>
       </c>
       <c r="AE59" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AF59" t="inlineStr">
         <is>
           <t>no corresponde</t>
         </is>
@@ -8230,88 +8525,88 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
+          <t>Hepatitis virales</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
           <t>Hepatitis B</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>Hepatitis virales</t>
-        </is>
-      </c>
       <c r="E60" t="inlineStr">
         <is>
+          <t>Hepatitis virales</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
           <t>04. Caso CONFIRMADO de Infección por VHB</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t>PRETO</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="H60" t="inlineStr">
         <is>
           <t>CATALINA</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="I60" t="inlineStr">
         <is>
           <t>DEL TOLKEYEN</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
+      <c r="J60" t="inlineStr">
         <is>
           <t>2145</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr">
+      <c r="K60" t="inlineStr">
         <is>
           <t>USHUAIA</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
+      <c r="L60" t="inlineStr">
         <is>
           <t>S/D</t>
         </is>
       </c>
-      <c r="L60">
+      <c r="M60">
         <v>72</v>
       </c>
-      <c r="M60" t="inlineStr">
+      <c r="N60" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="N60" t="inlineStr">
+      <c r="O60" t="inlineStr">
         <is>
           <t>DNI</t>
         </is>
       </c>
-      <c r="O60" t="inlineStr">
+      <c r="P60" t="inlineStr">
         <is>
           <t>HOSPITAL REGIONAL USHUAIA GOBERNADOR ERNESTO M. CAMPOS</t>
         </is>
       </c>
-      <c r="P60">
+      <c r="Q60">
         <v>45925</v>
       </c>
-      <c r="Q60" t="inlineStr">
+      <c r="R60" t="inlineStr">
         <is>
           <t>45919</t>
         </is>
       </c>
-      <c r="R60" t="inlineStr">
+      <c r="S60" t="inlineStr">
         <is>
           <t>45919</t>
         </is>
       </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>*sin dato*</t>
-        </is>
-      </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>*sin dato*</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -8321,7 +8616,7 @@
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>*sin dato*</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="W60" t="inlineStr">
@@ -8331,29 +8626,29 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
+          <t>*sin dato*</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="Y60" t="inlineStr">
+      <c r="Z60" t="inlineStr">
         <is>
           <t>Crónica</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="AC60" t="inlineStr">
         <is>
           <t>NO</t>
@@ -8365,6 +8660,11 @@
         </is>
       </c>
       <c r="AE60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AF60" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
@@ -8381,88 +8681,88 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
+          <t>Hepatitis virales</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
           <t>Hepatitis B</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>Hepatitis virales</t>
-        </is>
-      </c>
       <c r="E61" t="inlineStr">
         <is>
+          <t>Hepatitis virales</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
           <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t>PEÑALOZA</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="H61" t="inlineStr">
         <is>
           <t>LUIS ALBERTO</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="I61" t="inlineStr">
         <is>
           <t>MOSCONI</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
+      <c r="J61" t="inlineStr">
         <is>
           <t>1370</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr">
+      <c r="K61" t="inlineStr">
         <is>
           <t>RIO GRANDE</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
+      <c r="L61" t="inlineStr">
         <is>
           <t>S/D</t>
         </is>
       </c>
-      <c r="L61">
+      <c r="M61">
         <v>58</v>
       </c>
-      <c r="M61" t="inlineStr">
+      <c r="N61" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr">
+      <c r="O61" t="inlineStr">
         <is>
           <t>DNI</t>
         </is>
       </c>
-      <c r="O61" t="inlineStr">
+      <c r="P61" t="inlineStr">
         <is>
           <t>HOSPITAL REGIONAL USHUAIA GOBERNADOR ERNESTO M. CAMPOS</t>
         </is>
       </c>
-      <c r="P61">
+      <c r="Q61">
         <v>45244</v>
       </c>
-      <c r="Q61" t="inlineStr">
+      <c r="R61" t="inlineStr">
         <is>
           <t>39035</t>
         </is>
       </c>
-      <c r="R61" t="inlineStr">
+      <c r="S61" t="inlineStr">
         <is>
           <t>45014</t>
         </is>
       </c>
-      <c r="S61" t="inlineStr">
-        <is>
-          <t>*sin dato*</t>
-        </is>
-      </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>*sin dato*</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -8472,7 +8772,7 @@
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>*sin dato*</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="W61" t="inlineStr">
@@ -8482,19 +8782,19 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>*sin dato*</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
           <t>Crónica</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>NO</t>
@@ -8516,6 +8816,11 @@
         </is>
       </c>
       <c r="AE61" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AF61" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
@@ -8532,88 +8837,88 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
+          <t>Hepatitis virales</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
           <t>Hepatitis B</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>Hepatitis virales</t>
-        </is>
-      </c>
       <c r="E62" t="inlineStr">
         <is>
+          <t>Hepatitis virales</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
           <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t>MOLINA</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="H62" t="inlineStr">
         <is>
           <t>VICENTE DURVAL</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="I62" t="inlineStr">
         <is>
           <t>RINCON DEL BOSQUE</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
+      <c r="J62" t="inlineStr">
         <is>
           <t>870</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr">
+      <c r="K62" t="inlineStr">
         <is>
           <t>USHUAIA</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
+      <c r="L62" t="inlineStr">
         <is>
           <t>S/D</t>
         </is>
       </c>
-      <c r="L62">
+      <c r="M62">
         <v>55</v>
       </c>
-      <c r="M62" t="inlineStr">
+      <c r="N62" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="N62" t="inlineStr">
+      <c r="O62" t="inlineStr">
         <is>
           <t>DNI</t>
         </is>
       </c>
-      <c r="O62" t="inlineStr">
+      <c r="P62" t="inlineStr">
         <is>
           <t>HOSPITAL REGIONAL USHUAIA GOBERNADOR ERNESTO M. CAMPOS</t>
         </is>
       </c>
-      <c r="P62">
+      <c r="Q62">
         <v>45240</v>
       </c>
-      <c r="Q62" t="inlineStr">
+      <c r="R62" t="inlineStr">
         <is>
           <t>43514</t>
         </is>
       </c>
-      <c r="R62" t="inlineStr">
+      <c r="S62" t="inlineStr">
         <is>
           <t>43514</t>
         </is>
       </c>
-      <c r="S62" t="inlineStr">
-        <is>
-          <t>*sin dato*</t>
-        </is>
-      </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>*sin dato*</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -8623,7 +8928,7 @@
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>*sin dato*</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="W62" t="inlineStr">
@@ -8633,29 +8938,29 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>*sin dato*</t>
         </is>
       </c>
       <c r="Y62" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
           <t>Crónica</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="AC62" t="inlineStr">
         <is>
           <t>NO</t>
@@ -8667,6 +8972,11 @@
         </is>
       </c>
       <c r="AE62" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AF62" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
@@ -8683,88 +8993,88 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
+          <t>Hepatitis virales</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
           <t>Hepatitis B</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>Hepatitis virales</t>
-        </is>
-      </c>
       <c r="E63" t="inlineStr">
         <is>
+          <t>Hepatitis virales</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
           <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="G63" t="inlineStr">
         <is>
           <t>FERREYRA</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="H63" t="inlineStr">
         <is>
           <t>RICARDO MANUEL</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="I63" t="inlineStr">
         <is>
           <t>SOBERANIA NACIONAL</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
+      <c r="J63" t="inlineStr">
         <is>
           <t>1793</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr">
+      <c r="K63" t="inlineStr">
         <is>
           <t>USHUAIA</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
+      <c r="L63" t="inlineStr">
         <is>
           <t>Obra social</t>
         </is>
       </c>
-      <c r="L63">
+      <c r="M63">
         <v>66</v>
       </c>
-      <c r="M63" t="inlineStr">
+      <c r="N63" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="N63" t="inlineStr">
+      <c r="O63" t="inlineStr">
         <is>
           <t>DNI</t>
         </is>
       </c>
-      <c r="O63" t="inlineStr">
+      <c r="P63" t="inlineStr">
         <is>
           <t>HOSPITAL REGIONAL USHUAIA GOBERNADOR ERNESTO M. CAMPOS</t>
         </is>
       </c>
-      <c r="P63">
+      <c r="Q63">
         <v>44693</v>
       </c>
-      <c r="Q63" t="inlineStr">
+      <c r="R63" t="inlineStr">
         <is>
           <t>44889</t>
         </is>
       </c>
-      <c r="R63" t="inlineStr">
+      <c r="S63" t="inlineStr">
         <is>
           <t>44524</t>
         </is>
       </c>
-      <c r="S63" t="inlineStr">
-        <is>
-          <t>*sin dato*</t>
-        </is>
-      </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>*sin dato*</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -8774,7 +9084,7 @@
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>*sin dato*</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="W63" t="inlineStr">
@@ -8784,19 +9094,19 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>*sin dato*</t>
         </is>
       </c>
       <c r="Y63" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
           <t>Crónica</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>NO</t>
@@ -8818,6 +9128,11 @@
         </is>
       </c>
       <c r="AE63" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AF63" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
@@ -8834,80 +9149,80 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
+          <t>Hepatitis virales</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
           <t>Hepatitis B</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>Hepatitis virales</t>
-        </is>
-      </c>
       <c r="E64" t="inlineStr">
         <is>
+          <t>Hepatitis virales</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
           <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t>ANDERSEN</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="H64" t="inlineStr">
         <is>
           <t>JOSE DAVID</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="I64" t="inlineStr">
         <is>
           <t>JULIO LEGUIZAMON</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
+      <c r="J64" t="inlineStr">
         <is>
           <t>92</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
+      <c r="K64" t="inlineStr">
         <is>
           <t>TOLHUIN</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
+      <c r="L64" t="inlineStr">
         <is>
           <t>S/D</t>
         </is>
       </c>
-      <c r="L64">
+      <c r="M64">
         <v>63</v>
       </c>
-      <c r="M64" t="inlineStr">
+      <c r="N64" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="N64" t="inlineStr">
+      <c r="O64" t="inlineStr">
         <is>
           <t>DNI</t>
         </is>
       </c>
-      <c r="O64" t="inlineStr">
+      <c r="P64" t="inlineStr">
         <is>
           <t>HOSPITAL REGIONAL USHUAIA GOBERNADOR ERNESTO M. CAMPOS</t>
         </is>
       </c>
-      <c r="P64">
+      <c r="Q64">
         <v>45370</v>
       </c>
-      <c r="Q64" t="inlineStr">
+      <c r="R64" t="inlineStr">
         <is>
           <t>45370</t>
         </is>
       </c>
-      <c r="R64" t="inlineStr">
-        <is>
-          <t>*sin dato*</t>
-        </is>
-      </c>
       <c r="S64" t="inlineStr">
         <is>
           <t>*sin dato*</t>
@@ -8935,40 +9250,45 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>*sin dato*</t>
         </is>
       </c>
       <c r="Y64" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
           <t>Crónica</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
+      <c r="AA64" t="inlineStr">
         <is>
           <t>sin datos</t>
         </is>
       </c>
-      <c r="AA64" t="inlineStr">
+      <c r="AB64" t="inlineStr">
         <is>
           <t>sin dato</t>
         </is>
       </c>
-      <c r="AB64" t="inlineStr">
+      <c r="AC64" t="inlineStr">
         <is>
           <t>sin dato</t>
         </is>
       </c>
-      <c r="AC64" t="inlineStr">
+      <c r="AD64" t="inlineStr">
         <is>
           <t>sin dato</t>
         </is>
       </c>
-      <c r="AD64" t="inlineStr">
+      <c r="AE64" t="inlineStr">
         <is>
           <t>sin dato</t>
         </is>
       </c>
-      <c r="AE64" t="inlineStr">
+      <c r="AF64" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
@@ -8985,75 +9305,75 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
+          <t>Banco de Sangre</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
           <t>Hepatitis B</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="E65" t="inlineStr">
         <is>
           <t>Banco de Sangre</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="F65" t="inlineStr">
         <is>
           <t>02. Caso sospechoso en banco de sangre</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="G65" t="inlineStr">
         <is>
           <t>CARMONA</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="H65" t="inlineStr">
         <is>
           <t>NORBERTO ALEJANDRO</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t>Inkuakayen</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
+      <c r="J65" t="inlineStr">
         <is>
           <t>1860</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr">
+      <c r="K65" t="inlineStr">
         <is>
           <t>USHUAIA</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
+      <c r="L65" t="inlineStr">
         <is>
           <t>S/D</t>
         </is>
       </c>
-      <c r="L65">
+      <c r="M65">
         <v>52</v>
       </c>
-      <c r="M65" t="inlineStr">
+      <c r="N65" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="N65" t="inlineStr">
+      <c r="O65" t="inlineStr">
         <is>
           <t>DNI</t>
         </is>
       </c>
-      <c r="O65" t="inlineStr">
+      <c r="P65" t="inlineStr">
         <is>
           <t>HOSPITAL REGIONAL USHUAIA GOBERNADOR ERNESTO M. CAMPOS</t>
         </is>
       </c>
-      <c r="P65">
+      <c r="Q65">
         <v>44082</v>
       </c>
-      <c r="Q65" t="inlineStr">
-        <is>
-          <t>*sin dato*</t>
-        </is>
-      </c>
       <c r="R65" t="inlineStr">
         <is>
           <t>*sin dato*</t>
@@ -9086,10 +9406,15 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>*sin dato*</t>
         </is>
       </c>
       <c r="Y65" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
         <is>
           <t>Sin datos</t>
         </is>
@@ -9106,75 +9431,75 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
+          <t>Banco de Sangre</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
           <t>Hepatitis B</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="E66" t="inlineStr">
         <is>
           <t>Banco de Sangre</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="F66" t="inlineStr">
         <is>
           <t>01. Caso probable en banco de sangre</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="G66" t="inlineStr">
         <is>
           <t>MELGAREJO</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="H66" t="inlineStr">
         <is>
           <t>ZULLY FRANCISCA EDITH</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="I66" t="inlineStr">
         <is>
           <t>JULIO TROXLER</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
+      <c r="J66" t="inlineStr">
         <is>
           <t>249</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr">
+      <c r="K66" t="inlineStr">
         <is>
           <t>USHUAIA</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
+      <c r="L66" t="inlineStr">
         <is>
           <t>S/D</t>
         </is>
       </c>
-      <c r="L66">
+      <c r="M66">
         <v>56</v>
       </c>
-      <c r="M66" t="inlineStr">
+      <c r="N66" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="N66" t="inlineStr">
+      <c r="O66" t="inlineStr">
         <is>
           <t>DNI</t>
         </is>
       </c>
-      <c r="O66" t="inlineStr">
+      <c r="P66" t="inlineStr">
         <is>
           <t>HOSPITAL REGIONAL USHUAIA GOBERNADOR ERNESTO M. CAMPOS</t>
         </is>
       </c>
-      <c r="P66">
+      <c r="Q66">
         <v>43739</v>
       </c>
-      <c r="Q66" t="inlineStr">
-        <is>
-          <t>*sin dato*</t>
-        </is>
-      </c>
       <c r="R66" t="inlineStr">
         <is>
           <t>*sin dato*</t>
@@ -9207,19 +9532,19 @@
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>*sin dato*</t>
         </is>
       </c>
       <c r="Y66" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
           <t>Resuelta</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>NO</t>
@@ -9241,6 +9566,11 @@
         </is>
       </c>
       <c r="AE66" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AF66" t="inlineStr">
         <is>
           <t>NO</t>
         </is>

--- a/Salidas/data_B_completa.xlsx
+++ b/Salidas/data_B_completa.xlsx
@@ -478,21 +478,21 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>28008546</v>
+        <v>14799238</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SENILLIANI MELCHIOR</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CECILIA</t>
+          <t>VILMA</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>De 35 a 44 años</t>
+          <t>De 45 a 65 años</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -516,21 +516,21 @@
         </is>
       </c>
       <c r="I2">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="J2">
-        <v>2019</v>
+        <v>2024</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2019-33</t>
+          <t>2024-40</t>
         </is>
       </c>
       <c r="L2" s="2">
-        <v>43692</v>
+        <v>45565</v>
       </c>
       <c r="M2" s="3">
-        <v>43692</v>
+        <v>45565</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -580,16 +580,16 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>27834459</v>
+        <v>29293036</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ALCOBA</t>
+          <t>CAJAL</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>LUISA AUDELINA</t>
+          <t>CAROLINA DE LOS ANGELES</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -609,39 +609,69 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Banco de Sangre</t>
+          <t>Hepatitis virales</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>01. Caso probable en banco de sangre</t>
+          <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
         </is>
       </c>
       <c r="I3">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="J3">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2019-49</t>
+          <t>2018-28</t>
         </is>
       </c>
       <c r="L3" s="2">
-        <v>43851</v>
+        <v>43298</v>
       </c>
       <c r="M3" s="3">
-        <v>43804</v>
+        <v>43292</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>RIO GRANDE</t>
+          <t>TOLHUIN</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Crónica</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>SI</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -652,21 +682,21 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>13454523</v>
+        <v>28096685</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PELLEGRINI</t>
+          <t>YURQUINA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>EDGARDO ENZO</t>
+          <t>NECTOR OSCAR</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>De 45 a 65 años</t>
+          <t>De 35 a 44 años</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -681,69 +711,39 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatitis virales</t>
+          <t>Banco de Sangre</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
+          <t>02. Caso sospechoso en banco de sangre</t>
         </is>
       </c>
       <c r="I4">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J4">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2022-51</t>
+          <t>2019-50</t>
         </is>
       </c>
       <c r="L4" s="2">
-        <v>44928</v>
+        <v>43851</v>
       </c>
       <c r="M4" s="3">
-        <v>44917</v>
+        <v>43812</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>*sin dato*</t>
+          <t>RIO GRANDE</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Crónica</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>SI</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -754,26 +754,26 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>26930068</v>
+        <v>11006818</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t>CAYO</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SILVIO ALFREDO</t>
+          <t>RAMONA ANDREA</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>De 35 a 44 años</t>
+          <t>Mayores de 65 años</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -783,30 +783,30 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Banco de Sangre</t>
+          <t>Hepatitis virales</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>02. Caso sospechoso en banco de sangre</t>
+          <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
         </is>
       </c>
       <c r="I5">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="J5">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2019-14</t>
+          <t>2017-20</t>
         </is>
       </c>
       <c r="L5" s="2">
-        <v>43598</v>
+        <v>44928</v>
       </c>
       <c r="M5" s="3">
-        <v>43556</v>
+        <v>42873</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -815,7 +815,37 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Crónica</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -826,21 +856,21 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>19092851</v>
+        <v>16859856</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PEREZ LUNA RAFAJLOVSKI</t>
+          <t>SCHOLLES</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>PARASHKEVA</t>
+          <t>MARTA GRACIELA</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>De 35 a 44 años</t>
+          <t>De 45 a 65 años</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -864,30 +894,30 @@
         </is>
       </c>
       <c r="I6">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="J6">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2023-35</t>
+          <t>2025-40</t>
         </is>
       </c>
       <c r="L6" s="2">
-        <v>45183</v>
+        <v>46093</v>
       </c>
       <c r="M6" s="3">
-        <v>45169</v>
+        <v>45929</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>RIO GRANDE</t>
+          <t>*sin dato*</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Crónica</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -917,7 +947,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -928,26 +958,26 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>95894978</v>
+        <v>18597623</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ROMERO QUIROGA</t>
+          <t>NUÑEZ</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CINTHIA SOLEDAD</t>
+          <t>JOSE JESUS</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>De 20 a 24 años</t>
+          <t>De 45 a 65 años</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -966,21 +996,21 @@
         </is>
       </c>
       <c r="I7">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J7">
         <v>2019</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2019-02</t>
+          <t>2019-07</t>
         </is>
       </c>
       <c r="L7" s="2">
         <v>43511</v>
       </c>
       <c r="M7" s="3">
-        <v>43472</v>
+        <v>43508</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -1030,16 +1060,16 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>20256616</v>
+        <v>25633171</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CARMONA</t>
+          <t>VERA OYARZO</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>NORBERTO ALEJANDRO</t>
+          <t>RUBEN MARCELO</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1059,30 +1089,30 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Banco de Sangre</t>
+          <t>Hepatitis virales</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>02. Caso sospechoso en banco de sangre</t>
+          <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
         </is>
       </c>
       <c r="I8">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="J8">
-        <v>2020</v>
+        <v>2025</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2020-14</t>
+          <t>2025-50</t>
         </is>
       </c>
       <c r="L8" s="2">
-        <v>44082</v>
+        <v>46001</v>
       </c>
       <c r="M8" s="3">
-        <v>43922</v>
+        <v>46001</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -1091,7 +1121,37 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Crónica</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1102,21 +1162,21 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>23140885</v>
+        <v>10619060</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PORTAL</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>HUGO CESAR</t>
+          <t>EDGARDO RUBEN</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>De 45 a 65 años</t>
+          <t>Mayores de 65 años</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1140,25 +1200,25 @@
         </is>
       </c>
       <c r="I9">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="J9">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2023-10</t>
+          <t>2021-23</t>
         </is>
       </c>
       <c r="L9" s="2">
-        <v>45244</v>
+        <v>44365</v>
       </c>
       <c r="M9" s="3">
-        <v>44991</v>
+        <v>44357</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>USHUAIA</t>
+          <t>TOLHUIN</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1173,7 +1233,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1193,7 +1253,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1204,16 +1264,16 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>29372354</v>
+        <v>30675706</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>GUANDARILLO</t>
+          <t>VILLALOBOS</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ABEL MARCELO</t>
+          <t>EVA MARIA</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1223,7 +1283,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1233,30 +1293,30 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatitis virales</t>
+          <t>Banco de Sangre</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>07. Hepatitis B Resuelta - Infección Pasada</t>
+          <t>09. Caso CONFIRMADO de Infección OCULTA por VHB</t>
         </is>
       </c>
       <c r="I10">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="J10">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2024-17</t>
+          <t>2025-38</t>
         </is>
       </c>
       <c r="L10" s="2">
-        <v>45441</v>
+        <v>45936</v>
       </c>
       <c r="M10" s="3">
-        <v>45407</v>
+        <v>45918</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -1265,37 +1325,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Resuelta</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1306,26 +1336,26 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>16150973</v>
+        <v>27422758</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>VARGAS</t>
+          <t>AVALO</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ALDO WALTER</t>
+          <t>MARCELA MARIA ITATI</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>De 45 a 65 años</t>
+          <t>De 35 a 44 años</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1340,34 +1370,64 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>01. Caso probable en banco de sangre</t>
+          <t>07. Hepatitis B Resuelta - Infección Pasada</t>
         </is>
       </c>
       <c r="I11">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="J11">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2019-30</t>
+          <t>2022-34</t>
         </is>
       </c>
       <c r="L11" s="2">
-        <v>43675</v>
+        <v>44916</v>
       </c>
       <c r="M11" s="3">
-        <v>43672</v>
+        <v>44796</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>RIO GRANDE</t>
+          <t>USHUAIA</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Resuelta</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1378,21 +1438,21 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>14450682</v>
+        <v>10312933</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GRAMAJO</t>
+          <t>FERRARESE</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>NORMANDO</t>
+          <t>DALMACIO ESTEBAN</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>De 45 a 65 años</t>
+          <t>Mayores de 65 años</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1407,39 +1467,69 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Banco de Sangre</t>
+          <t>Hepatitis virales</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>03. Caso PROBABLE de Infección por VHB</t>
+          <t>07. Hepatitis B Resuelta - Infección Pasada</t>
         </is>
       </c>
       <c r="I12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J12">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2022-03</t>
         </is>
       </c>
       <c r="L12" s="2">
-        <v>45414</v>
+        <v>44701</v>
       </c>
       <c r="M12" s="3">
-        <v>45315</v>
+        <v>44581</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>USHUAIA</t>
+          <t>*SIN DATO* (*SIN DATO*)</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Descartado</t>
+          <t>Aguda y resuelta</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>No corresponde</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1450,21 +1540,21 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>26710844</v>
+        <v>39202696</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>FLEITAS</t>
+          <t>CARI</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CARLOS FELIPE</t>
+          <t>EMANUEL BRIAN</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>De 35 a 44 años</t>
+          <t>De 20 a 24 años</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1479,7 +1569,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatitis virales</t>
+          <t>Banco de Sangre</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1488,30 +1578,30 @@
         </is>
       </c>
       <c r="I13">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J13">
-        <v>2023</v>
+        <v>2019</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2023-28</t>
+          <t>2019-27</t>
         </is>
       </c>
       <c r="L13" s="2">
-        <v>45122</v>
+        <v>43739</v>
       </c>
       <c r="M13" s="3">
-        <v>45118</v>
+        <v>43648</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>TOLHUIN</t>
+          <t>USHUAIA</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Crónica</t>
+          <t>Resuelta</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1541,7 +1631,7 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -1552,26 +1642,26 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>24557964</v>
+        <v>96420346</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>MUÑOZ BUSTAMANTE</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>OSVALDO CRISTIAN</t>
+          <t>ELITA</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>De 35 a 44 años</t>
+          <t>De 25 a 34 años</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1586,25 +1676,25 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>06. Caso CONFIRMADO de Infección Aguda por VHB</t>
+          <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
         </is>
       </c>
       <c r="I14">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="J14">
-        <v>2019</v>
+        <v>2025</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2019-35</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="L14" s="2">
-        <v>43707</v>
+        <v>45744</v>
       </c>
       <c r="M14" s="3">
-        <v>43703</v>
+        <v>45686</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -1613,7 +1703,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Aguda</t>
+          <t>Crónica</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1623,27 +1713,27 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -1654,16 +1744,16 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>30144181</v>
+        <v>94509088</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DAVIDSON</t>
+          <t>YECGUANCHUY CHAVEZ</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ANDRES SILVIO DE LA CRUZ</t>
+          <t>RAUL ANTONY</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1688,25 +1778,25 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>07. Hepatitis B Resuelta - Infección Pasada</t>
+          <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
         </is>
       </c>
       <c r="I15">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J15">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2024-44</t>
+          <t>2023-46</t>
         </is>
       </c>
       <c r="L15" s="2">
-        <v>45595</v>
+        <v>45246</v>
       </c>
       <c r="M15" s="3">
-        <v>45593</v>
+        <v>45246</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -1715,17 +1805,17 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Aguda y resuelta</t>
+          <t>Crónica</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>HIV/HCV</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1745,7 +1835,7 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>No corresponde</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -1756,21 +1846,21 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>38776020</v>
+        <v>22539485</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GODOY</t>
+          <t>CABRERA</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>DANIEL ALBERTO</t>
+          <t>MARIO ADRIAN</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>De 25 a 34 años</t>
+          <t>De 45 a 65 años</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1790,64 +1880,39 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>06. Caso CONFIRMADO de Infección Aguda por VHB</t>
+          <t>11. En estudio para hepatitis B</t>
         </is>
       </c>
       <c r="I16">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="J16">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2019-34</t>
+          <t>2020-51</t>
         </is>
       </c>
       <c r="L16" s="2">
-        <v>43714</v>
+        <v>44182</v>
       </c>
       <c r="M16" s="3">
-        <v>43697</v>
+        <v>44182</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>RIO GALLEGOS</t>
+          <t>RIO GRANDE</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Aguda</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>SI</t>
+          <t>HIV</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -1858,26 +1923,26 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>27047731</v>
+        <v>10857365</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CENA</t>
+          <t>FERREYRA</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>JUAN ALBERTO</t>
+          <t>ARSENIA ISABEL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>De 45 a 65 años</t>
+          <t>Mayores de 65 años</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1892,34 +1957,64 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>07. Hepatitis B Resuelta - Infección Pasada</t>
+          <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
         </is>
       </c>
       <c r="I17">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="J17">
-        <v>2017</v>
+        <v>2021</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2017-26</t>
+          <t>2021-36</t>
         </is>
       </c>
       <c r="L17" s="2">
-        <v>46139</v>
+        <v>45244</v>
       </c>
       <c r="M17" s="3">
-        <v>42914</v>
+        <v>44445</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>SAN IGNACIO</t>
+          <t>USHUAIA</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Crónica</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -1930,26 +2025,26 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>7930029</v>
+        <v>26421454</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>OCAMPO</t>
+          <t>QUIROZ</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ELIO JAVIER</t>
+          <t>LILIANA ROXANA</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Mayores de 65 años</t>
+          <t>De 35 a 44 años</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1968,21 +2063,21 @@
         </is>
       </c>
       <c r="I18">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="J18">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2024-36</t>
+          <t>2022-21</t>
         </is>
       </c>
       <c r="L18" s="2">
-        <v>45565</v>
+        <v>44708</v>
       </c>
       <c r="M18" s="3">
-        <v>45537</v>
+        <v>44705</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -1996,27 +2091,27 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2032,26 +2127,26 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>13861790</v>
+        <v>31761053</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CAMERA</t>
+          <t>SOSA</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>OMAR MIGUEL</t>
+          <t>SANDRA VIVIANA</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>De 45 a 65 años</t>
+          <t>De 35 a 44 años</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2066,29 +2161,29 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>12. Virus Hepatitis B</t>
+          <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
         </is>
       </c>
       <c r="I19">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J19">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2021-31</t>
+          <t>2023-35</t>
         </is>
       </c>
       <c r="L19" s="2">
-        <v>44701</v>
+        <v>45169</v>
       </c>
       <c r="M19" s="3">
-        <v>44410</v>
+        <v>45169</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>CIUDAD DE BUENOS AIRES</t>
+          <t>TOLHUIN</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -2098,22 +2193,22 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>HIV</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
@@ -2134,16 +2229,16 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>30702578</v>
+        <v>25800340</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>LAREO</t>
+          <t>PAVLOV</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MARINA PAULA</t>
+          <t>VANINA LORENA</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2163,30 +2258,30 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Banco de Sangre</t>
+          <t>Hepatitis virales</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>01. Caso probable en banco de sangre</t>
+          <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
         </is>
       </c>
       <c r="I20">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="J20">
-        <v>2020</v>
+        <v>2017</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2020-18</t>
+          <t>2017-31</t>
         </is>
       </c>
       <c r="L20" s="2">
-        <v>44082</v>
+        <v>43692</v>
       </c>
       <c r="M20" s="3">
-        <v>43951</v>
+        <v>42950</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -2195,7 +2290,37 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Crónica</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -2206,16 +2331,16 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>22534702</v>
+        <v>18117411</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ANACHURI</t>
+          <t>VILLARREAL</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>PASCUAL</t>
+          <t>DANIEL EDUARDO</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2235,30 +2360,30 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Banco de Sangre</t>
+          <t>Hepatitis virales</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>02. Caso sospechoso en banco de sangre</t>
+          <t>06. Caso CONFIRMADO de Infección Aguda por VHB</t>
         </is>
       </c>
       <c r="I21">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="J21">
-        <v>2019</v>
+        <v>2023</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2019-26</t>
+          <t>2023-48</t>
         </is>
       </c>
       <c r="L21" s="2">
-        <v>43739</v>
+        <v>45257</v>
       </c>
       <c r="M21" s="3">
-        <v>43644</v>
+        <v>45257</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -2267,7 +2392,37 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Crónica</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>SI</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -2278,26 +2433,26 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>14799238</v>
+        <v>25633109</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>MOTTER</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>VILMA</t>
+          <t>DIEGO IGNACIO</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>De 45 a 65 años</t>
+          <t>De 35 a 44 años</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2316,21 +2471,21 @@
         </is>
       </c>
       <c r="I22">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="J22">
-        <v>2024</v>
+        <v>2020</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2024-40</t>
+          <t>2020-45</t>
         </is>
       </c>
       <c r="L22" s="2">
-        <v>45565</v>
+        <v>44221</v>
       </c>
       <c r="M22" s="3">
-        <v>45565</v>
+        <v>44140</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -2344,12 +2499,12 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2380,26 +2535,26 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>29293036</v>
+        <v>22193794</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CAJAL</t>
+          <t>NIEVA</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CAROLINA DE LOS ANGELES</t>
+          <t>ENRIQUE ALBERTO</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>De 35 a 44 años</t>
+          <t>De 45 a 65 años</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2414,59 +2569,34 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
+          <t>04. Caso CONFIRMADO de Infección por VHB</t>
         </is>
       </c>
       <c r="I23">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J23">
-        <v>2018</v>
+        <v>2022</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2018-28</t>
+          <t>2022-30</t>
         </is>
       </c>
       <c r="L23" s="2">
-        <v>43298</v>
+        <v>46116</v>
       </c>
       <c r="M23" s="3">
-        <v>43292</v>
+        <v>44770</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>TOLHUIN</t>
+          <t>USHUAIA</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Crónica</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
+          <t>Aguda</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2476,27 +2606,27 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <v>11006818</v>
+        <v>41058767</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CAYO</t>
+          <t>GONZALEZ MOLINA</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>RAMONA ANDREA</t>
+          <t>LOURDES MARIANELA</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Mayores de 65 años</t>
+          <t>De 20 a 24 años</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2516,64 +2646,34 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
+          <t>Caso descartado Hepatitis B</t>
         </is>
       </c>
       <c r="I24">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="J24">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2017-20</t>
+          <t>2019-31</t>
         </is>
       </c>
       <c r="L24" s="2">
-        <v>44928</v>
+        <v>43689</v>
       </c>
       <c r="M24" s="3">
-        <v>42873</v>
+        <v>43677</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>RIO GRANDE</t>
+          <t>USHUAIA</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Crónica</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
@@ -2584,26 +2684,26 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>26421454</v>
+        <v>17396287</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>QUIROZ</t>
+          <t>LAMA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>LILIANA ROXANA</t>
+          <t>MIGUEL ANGEL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>De 35 a 44 años</t>
+          <t>De 45 a 65 años</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2618,25 +2718,25 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>03. Caso PROBABLE de Infección por VHB</t>
+          <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
         </is>
       </c>
       <c r="I25">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J25">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2022-21</t>
+          <t>2018-27</t>
         </is>
       </c>
       <c r="L25" s="2">
-        <v>44708</v>
+        <v>43424</v>
       </c>
       <c r="M25" s="3">
-        <v>44705</v>
+        <v>43286</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -2650,27 +2750,27 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -2686,21 +2786,21 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>28096685</v>
+        <v>37356837</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>YURQUINA</t>
+          <t>MONTEIRO TOLOSA</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>NECTOR OSCAR</t>
+          <t>ALBERTO EZEQUIEL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>De 35 a 44 años</t>
+          <t>De 25 a 34 años</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2715,39 +2815,69 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Banco de Sangre</t>
+          <t>Hepatitis virales</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>02. Caso sospechoso en banco de sangre</t>
+          <t>06. Caso CONFIRMADO de Infección Aguda por VHB</t>
         </is>
       </c>
       <c r="I26">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="J26">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2019-50</t>
+          <t>2021-35</t>
         </is>
       </c>
       <c r="L26" s="2">
-        <v>43851</v>
+        <v>46139</v>
       </c>
       <c r="M26" s="3">
-        <v>43812</v>
+        <v>44440</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>RIO GRANDE</t>
+          <t>TIGRE</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Aguda y resuelta</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>HIV</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>No corresponde</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
@@ -2758,21 +2888,21 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>16859856</v>
+        <v>28227396</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SCHOLLES</t>
+          <t>FIGEROA</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>MARTA GRACIELA</t>
+          <t>VICTORIA ELENA</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>De 45 a 65 años</t>
+          <t>De 35 a 44 años</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2787,39 +2917,39 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatitis virales</t>
+          <t>Banco de Sangre</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>12. Virus Hepatitis B</t>
+          <t>07. Hepatitis B Resuelta - Infección Pasada</t>
         </is>
       </c>
       <c r="I27">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="J27">
-        <v>2025</v>
+        <v>2019</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2025-40</t>
+          <t>2019-28</t>
         </is>
       </c>
       <c r="L27" s="2">
-        <v>46093</v>
+        <v>43668</v>
       </c>
       <c r="M27" s="3">
-        <v>45929</v>
+        <v>43658</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>*sin dato*</t>
+          <t>RIO GRANDE</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Resuelta</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -2849,7 +2979,7 @@
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
@@ -2860,21 +2990,21 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>10619060</v>
+        <v>14898515</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>SALAS</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>EDGARDO RUBEN</t>
+          <t>EVARISTO SILVANO</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Mayores de 65 años</t>
+          <t>De 45 a 65 años</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2898,25 +3028,25 @@
         </is>
       </c>
       <c r="I28">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J28">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2021-23</t>
+          <t>2018-20</t>
         </is>
       </c>
       <c r="L28" s="2">
-        <v>44365</v>
+        <v>43243</v>
       </c>
       <c r="M28" s="3">
-        <v>44357</v>
+        <v>43237</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>TOLHUIN</t>
+          <t>USHUAIA</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -2926,32 +3056,32 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
           <t>SI</t>
-        </is>
-      </c>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>NO</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
@@ -2962,21 +3092,21 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>25633171</v>
+        <v>33013011</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>VERA OYARZO</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>RUBEN MARCELO</t>
+          <t>GUILLERMO OSCAR</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>De 45 a 65 años</t>
+          <t>De 35 a 44 años</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3000,21 +3130,21 @@
         </is>
       </c>
       <c r="I29">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="J29">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2025-50</t>
+          <t>2024-17</t>
         </is>
       </c>
       <c r="L29" s="2">
-        <v>46001</v>
+        <v>45405</v>
       </c>
       <c r="M29" s="3">
-        <v>46001</v>
+        <v>45404</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
@@ -3028,12 +3158,12 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>HIV</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -3048,12 +3178,12 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
@@ -3064,21 +3194,21 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>18597623</v>
+        <v>30030925</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>NUÑEZ</t>
+          <t>SEQUEIRA</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>JOSE JESUS</t>
+          <t>SILVANO JOAQUIN</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>De 45 a 65 años</t>
+          <t>De 35 a 44 años</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3098,25 +3228,25 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>12. Virus Hepatitis B</t>
+          <t>06. Caso CONFIRMADO de Infección Aguda por VHB</t>
         </is>
       </c>
       <c r="I30">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J30">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2019-07</t>
+          <t>2020-03</t>
         </is>
       </c>
       <c r="L30" s="2">
-        <v>43511</v>
+        <v>43846</v>
       </c>
       <c r="M30" s="3">
-        <v>43508</v>
+        <v>43846</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
@@ -3125,37 +3255,37 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Crónica</t>
+          <t>Aguda y resuelta</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>No corresponde</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
@@ -3166,26 +3296,26 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>30675706</v>
+        <v>32207592</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>VILLALOBOS</t>
+          <t>ALVAREZ</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>EVA MARIA</t>
+          <t>FRANCISCO MANUEL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>De 35 a 44 años</t>
+          <t>De 25 a 34 años</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -3195,39 +3325,69 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Banco de Sangre</t>
+          <t>Hepatitis virales</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>09. Caso CONFIRMADO de Infección OCULTA por VHB</t>
+          <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
         </is>
       </c>
       <c r="I31">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="J31">
-        <v>2025</v>
+        <v>2017</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2025-38</t>
+          <t>2017-10</t>
         </is>
       </c>
       <c r="L31" s="2">
-        <v>45936</v>
+        <v>43706</v>
       </c>
       <c r="M31" s="3">
-        <v>45918</v>
+        <v>42804</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>RIO GRANDE</t>
+          <t>USHUAIA</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Crónica</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>HIV</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>SI</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
@@ -3238,26 +3398,26 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>10312933</v>
+        <v>16664022</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>FERRARESE</t>
+          <t>MELGAREJO</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>DALMACIO ESTEBAN</t>
+          <t>ZULLY FRANCISCA EDITH</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Mayores de 65 años</t>
+          <t>De 45 a 65 años</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -3267,7 +3427,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hepatitis virales</t>
+          <t>Banco de Sangre</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3276,30 +3436,30 @@
         </is>
       </c>
       <c r="I32">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="J32">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2022-03</t>
+          <t>2019-26</t>
         </is>
       </c>
       <c r="L32" s="2">
-        <v>44701</v>
+        <v>43739</v>
       </c>
       <c r="M32" s="3">
-        <v>44581</v>
+        <v>43644</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>*SIN DATO* (*SIN DATO*)</t>
+          <t>USHUAIA</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Aguda y resuelta</t>
+          <t>Resuelta</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3329,7 +3489,7 @@
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>No corresponde</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
@@ -3340,21 +3500,21 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>96420346</v>
+        <v>28008546</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>MUÑOZ BUSTAMANTE</t>
+          <t>SENILLIANI MELCHIOR</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ELITA</t>
+          <t>CECILIA</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>De 25 a 34 años</t>
+          <t>De 35 a 44 años</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3378,21 +3538,21 @@
         </is>
       </c>
       <c r="I33">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="J33">
-        <v>2025</v>
+        <v>2019</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2019-33</t>
         </is>
       </c>
       <c r="L33" s="2">
-        <v>45744</v>
+        <v>43692</v>
       </c>
       <c r="M33" s="3">
-        <v>45686</v>
+        <v>43692</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
@@ -3442,16 +3602,16 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>28227396</v>
+        <v>27834459</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>FIGEROA</t>
+          <t>ALCOBA</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>VICTORIA ELENA</t>
+          <t>LUISA AUDELINA</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -3476,25 +3636,25 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>11. En estudio para hepatitis B</t>
+          <t>01. Caso probable en banco de sangre</t>
         </is>
       </c>
       <c r="I34">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="J34">
         <v>2019</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2019-28</t>
+          <t>2019-49</t>
         </is>
       </c>
       <c r="L34" s="2">
-        <v>43668</v>
+        <v>43851</v>
       </c>
       <c r="M34" s="3">
-        <v>43658</v>
+        <v>43804</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
@@ -3503,37 +3663,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Resuelta</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="R34" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>SI</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
@@ -3544,16 +3674,16 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>94509088</v>
+        <v>26930068</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>YECGUANCHUY CHAVEZ</t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>RAUL ANTONY</t>
+          <t>SILVIO ALFREDO</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -3573,69 +3703,39 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hepatitis virales</t>
+          <t>Banco de Sangre</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
+          <t>02. Caso sospechoso en banco de sangre</t>
         </is>
       </c>
       <c r="I35">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="J35">
-        <v>2023</v>
+        <v>2019</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2023-46</t>
+          <t>2019-14</t>
         </is>
       </c>
       <c r="L35" s="2">
-        <v>45246</v>
+        <v>43598</v>
       </c>
       <c r="M35" s="3">
-        <v>45246</v>
+        <v>43556</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>USHUAIA</t>
+          <t>RIO GRANDE</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Crónica</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>HIV/HCV</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>SI</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -3646,16 +3746,16 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>22475930</v>
+        <v>13454523</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>MORAN</t>
+          <t>PELLEGRINI</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>LAURA MABEL</t>
+          <t>EDGARDO ENZO</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -3665,7 +3765,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -3675,39 +3775,39 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Banco de Sangre</t>
+          <t>Hepatitis virales</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>03. Caso PROBABLE de Infección por VHB</t>
+          <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
         </is>
       </c>
       <c r="I36">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="J36">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2025-28</t>
+          <t>2022-51</t>
         </is>
       </c>
       <c r="L36" s="2">
-        <v>45876</v>
+        <v>44928</v>
       </c>
       <c r="M36" s="3">
-        <v>45846</v>
+        <v>44917</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>USHUAIA</t>
+          <t>*sin dato*</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Resuelta</t>
+          <t>Crónica</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -3717,27 +3817,27 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
@@ -3748,26 +3848,26 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>22539485</v>
+        <v>19092851</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CABRERA</t>
+          <t>PEREZ LUNA RAFAJLOVSKI</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>MARIO ADRIAN</t>
+          <t>PARASHKEVA</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>De 45 a 65 años</t>
+          <t>De 35 a 44 años</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -3782,25 +3882,25 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>11. En estudio para hepatitis B</t>
+          <t>12. Virus Hepatitis B</t>
         </is>
       </c>
       <c r="I37">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="J37">
-        <v>2020</v>
+        <v>2023</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2020-51</t>
+          <t>2023-35</t>
         </is>
       </c>
       <c r="L37" s="2">
-        <v>44182</v>
+        <v>45183</v>
       </c>
       <c r="M37" s="3">
-        <v>44182</v>
+        <v>45169</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>
@@ -3809,12 +3909,37 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Crónica</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>HIV</t>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>SI</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
@@ -3825,26 +3950,26 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>18420802</v>
+        <v>29293499</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>AYALA</t>
+          <t>PEREA</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CARLA PATRICIA</t>
+          <t>MARTIN ALFREDO</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>De 45 a 65 años</t>
+          <t>De 35 a 44 años</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -3854,7 +3979,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hepatitis virales</t>
+          <t>Banco de Sangre</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3863,30 +3988,30 @@
         </is>
       </c>
       <c r="I38">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="J38">
-        <v>2025</v>
+        <v>2019</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2019-24</t>
         </is>
       </c>
       <c r="L38" s="2">
-        <v>45876</v>
+        <v>43739</v>
       </c>
       <c r="M38" s="3">
-        <v>45670</v>
+        <v>43626</v>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>*SIN DATO* (*SIN DATO*)</t>
+          <t>USHUAIA</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>Descartado</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
@@ -3897,21 +4022,21 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>31761053</v>
+        <v>95894978</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SOSA</t>
+          <t>ROMERO QUIROGA</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>SANDRA VIVIANA</t>
+          <t>CINTHIA SOLEDAD</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>De 35 a 44 años</t>
+          <t>De 20 a 24 años</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -3931,29 +4056,29 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
+          <t>12. Virus Hepatitis B</t>
         </is>
       </c>
       <c r="I39">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="J39">
-        <v>2023</v>
+        <v>2019</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2023-35</t>
+          <t>2019-02</t>
         </is>
       </c>
       <c r="L39" s="2">
-        <v>45169</v>
+        <v>43511</v>
       </c>
       <c r="M39" s="3">
-        <v>45169</v>
+        <v>43472</v>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>TOLHUIN</t>
+          <t>USHUAIA</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -3999,26 +4124,26 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>10857365</v>
+        <v>14450682</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>FERREYRA</t>
+          <t>GRAMAJO</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ARSENIA ISABEL</t>
+          <t>NORMANDO</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Mayores de 65 años</t>
+          <t>De 45 a 65 años</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -4028,30 +4153,30 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hepatitis virales</t>
+          <t>Banco de Sangre</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
+          <t>Caso descartado Hepatitis B</t>
         </is>
       </c>
       <c r="I40">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="J40">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2021-36</t>
+          <t>2024-04</t>
         </is>
       </c>
       <c r="L40" s="2">
-        <v>45244</v>
+        <v>45414</v>
       </c>
       <c r="M40" s="3">
-        <v>44445</v>
+        <v>45315</v>
       </c>
       <c r="N40" t="inlineStr">
         <is>
@@ -4060,37 +4185,12 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Crónica</t>
-        </is>
-      </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="R40" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>Descartado</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>No corresponde</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
@@ -4101,21 +4201,21 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>29293499</v>
+        <v>20256616</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>PEREA</t>
+          <t>CARMONA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>MARTIN ALFREDO</t>
+          <t>NORBERTO ALEJANDRO</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>De 35 a 44 años</t>
+          <t>De 45 a 65 años</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -4139,21 +4239,21 @@
         </is>
       </c>
       <c r="I41">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="J41">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2019-24</t>
+          <t>2020-14</t>
         </is>
       </c>
       <c r="L41" s="2">
-        <v>43739</v>
+        <v>44082</v>
       </c>
       <c r="M41" s="3">
-        <v>43626</v>
+        <v>43922</v>
       </c>
       <c r="N41" t="inlineStr">
         <is>
@@ -4173,26 +4273,26 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>25800340</v>
+        <v>23140885</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>PAVLOV</t>
+          <t>PORTAL</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>VANINA LORENA</t>
+          <t>HUGO CESAR</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>De 35 a 44 años</t>
+          <t>De 45 a 65 años</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -4211,21 +4311,21 @@
         </is>
       </c>
       <c r="I42">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="J42">
-        <v>2017</v>
+        <v>2023</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2017-31</t>
+          <t>2023-10</t>
         </is>
       </c>
       <c r="L42" s="2">
-        <v>43692</v>
+        <v>45244</v>
       </c>
       <c r="M42" s="3">
-        <v>42950</v>
+        <v>44991</v>
       </c>
       <c r="N42" t="inlineStr">
         <is>
@@ -4264,7 +4364,7 @@
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
@@ -4275,16 +4375,16 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>25633109</v>
+        <v>29372354</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>MOTTER</t>
+          <t>GUANDARILLO</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>DIEGO IGNACIO</t>
+          <t>ABEL MARCELO</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -4309,44 +4409,44 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
+          <t>07. Hepatitis B Resuelta - Infección Pasada</t>
         </is>
       </c>
       <c r="I43">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="J43">
-        <v>2020</v>
+        <v>2024</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2020-45</t>
+          <t>2024-17</t>
         </is>
       </c>
       <c r="L43" s="2">
-        <v>44221</v>
+        <v>45441</v>
       </c>
       <c r="M43" s="3">
-        <v>44140</v>
+        <v>45407</v>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>USHUAIA</t>
+          <t>RIO GRANDE</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Crónica</t>
+          <t>Resuelta</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -4377,16 +4477,16 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>17396287</v>
+        <v>16150973</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>VARGAS</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>MIGUEL ANGEL</t>
+          <t>ALDO WALTER</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -4406,69 +4506,39 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hepatitis virales</t>
+          <t>Banco de Sangre</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
+          <t>01. Caso probable en banco de sangre</t>
         </is>
       </c>
       <c r="I44">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J44">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2018-27</t>
+          <t>2019-30</t>
         </is>
       </c>
       <c r="L44" s="2">
-        <v>43424</v>
+        <v>43675</v>
       </c>
       <c r="M44" s="3">
-        <v>43286</v>
+        <v>43672</v>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>USHUAIA</t>
+          <t>RIO GRANDE</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Crónica</t>
-        </is>
-      </c>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="R44" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t>SI</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
@@ -4479,21 +4549,21 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>18117411</v>
+        <v>30144181</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>VILLARREAL</t>
+          <t>DAVIDSON</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>DANIEL EDUARDO</t>
+          <t>ANDRES SILVIO DE LA CRUZ</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>De 45 a 65 años</t>
+          <t>De 35 a 44 años</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -4513,25 +4583,25 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>06. Caso CONFIRMADO de Infección Aguda por VHB</t>
+          <t>07. Hepatitis B Resuelta - Infección Pasada</t>
         </is>
       </c>
       <c r="I45">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="J45">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2023-48</t>
+          <t>2024-44</t>
         </is>
       </c>
       <c r="L45" s="2">
-        <v>45257</v>
+        <v>45595</v>
       </c>
       <c r="M45" s="3">
-        <v>45257</v>
+        <v>45593</v>
       </c>
       <c r="N45" t="inlineStr">
         <is>
@@ -4540,7 +4610,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>Crónica</t>
+          <t>Aguda y resuelta</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -4565,12 +4635,12 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>No corresponde</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
@@ -4581,21 +4651,21 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>22193794</v>
+        <v>26710844</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>NIEVA</t>
+          <t>FLEITAS</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>ENRIQUE ALBERTO</t>
+          <t>CARLOS FELIPE</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>De 45 a 65 años</t>
+          <t>De 35 a 44 años</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4615,34 +4685,59 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>04. Caso CONFIRMADO de Infección por VHB</t>
+          <t>07. Hepatitis B Resuelta - Infección Pasada</t>
         </is>
       </c>
       <c r="I46">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="J46">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2022-30</t>
+          <t>2023-28</t>
         </is>
       </c>
       <c r="L46" s="2">
-        <v>46116</v>
+        <v>45122</v>
       </c>
       <c r="M46" s="3">
-        <v>44770</v>
+        <v>45118</v>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>USHUAIA</t>
+          <t>TOLHUIN</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Aguda</t>
+          <t>Crónica</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -4652,27 +4747,27 @@
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47">
-        <v>37356837</v>
+        <v>24557964</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>MONTEIRO TOLOSA</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ALBERTO EZEQUIEL</t>
+          <t>OSVALDO CRISTIAN</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>De 25 a 34 años</t>
+          <t>De 35 a 44 años</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -4699,57 +4794,57 @@
         <v>35</v>
       </c>
       <c r="J47">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2021-35</t>
+          <t>2019-35</t>
         </is>
       </c>
       <c r="L47" s="2">
-        <v>46139</v>
+        <v>43707</v>
       </c>
       <c r="M47" s="3">
-        <v>44440</v>
+        <v>43703</v>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>TIGRE</t>
+          <t>USHUAIA</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Aguda y resuelta</t>
+          <t>Aguda</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>HIV</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>No corresponde</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
@@ -4760,21 +4855,21 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>14898515</v>
+        <v>38776020</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SALAS</t>
+          <t>GODOY</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>EVARISTO SILVANO</t>
+          <t>DANIEL ALBERTO</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>De 45 a 65 años</t>
+          <t>De 25 a 34 años</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -4794,34 +4889,34 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
+          <t>06. Caso CONFIRMADO de Infección Aguda por VHB</t>
         </is>
       </c>
       <c r="I48">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="J48">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2018-20</t>
+          <t>2019-34</t>
         </is>
       </c>
       <c r="L48" s="2">
-        <v>43243</v>
+        <v>43714</v>
       </c>
       <c r="M48" s="3">
-        <v>43237</v>
+        <v>43697</v>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>USHUAIA</t>
+          <t>RIO GALLEGOS</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>Crónica</t>
+          <t>Aguda</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -4862,21 +4957,21 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>33013011</v>
+        <v>27047731</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>CENA</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>GUILLERMO OSCAR</t>
+          <t>JUAN ALBERTO</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>De 35 a 44 años</t>
+          <t>De 45 a 65 años</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -4896,64 +4991,34 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
+          <t>07. Hepatitis B Resuelta - Infección Pasada</t>
         </is>
       </c>
       <c r="I49">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J49">
-        <v>2024</v>
+        <v>2017</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2024-17</t>
+          <t>2017-26</t>
         </is>
       </c>
       <c r="L49" s="2">
-        <v>45405</v>
+        <v>46139</v>
       </c>
       <c r="M49" s="3">
-        <v>45404</v>
+        <v>42914</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>USHUAIA</t>
+          <t>SAN IGNACIO</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>Crónica</t>
-        </is>
-      </c>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>HIV</t>
-        </is>
-      </c>
-      <c r="Q49" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="R49" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="U49" t="inlineStr">
-        <is>
-          <t>SI</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
@@ -4998,7 +5063,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>03. Caso PROBABLE de Infección por VHB</t>
+          <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
         </is>
       </c>
       <c r="I50">
@@ -5066,26 +5131,26 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>27422758</v>
+        <v>7930029</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>AVALO</t>
+          <t>OCAMPO</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>MARCELA MARIA ITATI</t>
+          <t>ELIO JAVIER</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>De 35 a 44 años</t>
+          <t>Mayores de 65 años</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -5095,30 +5160,30 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Banco de Sangre</t>
+          <t>Hepatitis virales</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>01. Caso probable en banco de sangre</t>
+          <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
         </is>
       </c>
       <c r="I51">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J51">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2022-34</t>
+          <t>2024-36</t>
         </is>
       </c>
       <c r="L51" s="2">
-        <v>44916</v>
+        <v>45565</v>
       </c>
       <c r="M51" s="3">
-        <v>44796</v>
+        <v>45537</v>
       </c>
       <c r="N51" t="inlineStr">
         <is>
@@ -5127,7 +5192,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>Resuelta</t>
+          <t>Crónica</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -5137,7 +5202,7 @@
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
@@ -5157,7 +5222,7 @@
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
@@ -5168,26 +5233,26 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>30030925</v>
+        <v>18420802</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>SEQUEIRA</t>
+          <t>AYALA</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>SILVANO JOAQUIN</t>
+          <t>CARLA PATRICIA</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>De 35 a 44 años</t>
+          <t>De 45 a 65 años</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -5202,59 +5267,34 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>06. Caso CONFIRMADO de Infección Aguda por VHB</t>
+          <t>Caso descartado Hepatitis B</t>
         </is>
       </c>
       <c r="I52">
         <v>3</v>
       </c>
       <c r="J52">
-        <v>2020</v>
+        <v>2025</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2020-03</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="L52" s="2">
-        <v>43846</v>
+        <v>45876</v>
       </c>
       <c r="M52" s="3">
-        <v>43846</v>
+        <v>45670</v>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>USHUAIA</t>
+          <t>*SIN DATO* (*SIN DATO*)</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>Aguda y resuelta</t>
-        </is>
-      </c>
-      <c r="P52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="R52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="T52" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>Descartado</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -5270,21 +5310,21 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>32207592</v>
+        <v>13861790</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ALVAREZ</t>
+          <t>CAMERA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>FRANCISCO MANUEL</t>
+          <t>OMAR MIGUEL</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>De 25 a 34 años</t>
+          <t>De 45 a 65 años</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -5304,29 +5344,29 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
+          <t>12. Virus Hepatitis B</t>
         </is>
       </c>
       <c r="I53">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="J53">
-        <v>2017</v>
+        <v>2021</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2017-10</t>
+          <t>2021-31</t>
         </is>
       </c>
       <c r="L53" s="2">
-        <v>43706</v>
+        <v>44701</v>
       </c>
       <c r="M53" s="3">
-        <v>42804</v>
+        <v>44410</v>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>USHUAIA</t>
+          <t>CIUDAD DE BUENOS AIRES</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -5356,7 +5396,7 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -5372,16 +5412,16 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>27908220</v>
+        <v>30702578</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>BAZAN</t>
+          <t>LAREO</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>JUAN FRANCO SANTIAGO</t>
+          <t>MARINA PAULA</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -5391,7 +5431,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -5401,30 +5441,30 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hepatitis virales</t>
+          <t>Banco de Sangre</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
+          <t>01. Caso probable en banco de sangre</t>
         </is>
       </c>
       <c r="I54">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="J54">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2023-45</t>
+          <t>2020-18</t>
         </is>
       </c>
       <c r="L54" s="2">
-        <v>45244</v>
+        <v>44082</v>
       </c>
       <c r="M54" s="3">
-        <v>45239</v>
+        <v>43951</v>
       </c>
       <c r="N54" t="inlineStr">
         <is>
@@ -5433,37 +5473,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>Crónica</t>
-        </is>
-      </c>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q54" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="R54" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="T54" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U54" t="inlineStr">
-        <is>
-          <t>SI</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
@@ -5474,21 +5484,21 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>40000129</v>
+        <v>22534702</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>NAVIA CASTELLON</t>
+          <t>ANACHURI</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>GUSTAVO ENZO</t>
+          <t>PASCUAL</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>De 20 a 24 años</t>
+          <t>De 45 a 65 años</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -5503,30 +5513,30 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hepatitis virales</t>
+          <t>Banco de Sangre</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Paciente en seguimiento</t>
+          <t>02. Caso sospechoso en banco de sangre</t>
         </is>
       </c>
       <c r="I55">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="J55">
         <v>2019</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2019-31</t>
+          <t>2019-26</t>
         </is>
       </c>
       <c r="L55" s="2">
-        <v>43689</v>
+        <v>43739</v>
       </c>
       <c r="M55" s="3">
-        <v>43677</v>
+        <v>43644</v>
       </c>
       <c r="N55" t="inlineStr">
         <is>
@@ -5535,7 +5545,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>Descartado</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
@@ -5546,16 +5556,16 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>17656573</v>
+        <v>22475930</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>HEREDIA</t>
+          <t>MORAN</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>SERGIO OSCAR</t>
+          <t>LAURA MABEL</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -5565,7 +5575,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -5575,30 +5585,30 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hepatitis virales</t>
+          <t>Banco de Sangre</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>12. Virus Hepatitis B</t>
+          <t>07. Hepatitis B Resuelta - Infección Pasada</t>
         </is>
       </c>
       <c r="I56">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="J56">
-        <v>2020</v>
+        <v>2025</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2020-07</t>
+          <t>2025-28</t>
         </is>
       </c>
       <c r="L56" s="2">
-        <v>43892</v>
+        <v>45876</v>
       </c>
       <c r="M56" s="3">
-        <v>43872</v>
+        <v>45846</v>
       </c>
       <c r="N56" t="inlineStr">
         <is>
@@ -5607,7 +5617,37 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Resuelta</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
@@ -5618,26 +5658,26 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>94289655</v>
+        <v>27908220</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>CAMPOS VARGAS</t>
+          <t>BAZAN</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>FIDELIA</t>
+          <t>JUAN FRANCO SANTIAGO</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>De 45 a 65 años</t>
+          <t>De 35 a 44 años</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -5656,21 +5696,21 @@
         </is>
       </c>
       <c r="I57">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="J57">
-        <v>2019</v>
+        <v>2023</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2019-23</t>
+          <t>2023-45</t>
         </is>
       </c>
       <c r="L57" s="2">
-        <v>46139</v>
+        <v>45244</v>
       </c>
       <c r="M57" s="3">
-        <v>43621</v>
+        <v>45239</v>
       </c>
       <c r="N57" t="inlineStr">
         <is>
@@ -5684,27 +5724,27 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -5720,16 +5760,16 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>20799126</v>
+        <v>94289655</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>LLAMPA</t>
+          <t>CAMPOS VARGAS</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>ROSALIA SABINA</t>
+          <t>FIDELIA</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -5758,21 +5798,21 @@
         </is>
       </c>
       <c r="I58">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="J58">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2022-45</t>
+          <t>2019-23</t>
         </is>
       </c>
       <c r="L58" s="2">
-        <v>44932</v>
+        <v>46139</v>
       </c>
       <c r="M58" s="3">
-        <v>44873</v>
+        <v>43621</v>
       </c>
       <c r="N58" t="inlineStr">
         <is>
@@ -5786,32 +5826,32 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
@@ -5822,26 +5862,26 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>41058767</v>
+        <v>17656573</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>GONZALEZ MOLINA</t>
+          <t>HEREDIA</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>LOURDES MARIANELA</t>
+          <t>SERGIO OSCAR</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>De 20 a 24 años</t>
+          <t>De 45 a 65 años</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -5856,25 +5896,25 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Paciente en seguimiento</t>
+          <t>12. Virus Hepatitis B</t>
         </is>
       </c>
       <c r="I59">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="J59">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2019-31</t>
+          <t>2020-07</t>
         </is>
       </c>
       <c r="L59" s="2">
-        <v>43689</v>
+        <v>43892</v>
       </c>
       <c r="M59" s="3">
-        <v>43677</v>
+        <v>43872</v>
       </c>
       <c r="N59" t="inlineStr">
         <is>
@@ -5894,16 +5934,16 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>14405748</v>
+        <v>20799126</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>BAZAN</t>
+          <t>LLAMPA</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>ANA MARIA</t>
+          <t>ROSALIA SABINA</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -5928,29 +5968,29 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>03. Caso PROBABLE de Infección por VHB</t>
+          <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
         </is>
       </c>
       <c r="I60">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="J60">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2020-30</t>
+          <t>2022-45</t>
         </is>
       </c>
       <c r="L60" s="2">
-        <v>44176</v>
+        <v>44932</v>
       </c>
       <c r="M60" s="3">
-        <v>44032</v>
+        <v>44873</v>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>RIO GRANDE</t>
+          <t>USHUAIA</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -5960,32 +6000,32 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
@@ -6098,26 +6138,26 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>17372956</v>
+        <v>95045940</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>PEÑALOZA</t>
+          <t>MERUVIA ROBLES</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>LUIS ALBERTO</t>
+          <t>HERLINDA</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>De 45 a 65 años</t>
+          <t>De 25 a 34 años</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -6136,25 +6176,25 @@
         </is>
       </c>
       <c r="I62">
-        <v>46</v>
+        <v>2</v>
       </c>
       <c r="J62">
-        <v>2006</v>
+        <v>2019</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2006-46</t>
+          <t>2019-02</t>
         </is>
       </c>
       <c r="L62" s="2">
-        <v>45244</v>
+        <v>43524</v>
       </c>
       <c r="M62" s="3">
-        <v>39035</v>
+        <v>43472</v>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>RIO GRANDE</t>
+          <t>USHUAIA</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -6189,7 +6229,7 @@
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
@@ -6200,26 +6240,26 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>95045940</v>
+        <v>17372956</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>MERUVIA ROBLES</t>
+          <t>PEÑALOZA</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>HERLINDA</t>
+          <t>LUIS ALBERTO</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>De 25 a 34 años</t>
+          <t>De 45 a 65 años</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -6238,25 +6278,25 @@
         </is>
       </c>
       <c r="I63">
-        <v>2</v>
+        <v>46</v>
       </c>
       <c r="J63">
-        <v>2019</v>
+        <v>2006</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2019-02</t>
+          <t>2006-46</t>
         </is>
       </c>
       <c r="L63" s="2">
-        <v>43524</v>
+        <v>45244</v>
       </c>
       <c r="M63" s="3">
-        <v>43472</v>
+        <v>39035</v>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>USHUAIA</t>
+          <t>RIO GRANDE</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
@@ -6291,7 +6331,7 @@
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
@@ -6302,21 +6342,21 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>39202696</v>
+        <v>20159193</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>CARI</t>
+          <t>MOLINA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>EMANUEL BRIAN</t>
+          <t>VICENTE DURVAL</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>De 20 a 24 años</t>
+          <t>De 45 a 65 años</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -6331,30 +6371,30 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Banco de Sangre</t>
+          <t>Hepatitis virales</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>02. Caso sospechoso en banco de sangre</t>
+          <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
         </is>
       </c>
       <c r="I64">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="J64">
         <v>2019</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2019-27</t>
+          <t>2019-08</t>
         </is>
       </c>
       <c r="L64" s="2">
-        <v>43739</v>
+        <v>45240</v>
       </c>
       <c r="M64" s="3">
-        <v>43648</v>
+        <v>43514</v>
       </c>
       <c r="N64" t="inlineStr">
         <is>
@@ -6363,7 +6403,7 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>Resuelta</t>
+          <t>Crónica</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -6373,7 +6413,7 @@
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
@@ -6404,16 +6444,16 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>12956640</v>
+        <v>14405748</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>RUSCH</t>
+          <t>BAZAN</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>GERMAN ALFREDO</t>
+          <t>ANA MARIA</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -6423,7 +6463,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -6442,25 +6482,25 @@
         </is>
       </c>
       <c r="I65">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="J65">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2023-47</t>
+          <t>2020-30</t>
         </is>
       </c>
       <c r="L65" s="2">
-        <v>45295</v>
+        <v>44176</v>
       </c>
       <c r="M65" s="3">
-        <v>45252</v>
+        <v>44032</v>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>TOLHUIN</t>
+          <t>RIO GRANDE</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
@@ -6506,16 +6546,16 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>20159193</v>
+        <v>12956640</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>MOLINA</t>
+          <t>RUSCH</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>VICENTE DURVAL</t>
+          <t>GERMAN ALFREDO</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -6544,25 +6584,25 @@
         </is>
       </c>
       <c r="I66">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="J66">
-        <v>2019</v>
+        <v>2023</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2019-08</t>
+          <t>2023-47</t>
         </is>
       </c>
       <c r="L66" s="2">
-        <v>45240</v>
+        <v>45295</v>
       </c>
       <c r="M66" s="3">
-        <v>43514</v>
+        <v>45252</v>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>USHUAIA</t>
+          <t>TOLHUIN</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
@@ -6572,32 +6612,32 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
           <t>SI</t>
-        </is>
-      </c>
-      <c r="R66" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="S66" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="T66" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U66" t="inlineStr">
-        <is>
-          <t>NO</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
@@ -6710,21 +6750,21 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>12145481</v>
+        <v>40000129</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>FERREYRA</t>
+          <t>NAVIA CASTELLON</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>RICARDO MANUEL</t>
+          <t>GUSTAVO ENZO</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Mayores de 65 años</t>
+          <t>De 20 a 24 años</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -6744,25 +6784,25 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
+          <t>Caso descartado Hepatitis B</t>
         </is>
       </c>
       <c r="I68">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="J68">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2022-47</t>
+          <t>2019-31</t>
         </is>
       </c>
       <c r="L68" s="2">
-        <v>44693</v>
+        <v>43689</v>
       </c>
       <c r="M68" s="3">
-        <v>44889</v>
+        <v>43677</v>
       </c>
       <c r="N68" t="inlineStr">
         <is>
@@ -6771,37 +6811,12 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>Crónica</t>
-        </is>
-      </c>
-      <c r="P68" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q68" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="R68" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="S68" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="T68" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>Descartado</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>No corresponde</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
@@ -6812,26 +6827,26 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>36733857</v>
+        <v>12145481</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>ORTIZ</t>
+          <t>FERREYRA</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>NATALIA ALEJANDRA</t>
+          <t>RICARDO MANUEL</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>De 25 a 34 años</t>
+          <t>Mayores de 65 años</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -6841,39 +6856,69 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Banco de Sangre</t>
+          <t>Hepatitis virales</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>09. Caso CONFIRMADO de Infección OCULTA por VHB</t>
+          <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
         </is>
       </c>
       <c r="I69">
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="J69">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2022-47</t>
         </is>
       </c>
       <c r="L69" s="2">
-        <v>45733</v>
+        <v>44693</v>
       </c>
       <c r="M69" s="3">
-        <v>45677</v>
+        <v>44889</v>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>RIO GRANDE</t>
+          <t>USHUAIA</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Crónica</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
@@ -6884,26 +6929,26 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>13814814</v>
+        <v>36733857</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>ANDERSEN</t>
+          <t>ORTIZ</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>JOSE DAVID</t>
+          <t>NATALIA ALEJANDRA</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>De 45 a 65 años</t>
+          <t>De 25 a 34 años</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -6913,69 +6958,39 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hepatitis virales</t>
+          <t>Banco de Sangre</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
+          <t>09. Caso CONFIRMADO de Infección OCULTA por VHB</t>
         </is>
       </c>
       <c r="I70">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="J70">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="L70" s="2">
-        <v>45370</v>
+        <v>45733</v>
       </c>
       <c r="M70" s="3">
-        <v>45370</v>
+        <v>45677</v>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>TOLHUIN</t>
+          <t>RIO GRANDE</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>Crónica</t>
-        </is>
-      </c>
-      <c r="P70" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="Q70" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="R70" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="S70" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="T70" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="U70" t="inlineStr">
-        <is>
-          <t>SI</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
@@ -6986,16 +7001,16 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>16664022</v>
+        <v>13814814</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>MELGAREJO</t>
+          <t>ANDERSEN</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>ZULLY FRANCISCA EDITH</t>
+          <t>JOSE DAVID</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -7005,7 +7020,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -7015,69 +7030,69 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Banco de Sangre</t>
+          <t>Hepatitis virales</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>01. Caso probable en banco de sangre</t>
+          <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
         </is>
       </c>
       <c r="I71">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="J71">
-        <v>2019</v>
+        <v>2024</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2019-26</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="L71" s="2">
-        <v>43739</v>
+        <v>45370</v>
       </c>
       <c r="M71" s="3">
-        <v>43644</v>
+        <v>45370</v>
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>USHUAIA</t>
+          <t>TOLHUIN</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>Resuelta</t>
+          <t>Crónica</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">

--- a/Salidas/data_B_completa.xlsx
+++ b/Salidas/data_B_completa.xlsx
@@ -357,7 +357,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:V72"/>
+  <dimension ref="A1:V67"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="12" max="12" width="20.7109375" style="2" customWidth="1"/>
@@ -754,21 +754,21 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>11006818</v>
+        <v>16859856</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CAYO</t>
+          <t>SCHOLLES</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>RAMONA ANDREA</t>
+          <t>MARTA GRACIELA</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Mayores de 65 años</t>
+          <t>De 45 a 65 años</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -788,64 +788,64 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
+          <t>12. Virus Hepatitis B</t>
         </is>
       </c>
       <c r="I5">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="J5">
-        <v>2017</v>
+        <v>2025</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2017-20</t>
+          <t>2025-40</t>
         </is>
       </c>
       <c r="L5" s="2">
-        <v>44928</v>
+        <v>46093</v>
       </c>
       <c r="M5" s="3">
-        <v>42873</v>
+        <v>45929</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>RIO GRANDE</t>
+          <t>*sin dato*</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Crónica</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -856,16 +856,16 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>16859856</v>
+        <v>18597623</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SCHOLLES</t>
+          <t>NUÑEZ</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MARTA GRACIELA</t>
+          <t>JOSE JESUS</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -875,7 +875,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -894,30 +894,30 @@
         </is>
       </c>
       <c r="I6">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="J6">
-        <v>2025</v>
+        <v>2019</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2025-40</t>
+          <t>2019-07</t>
         </is>
       </c>
       <c r="L6" s="2">
-        <v>46093</v>
+        <v>43511</v>
       </c>
       <c r="M6" s="3">
-        <v>45929</v>
+        <v>43508</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>*sin dato*</t>
+          <t>USHUAIA</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Crónica</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -958,16 +958,16 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>18597623</v>
+        <v>25633171</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NUÑEZ</t>
+          <t>VERA OYARZO</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>JOSE JESUS</t>
+          <t>RUBEN MARCELO</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -992,25 +992,25 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>12. Virus Hepatitis B</t>
+          <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
         </is>
       </c>
       <c r="I7">
-        <v>7</v>
+        <v>50</v>
       </c>
       <c r="J7">
-        <v>2019</v>
+        <v>2025</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2019-07</t>
+          <t>2025-50</t>
         </is>
       </c>
       <c r="L7" s="2">
-        <v>43511</v>
+        <v>46001</v>
       </c>
       <c r="M7" s="3">
-        <v>43508</v>
+        <v>46001</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -1024,32 +1024,32 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1060,21 +1060,21 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>25633171</v>
+        <v>10619060</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>VERA OYARZO</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>RUBEN MARCELO</t>
+          <t>EDGARDO RUBEN</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>De 45 a 65 años</t>
+          <t>Mayores de 65 años</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1098,25 +1098,25 @@
         </is>
       </c>
       <c r="I8">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="J8">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2025-50</t>
+          <t>2021-23</t>
         </is>
       </c>
       <c r="L8" s="2">
-        <v>46001</v>
+        <v>44365</v>
       </c>
       <c r="M8" s="3">
-        <v>46001</v>
+        <v>44357</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>USHUAIA</t>
+          <t>TOLHUIN</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1162,26 +1162,26 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>10619060</v>
+        <v>30675706</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>VILLALOBOS</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>EDGARDO RUBEN</t>
+          <t>EVA MARIA</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Mayores de 65 años</t>
+          <t>De 35 a 44 años</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1191,69 +1191,39 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatitis virales</t>
+          <t>Banco de Sangre</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
+          <t>09. Caso CONFIRMADO de Infección OCULTA por VHB</t>
         </is>
       </c>
       <c r="I9">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="J9">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2021-23</t>
+          <t>2025-38</t>
         </is>
       </c>
       <c r="L9" s="2">
-        <v>44365</v>
+        <v>45936</v>
       </c>
       <c r="M9" s="3">
-        <v>44357</v>
+        <v>45918</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>TOLHUIN</t>
+          <t>RIO GRANDE</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Crónica</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1264,16 +1234,16 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>30675706</v>
+        <v>27422758</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>VILLALOBOS</t>
+          <t>AVALO</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>EVA MARIA</t>
+          <t>MARCELA MARIA ITATI</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1298,34 +1268,64 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>09. Caso CONFIRMADO de Infección OCULTA por VHB</t>
+          <t>07. Hepatitis B Resuelta - Infección Pasada</t>
         </is>
       </c>
       <c r="I10">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="J10">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2025-38</t>
+          <t>2022-34</t>
         </is>
       </c>
       <c r="L10" s="2">
-        <v>45936</v>
+        <v>44916</v>
       </c>
       <c r="M10" s="3">
-        <v>45918</v>
+        <v>44796</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>RIO GRANDE</t>
+          <t>USHUAIA</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Resuelta</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1336,26 +1336,26 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>27422758</v>
+        <v>10312933</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AVALO</t>
+          <t>FERRARESE</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MARCELA MARIA ITATI</t>
+          <t>DALMACIO ESTEBAN</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>De 35 a 44 años</t>
+          <t>Mayores de 65 años</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Banco de Sangre</t>
+          <t>Hepatitis virales</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1374,30 +1374,30 @@
         </is>
       </c>
       <c r="I11">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="J11">
         <v>2022</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2022-34</t>
+          <t>2022-03</t>
         </is>
       </c>
       <c r="L11" s="2">
-        <v>44916</v>
+        <v>44701</v>
       </c>
       <c r="M11" s="3">
-        <v>44796</v>
+        <v>44581</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>USHUAIA</t>
+          <t>*SIN DATO* (*SIN DATO*)</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Resuelta</t>
+          <t>Aguda y resuelta</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>No corresponde</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1438,21 +1438,21 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>10312933</v>
+        <v>39202696</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>FERRARESE</t>
+          <t>CARI</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>DALMACIO ESTEBAN</t>
+          <t>EMANUEL BRIAN</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Mayores de 65 años</t>
+          <t>De 20 a 24 años</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatitis virales</t>
+          <t>Banco de Sangre</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1476,30 +1476,30 @@
         </is>
       </c>
       <c r="I12">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="J12">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2022-03</t>
+          <t>2019-27</t>
         </is>
       </c>
       <c r="L12" s="2">
-        <v>44701</v>
+        <v>43739</v>
       </c>
       <c r="M12" s="3">
-        <v>44581</v>
+        <v>43648</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>*SIN DATO* (*SIN DATO*)</t>
+          <t>USHUAIA</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Aguda y resuelta</t>
+          <t>Resuelta</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>No corresponde</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1540,26 +1540,26 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>39202696</v>
+        <v>96420346</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CARI</t>
+          <t>MUÑOZ BUSTAMANTE</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>EMANUEL BRIAN</t>
+          <t>ELITA</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>De 20 a 24 años</t>
+          <t>De 25 a 34 años</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1569,30 +1569,30 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Banco de Sangre</t>
+          <t>Hepatitis virales</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>07. Hepatitis B Resuelta - Infección Pasada</t>
+          <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
         </is>
       </c>
       <c r="I13">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="J13">
-        <v>2019</v>
+        <v>2025</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2019-27</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="L13" s="2">
-        <v>43739</v>
+        <v>45744</v>
       </c>
       <c r="M13" s="3">
-        <v>43648</v>
+        <v>45686</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Resuelta</t>
+          <t>Crónica</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1642,26 +1642,26 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>96420346</v>
+        <v>94509088</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MUÑOZ BUSTAMANTE</t>
+          <t>YECGUANCHUY CHAVEZ</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ELITA</t>
+          <t>RAUL ANTONY</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>De 25 a 34 años</t>
+          <t>De 35 a 44 años</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1680,21 +1680,21 @@
         </is>
       </c>
       <c r="I14">
-        <v>5</v>
+        <v>46</v>
       </c>
       <c r="J14">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2023-46</t>
         </is>
       </c>
       <c r="L14" s="2">
-        <v>45744</v>
+        <v>45246</v>
       </c>
       <c r="M14" s="3">
-        <v>45686</v>
+        <v>45246</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -1708,12 +1708,12 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>HIV/HCV</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1733,7 +1733,7 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -1744,21 +1744,21 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>94509088</v>
+        <v>22539485</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>YECGUANCHUY CHAVEZ</t>
+          <t>CABRERA</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>RAUL ANTONY</t>
+          <t>MARIO ADRIAN</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>De 35 a 44 años</t>
+          <t>De 45 a 65 años</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1778,64 +1778,39 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
+          <t>11. En estudio para hepatitis B</t>
         </is>
       </c>
       <c r="I15">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="J15">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2023-46</t>
+          <t>2020-51</t>
         </is>
       </c>
       <c r="L15" s="2">
-        <v>45246</v>
+        <v>44182</v>
       </c>
       <c r="M15" s="3">
-        <v>45246</v>
+        <v>44182</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>USHUAIA</t>
+          <t>RIO GRANDE</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Crónica</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>HIV/HCV</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>SI</t>
+          <t>HIV</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -1846,26 +1821,26 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>22539485</v>
+        <v>10857365</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CABRERA</t>
+          <t>FERREYRA</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MARIO ADRIAN</t>
+          <t>ARSENIA ISABEL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>De 45 a 65 años</t>
+          <t>Mayores de 65 años</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1880,39 +1855,64 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>11. En estudio para hepatitis B</t>
+          <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
         </is>
       </c>
       <c r="I16">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="J16">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2020-51</t>
+          <t>2021-36</t>
         </is>
       </c>
       <c r="L16" s="2">
-        <v>44182</v>
+        <v>45244</v>
       </c>
       <c r="M16" s="3">
-        <v>44182</v>
+        <v>44445</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>RIO GRANDE</t>
+          <t>USHUAIA</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Crónica</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>HIV</t>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -1923,21 +1923,21 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>10857365</v>
+        <v>26421454</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>FERREYRA</t>
+          <t>QUIROZ</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ARSENIA ISABEL</t>
+          <t>LILIANA ROXANA</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Mayores de 65 años</t>
+          <t>De 35 a 44 años</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1961,21 +1961,21 @@
         </is>
       </c>
       <c r="I17">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="J17">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2021-36</t>
+          <t>2022-21</t>
         </is>
       </c>
       <c r="L17" s="2">
-        <v>45244</v>
+        <v>44708</v>
       </c>
       <c r="M17" s="3">
-        <v>44445</v>
+        <v>44705</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1989,32 +1989,32 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
           <t>SI</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>NO</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -2025,16 +2025,16 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>26421454</v>
+        <v>31761053</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>QUIROZ</t>
+          <t>SOSA</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>LILIANA ROXANA</t>
+          <t>SANDRA VIVIANA</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2063,25 +2063,25 @@
         </is>
       </c>
       <c r="I18">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="J18">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2022-21</t>
+          <t>2023-35</t>
         </is>
       </c>
       <c r="L18" s="2">
-        <v>44708</v>
+        <v>45169</v>
       </c>
       <c r="M18" s="3">
-        <v>44705</v>
+        <v>45169</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>USHUAIA</t>
+          <t>TOLHUIN</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -2127,26 +2127,26 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>31761053</v>
+        <v>18117411</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SOSA</t>
+          <t>VILLARREAL</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SANDRA VIVIANA</t>
+          <t>DANIEL EDUARDO</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>De 35 a 44 años</t>
+          <t>De 45 a 65 años</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2161,29 +2161,29 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
+          <t>06. Caso CONFIRMADO de Infección Aguda por VHB</t>
         </is>
       </c>
       <c r="I19">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="J19">
         <v>2023</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2023-35</t>
+          <t>2023-48</t>
         </is>
       </c>
       <c r="L19" s="2">
-        <v>45169</v>
+        <v>45257</v>
       </c>
       <c r="M19" s="3">
-        <v>45169</v>
+        <v>45257</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>TOLHUIN</t>
+          <t>USHUAIA</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -2193,27 +2193,27 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2229,16 +2229,16 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>25800340</v>
+        <v>25633109</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>PAVLOV</t>
+          <t>MOTTER</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>VANINA LORENA</t>
+          <t>DIEGO IGNACIO</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2248,7 +2248,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2267,21 +2267,21 @@
         </is>
       </c>
       <c r="I20">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="J20">
-        <v>2017</v>
+        <v>2020</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2017-31</t>
+          <t>2020-45</t>
         </is>
       </c>
       <c r="L20" s="2">
-        <v>43692</v>
+        <v>44221</v>
       </c>
       <c r="M20" s="3">
-        <v>42950</v>
+        <v>44140</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -2295,12 +2295,12 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -2331,16 +2331,16 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>18117411</v>
+        <v>22193794</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>VILLARREAL</t>
+          <t>NIEVA</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>DANIEL EDUARDO</t>
+          <t>ENRIQUE ALBERTO</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2365,25 +2365,25 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>06. Caso CONFIRMADO de Infección Aguda por VHB</t>
+          <t>04. Caso CONFIRMADO de Infección por VHB</t>
         </is>
       </c>
       <c r="I21">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="J21">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2023-48</t>
+          <t>2022-30</t>
         </is>
       </c>
       <c r="L21" s="2">
-        <v>45257</v>
+        <v>46116</v>
       </c>
       <c r="M21" s="3">
-        <v>45257</v>
+        <v>44770</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -2392,67 +2392,42 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Crónica</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
+          <t>Aguda</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>SI</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>25633109</v>
+        <v>41058767</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>MOTTER</t>
+          <t>GONZALEZ MOLINA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>DIEGO IGNACIO</t>
+          <t>LOURDES MARIANELA</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>De 35 a 44 años</t>
+          <t>De 20 a 24 años</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2467,25 +2442,25 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
+          <t>Caso descartado Hepatitis B</t>
         </is>
       </c>
       <c r="I22">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="J22">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2020-45</t>
+          <t>2019-31</t>
         </is>
       </c>
       <c r="L22" s="2">
-        <v>44221</v>
+        <v>43689</v>
       </c>
       <c r="M22" s="3">
-        <v>44140</v>
+        <v>43677</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -2494,37 +2469,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Crónica</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -2535,16 +2480,16 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>22193794</v>
+        <v>17396287</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>NIEVA</t>
+          <t>LAMA</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ENRIQUE ALBERTO</t>
+          <t>MIGUEL ANGEL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2569,25 +2514,25 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>04. Caso CONFIRMADO de Infección por VHB</t>
+          <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
         </is>
       </c>
       <c r="I23">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J23">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2022-30</t>
+          <t>2018-27</t>
         </is>
       </c>
       <c r="L23" s="2">
-        <v>46116</v>
+        <v>43424</v>
       </c>
       <c r="M23" s="3">
-        <v>44770</v>
+        <v>43286</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -2596,7 +2541,32 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Aguda</t>
+          <t>Crónica</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2606,32 +2576,32 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <v>41058767</v>
+        <v>37356837</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>GONZALEZ MOLINA</t>
+          <t>MONTEIRO TOLOSA</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>LOURDES MARIANELA</t>
+          <t>ALBERTO EZEQUIEL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>De 20 a 24 años</t>
+          <t>De 25 a 34 años</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2646,34 +2616,64 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Caso descartado Hepatitis B</t>
+          <t>06. Caso CONFIRMADO de Infección Aguda por VHB</t>
         </is>
       </c>
       <c r="I24">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J24">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2019-31</t>
+          <t>2021-35</t>
         </is>
       </c>
       <c r="L24" s="2">
-        <v>43689</v>
+        <v>46139</v>
       </c>
       <c r="M24" s="3">
-        <v>43677</v>
+        <v>44440</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>USHUAIA</t>
+          <t>TIGRE</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Aguda y resuelta</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>HIV</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>No corresponde</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
@@ -2684,26 +2684,26 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>17396287</v>
+        <v>28227396</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>FIGEROA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>MIGUEL ANGEL</t>
+          <t>VICTORIA ELENA</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>De 45 a 65 años</t>
+          <t>De 35 a 44 años</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2713,64 +2713,64 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatitis virales</t>
+          <t>Banco de Sangre</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
+          <t>07. Hepatitis B Resuelta - Infección Pasada</t>
         </is>
       </c>
       <c r="I25">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J25">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2018-27</t>
+          <t>2019-28</t>
         </is>
       </c>
       <c r="L25" s="2">
-        <v>43424</v>
+        <v>43668</v>
       </c>
       <c r="M25" s="3">
-        <v>43286</v>
+        <v>43658</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>USHUAIA</t>
+          <t>RIO GRANDE</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Crónica</t>
+          <t>Resuelta</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -2786,21 +2786,21 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>37356837</v>
+        <v>14898515</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>MONTEIRO TOLOSA</t>
+          <t>SALAS</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ALBERTO EZEQUIEL</t>
+          <t>EVARISTO SILVANO</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>De 25 a 34 años</t>
+          <t>De 45 a 65 años</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2820,64 +2820,64 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>06. Caso CONFIRMADO de Infección Aguda por VHB</t>
+          <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
         </is>
       </c>
       <c r="I26">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="J26">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2021-35</t>
+          <t>2018-20</t>
         </is>
       </c>
       <c r="L26" s="2">
-        <v>46139</v>
+        <v>43243</v>
       </c>
       <c r="M26" s="3">
-        <v>44440</v>
+        <v>43237</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>TIGRE</t>
+          <t>USHUAIA</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Aguda y resuelta</t>
+          <t>Crónica</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>HIV</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>No corresponde</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
@@ -2888,16 +2888,16 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>28227396</v>
+        <v>33013011</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>FIGEROA</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>VICTORIA ELENA</t>
+          <t>GUILLERMO OSCAR</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2907,7 +2907,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2917,59 +2917,59 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Banco de Sangre</t>
+          <t>Hepatitis virales</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>07. Hepatitis B Resuelta - Infección Pasada</t>
+          <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
         </is>
       </c>
       <c r="I27">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="J27">
-        <v>2019</v>
+        <v>2024</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2019-28</t>
+          <t>2024-17</t>
         </is>
       </c>
       <c r="L27" s="2">
-        <v>43668</v>
+        <v>45405</v>
       </c>
       <c r="M27" s="3">
-        <v>43658</v>
+        <v>45404</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>RIO GRANDE</t>
+          <t>USHUAIA</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Resuelta</t>
+          <t>Crónica</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>HIV</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
@@ -2990,21 +2990,21 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>14898515</v>
+        <v>30030925</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SALAS</t>
+          <t>SEQUEIRA</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>EVARISTO SILVANO</t>
+          <t>SILVANO JOAQUIN</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>De 45 a 65 años</t>
+          <t>De 35 a 44 años</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3024,25 +3024,25 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
+          <t>06. Caso CONFIRMADO de Infección Aguda por VHB</t>
         </is>
       </c>
       <c r="I28">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="J28">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2018-20</t>
+          <t>2020-03</t>
         </is>
       </c>
       <c r="L28" s="2">
-        <v>43243</v>
+        <v>43846</v>
       </c>
       <c r="M28" s="3">
-        <v>43237</v>
+        <v>43846</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -3051,37 +3051,37 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Crónica</t>
+          <t>Aguda y resuelta</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>No corresponde</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
@@ -3092,26 +3092,26 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>33013011</v>
+        <v>16664022</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>MELGAREJO</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>GUILLERMO OSCAR</t>
+          <t>ZULLY FRANCISCA EDITH</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>De 35 a 44 años</t>
+          <t>De 45 a 65 años</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -3121,30 +3121,30 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatitis virales</t>
+          <t>Banco de Sangre</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
+          <t>07. Hepatitis B Resuelta - Infección Pasada</t>
         </is>
       </c>
       <c r="I29">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J29">
-        <v>2024</v>
+        <v>2019</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2024-17</t>
+          <t>2019-26</t>
         </is>
       </c>
       <c r="L29" s="2">
-        <v>45405</v>
+        <v>43739</v>
       </c>
       <c r="M29" s="3">
-        <v>45404</v>
+        <v>43644</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
@@ -3153,17 +3153,17 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Crónica</t>
+          <t>Resuelta</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>HIV</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -3178,12 +3178,12 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
@@ -3194,16 +3194,16 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>30030925</v>
+        <v>28008546</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SEQUEIRA</t>
+          <t>SENILLIANI MELCHIOR</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>SILVANO JOAQUIN</t>
+          <t>CECILIA</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -3228,25 +3228,25 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>06. Caso CONFIRMADO de Infección Aguda por VHB</t>
+          <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
         </is>
       </c>
       <c r="I30">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="J30">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2020-03</t>
+          <t>2019-33</t>
         </is>
       </c>
       <c r="L30" s="2">
-        <v>43846</v>
+        <v>43692</v>
       </c>
       <c r="M30" s="3">
-        <v>43846</v>
+        <v>43692</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Aguda y resuelta</t>
+          <t>Crónica</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>No corresponde</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
@@ -3296,26 +3296,26 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>32207592</v>
+        <v>27834459</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ALVAREZ</t>
+          <t>ALCOBA</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>FRANCISCO MANUEL</t>
+          <t>LUISA AUDELINA</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>De 25 a 34 años</t>
+          <t>De 35 a 44 años</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -3325,69 +3325,39 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hepatitis virales</t>
+          <t>Banco de Sangre</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
+          <t>01. Caso probable en banco de sangre</t>
         </is>
       </c>
       <c r="I31">
-        <v>10</v>
+        <v>49</v>
       </c>
       <c r="J31">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2017-10</t>
+          <t>2019-49</t>
         </is>
       </c>
       <c r="L31" s="2">
-        <v>43706</v>
+        <v>43851</v>
       </c>
       <c r="M31" s="3">
-        <v>42804</v>
+        <v>43804</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>USHUAIA</t>
+          <t>RIO GRANDE</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Crónica</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>HIV</t>
-        </is>
-      </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="R31" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>SI</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
@@ -3398,26 +3368,26 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>16664022</v>
+        <v>26930068</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>MELGAREJO</t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ZULLY FRANCISCA EDITH</t>
+          <t>SILVIO ALFREDO</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>De 45 a 65 años</t>
+          <t>De 35 a 44 años</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -3432,64 +3402,34 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>07. Hepatitis B Resuelta - Infección Pasada</t>
+          <t>02. Caso sospechoso en banco de sangre</t>
         </is>
       </c>
       <c r="I32">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="J32">
         <v>2019</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2019-26</t>
+          <t>2019-14</t>
         </is>
       </c>
       <c r="L32" s="2">
-        <v>43739</v>
+        <v>43598</v>
       </c>
       <c r="M32" s="3">
-        <v>43644</v>
+        <v>43556</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>USHUAIA</t>
+          <t>RIO GRANDE</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Resuelta</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="R32" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
@@ -3500,26 +3440,26 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>28008546</v>
+        <v>13454523</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SENILLIANI MELCHIOR</t>
+          <t>PELLEGRINI</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CECILIA</t>
+          <t>EDGARDO ENZO</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>De 35 a 44 años</t>
+          <t>De 45 a 65 años</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -3538,25 +3478,25 @@
         </is>
       </c>
       <c r="I33">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="J33">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2019-33</t>
+          <t>2022-51</t>
         </is>
       </c>
       <c r="L33" s="2">
-        <v>43692</v>
+        <v>44928</v>
       </c>
       <c r="M33" s="3">
-        <v>43692</v>
+        <v>44917</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>USHUAIA</t>
+          <t>*sin dato*</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -3571,27 +3511,27 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
@@ -3602,16 +3542,16 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>27834459</v>
+        <v>19092851</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ALCOBA</t>
+          <t>PEREZ LUNA RAFAJLOVSKI</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>LUISA AUDELINA</t>
+          <t>PARASHKEVA</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -3631,30 +3571,30 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Banco de Sangre</t>
+          <t>Hepatitis virales</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>01. Caso probable en banco de sangre</t>
+          <t>12. Virus Hepatitis B</t>
         </is>
       </c>
       <c r="I34">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="J34">
-        <v>2019</v>
+        <v>2023</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2019-49</t>
+          <t>2023-35</t>
         </is>
       </c>
       <c r="L34" s="2">
-        <v>43851</v>
+        <v>45183</v>
       </c>
       <c r="M34" s="3">
-        <v>43804</v>
+        <v>45169</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
@@ -3663,7 +3603,37 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Crónica</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>SI</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
@@ -3674,16 +3644,16 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>26930068</v>
+        <v>29293499</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t>PEREA</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>SILVIO ALFREDO</t>
+          <t>MARTIN ALFREDO</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -3708,29 +3678,29 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>02. Caso sospechoso en banco de sangre</t>
+          <t>07. Hepatitis B Resuelta - Infección Pasada</t>
         </is>
       </c>
       <c r="I35">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="J35">
         <v>2019</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2019-14</t>
+          <t>2019-24</t>
         </is>
       </c>
       <c r="L35" s="2">
-        <v>43598</v>
+        <v>43739</v>
       </c>
       <c r="M35" s="3">
-        <v>43556</v>
+        <v>43626</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>RIO GRANDE</t>
+          <t>USHUAIA</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -3746,26 +3716,26 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>13454523</v>
+        <v>95894978</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>PELLEGRINI</t>
+          <t>ROMERO QUIROGA</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>EDGARDO ENZO</t>
+          <t>CINTHIA SOLEDAD</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>De 45 a 65 años</t>
+          <t>De 20 a 24 años</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -3780,29 +3750,29 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
+          <t>12. Virus Hepatitis B</t>
         </is>
       </c>
       <c r="I36">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="J36">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2022-51</t>
+          <t>2019-02</t>
         </is>
       </c>
       <c r="L36" s="2">
-        <v>44928</v>
+        <v>43511</v>
       </c>
       <c r="M36" s="3">
-        <v>44917</v>
+        <v>43472</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>*sin dato*</t>
+          <t>USHUAIA</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -3812,7 +3782,7 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -3848,26 +3818,26 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>19092851</v>
+        <v>14450682</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>PEREZ LUNA RAFAJLOVSKI</t>
+          <t>GRAMAJO</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>PARASHKEVA</t>
+          <t>NORMANDO</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>De 35 a 44 años</t>
+          <t>De 45 a 65 años</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -3877,69 +3847,44 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hepatitis virales</t>
+          <t>Banco de Sangre</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>12. Virus Hepatitis B</t>
+          <t>Caso descartado Hepatitis B</t>
         </is>
       </c>
       <c r="I37">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="J37">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2023-35</t>
+          <t>2024-04</t>
         </is>
       </c>
       <c r="L37" s="2">
-        <v>45183</v>
+        <v>45414</v>
       </c>
       <c r="M37" s="3">
-        <v>45169</v>
+        <v>45315</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>RIO GRANDE</t>
+          <t>USHUAIA</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Crónica</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
+          <t>Descartado</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>No corresponde</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
@@ -3950,21 +3895,21 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>29293499</v>
+        <v>20256616</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>PEREA</t>
+          <t>CARMONA</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>MARTIN ALFREDO</t>
+          <t>NORBERTO ALEJANDRO</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>De 35 a 44 años</t>
+          <t>De 45 a 65 años</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -3984,25 +3929,25 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>07. Hepatitis B Resuelta - Infección Pasada</t>
+          <t>02. Caso sospechoso en banco de sangre</t>
         </is>
       </c>
       <c r="I38">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="J38">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2019-24</t>
+          <t>2020-14</t>
         </is>
       </c>
       <c r="L38" s="2">
-        <v>43739</v>
+        <v>44082</v>
       </c>
       <c r="M38" s="3">
-        <v>43626</v>
+        <v>43922</v>
       </c>
       <c r="N38" t="inlineStr">
         <is>
@@ -4022,26 +3967,26 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>95894978</v>
+        <v>23140885</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ROMERO QUIROGA</t>
+          <t>PORTAL</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CINTHIA SOLEDAD</t>
+          <t>HUGO CESAR</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>De 20 a 24 años</t>
+          <t>De 45 a 65 años</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -4056,25 +4001,25 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>12. Virus Hepatitis B</t>
+          <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
         </is>
       </c>
       <c r="I39">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J39">
-        <v>2019</v>
+        <v>2023</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2019-02</t>
+          <t>2023-10</t>
         </is>
       </c>
       <c r="L39" s="2">
-        <v>43511</v>
+        <v>45244</v>
       </c>
       <c r="M39" s="3">
-        <v>43472</v>
+        <v>44991</v>
       </c>
       <c r="N39" t="inlineStr">
         <is>
@@ -4088,27 +4033,27 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4124,21 +4069,21 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>14450682</v>
+        <v>29372354</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>GRAMAJO</t>
+          <t>GUANDARILLO</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>NORMANDO</t>
+          <t>ABEL MARCELO</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>De 45 a 65 años</t>
+          <t>De 35 a 44 años</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -4153,44 +4098,69 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Banco de Sangre</t>
+          <t>Hepatitis virales</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Caso descartado Hepatitis B</t>
+          <t>07. Hepatitis B Resuelta - Infección Pasada</t>
         </is>
       </c>
       <c r="I40">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="J40">
         <v>2024</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-17</t>
         </is>
       </c>
       <c r="L40" s="2">
-        <v>45414</v>
+        <v>45441</v>
       </c>
       <c r="M40" s="3">
-        <v>45315</v>
+        <v>45407</v>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>USHUAIA</t>
+          <t>RIO GRANDE</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Descartado</t>
+          <t>Resuelta</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>No corresponde</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
@@ -4201,16 +4171,16 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>20256616</v>
+        <v>16150973</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CARMONA</t>
+          <t>VARGAS</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>NORBERTO ALEJANDRO</t>
+          <t>ALDO WALTER</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -4235,29 +4205,29 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>02. Caso sospechoso en banco de sangre</t>
+          <t>01. Caso probable en banco de sangre</t>
         </is>
       </c>
       <c r="I41">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="J41">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2020-14</t>
+          <t>2019-30</t>
         </is>
       </c>
       <c r="L41" s="2">
-        <v>44082</v>
+        <v>43675</v>
       </c>
       <c r="M41" s="3">
-        <v>43922</v>
+        <v>43672</v>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>USHUAIA</t>
+          <t>RIO GRANDE</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -4273,21 +4243,21 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>23140885</v>
+        <v>30144181</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>PORTAL</t>
+          <t>DAVIDSON</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>HUGO CESAR</t>
+          <t>ANDRES SILVIO DE LA CRUZ</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>De 45 a 65 años</t>
+          <t>De 35 a 44 años</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -4307,25 +4277,25 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
+          <t>07. Hepatitis B Resuelta - Infección Pasada</t>
         </is>
       </c>
       <c r="I42">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="J42">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2023-10</t>
+          <t>2024-44</t>
         </is>
       </c>
       <c r="L42" s="2">
-        <v>45244</v>
+        <v>45595</v>
       </c>
       <c r="M42" s="3">
-        <v>44991</v>
+        <v>45593</v>
       </c>
       <c r="N42" t="inlineStr">
         <is>
@@ -4334,7 +4304,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Crónica</t>
+          <t>Aguda y resuelta</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -4364,7 +4334,7 @@
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>No corresponde</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
@@ -4375,16 +4345,16 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>29372354</v>
+        <v>26710844</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>GUANDARILLO</t>
+          <t>FLEITAS</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ABEL MARCELO</t>
+          <t>CARLOS FELIPE</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -4413,30 +4383,30 @@
         </is>
       </c>
       <c r="I43">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="J43">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2024-17</t>
+          <t>2023-28</t>
         </is>
       </c>
       <c r="L43" s="2">
-        <v>45441</v>
+        <v>45122</v>
       </c>
       <c r="M43" s="3">
-        <v>45407</v>
+        <v>45118</v>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>RIO GRANDE</t>
+          <t>TOLHUIN</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Resuelta</t>
+          <t>Crónica</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -4466,7 +4436,7 @@
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
@@ -4477,21 +4447,21 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>16150973</v>
+        <v>24557964</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>VARGAS</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>ALDO WALTER</t>
+          <t>OSVALDO CRISTIAN</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>De 45 a 65 años</t>
+          <t>De 35 a 44 años</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -4506,39 +4476,69 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Banco de Sangre</t>
+          <t>Hepatitis virales</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>01. Caso probable en banco de sangre</t>
+          <t>06. Caso CONFIRMADO de Infección Aguda por VHB</t>
         </is>
       </c>
       <c r="I44">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J44">
         <v>2019</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2019-30</t>
+          <t>2019-35</t>
         </is>
       </c>
       <c r="L44" s="2">
-        <v>43675</v>
+        <v>43707</v>
       </c>
       <c r="M44" s="3">
-        <v>43672</v>
+        <v>43703</v>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>RIO GRANDE</t>
+          <t>USHUAIA</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Aguda</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>SI</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
@@ -4549,21 +4549,21 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>30144181</v>
+        <v>38776020</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>DAVIDSON</t>
+          <t>GODOY</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ANDRES SILVIO DE LA CRUZ</t>
+          <t>DANIEL ALBERTO</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>De 35 a 44 años</t>
+          <t>De 25 a 34 años</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -4583,64 +4583,64 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>07. Hepatitis B Resuelta - Infección Pasada</t>
+          <t>06. Caso CONFIRMADO de Infección Aguda por VHB</t>
         </is>
       </c>
       <c r="I45">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="J45">
-        <v>2024</v>
+        <v>2019</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2024-44</t>
+          <t>2019-34</t>
         </is>
       </c>
       <c r="L45" s="2">
-        <v>45595</v>
+        <v>43714</v>
       </c>
       <c r="M45" s="3">
-        <v>45593</v>
+        <v>43697</v>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>USHUAIA</t>
+          <t>RIO GALLEGOS</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>Aguda y resuelta</t>
+          <t>Aguda</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>No corresponde</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
@@ -4651,21 +4651,21 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>26710844</v>
+        <v>14492074</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>FLEITAS</t>
+          <t>ESTIGARRIBIA ACOSTA</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>CARLOS FELIPE</t>
+          <t>CLAUDIO</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>De 35 a 44 años</t>
+          <t>De 45 a 65 años</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4685,25 +4685,25 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>07. Hepatitis B Resuelta - Infección Pasada</t>
+          <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
         </is>
       </c>
       <c r="I46">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="J46">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2023-28</t>
+          <t>2025-18</t>
         </is>
       </c>
       <c r="L46" s="2">
-        <v>45122</v>
+        <v>45777</v>
       </c>
       <c r="M46" s="3">
-        <v>45118</v>
+        <v>45777</v>
       </c>
       <c r="N46" t="inlineStr">
         <is>
@@ -4753,21 +4753,21 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>24557964</v>
+        <v>7930029</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>OCAMPO</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>OSVALDO CRISTIAN</t>
+          <t>ELIO JAVIER</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>De 35 a 44 años</t>
+          <t>Mayores de 65 años</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -4787,25 +4787,25 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>06. Caso CONFIRMADO de Infección Aguda por VHB</t>
+          <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
         </is>
       </c>
       <c r="I47">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J47">
-        <v>2019</v>
+        <v>2024</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2019-35</t>
+          <t>2024-36</t>
         </is>
       </c>
       <c r="L47" s="2">
-        <v>43707</v>
+        <v>45565</v>
       </c>
       <c r="M47" s="3">
-        <v>43703</v>
+        <v>45537</v>
       </c>
       <c r="N47" t="inlineStr">
         <is>
@@ -4814,7 +4814,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Aguda</t>
+          <t>Crónica</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -4824,22 +4824,22 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -4855,26 +4855,26 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>38776020</v>
+        <v>18420802</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>GODOY</t>
+          <t>AYALA</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>DANIEL ALBERTO</t>
+          <t>CARLA PATRICIA</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>De 25 a 34 años</t>
+          <t>De 45 a 65 años</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -4889,64 +4889,39 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>06. Caso CONFIRMADO de Infección Aguda por VHB</t>
+          <t>Caso descartado Hepatitis B</t>
         </is>
       </c>
       <c r="I48">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="J48">
-        <v>2019</v>
+        <v>2025</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2019-34</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="L48" s="2">
-        <v>43714</v>
+        <v>45876</v>
       </c>
       <c r="M48" s="3">
-        <v>43697</v>
+        <v>45670</v>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>RIO GALLEGOS</t>
+          <t>*SIN DATO* (*SIN DATO*)</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>Aguda</t>
-        </is>
-      </c>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="R48" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
+          <t>Descartado</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>No corresponde</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
@@ -4957,16 +4932,16 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>27047731</v>
+        <v>13861790</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CENA</t>
+          <t>CAMERA</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>JUAN ALBERTO</t>
+          <t>OMAR MIGUEL</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -4991,34 +4966,64 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>07. Hepatitis B Resuelta - Infección Pasada</t>
+          <t>12. Virus Hepatitis B</t>
         </is>
       </c>
       <c r="I49">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="J49">
-        <v>2017</v>
+        <v>2021</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2017-26</t>
+          <t>2021-31</t>
         </is>
       </c>
       <c r="L49" s="2">
-        <v>46139</v>
+        <v>44701</v>
       </c>
       <c r="M49" s="3">
-        <v>42914</v>
+        <v>44410</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>SAN IGNACIO</t>
+          <t>CIUDAD DE BUENOS AIRES</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Crónica</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>HIV</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>SI</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
@@ -5029,26 +5034,26 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>14492074</v>
+        <v>30702578</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ESTIGARRIBIA ACOSTA</t>
+          <t>LAREO</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>CLAUDIO</t>
+          <t>MARINA PAULA</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>De 45 a 65 años</t>
+          <t>De 35 a 44 años</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -5058,69 +5063,39 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hepatitis virales</t>
+          <t>Banco de Sangre</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
+          <t>01. Caso probable en banco de sangre</t>
         </is>
       </c>
       <c r="I50">
         <v>18</v>
       </c>
       <c r="J50">
-        <v>2025</v>
+        <v>2020</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2025-18</t>
+          <t>2020-18</t>
         </is>
       </c>
       <c r="L50" s="2">
-        <v>45777</v>
+        <v>44082</v>
       </c>
       <c r="M50" s="3">
-        <v>45777</v>
+        <v>43951</v>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>TOLHUIN</t>
+          <t>USHUAIA</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>Crónica</t>
-        </is>
-      </c>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q50" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="R50" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="T50" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U50" t="inlineStr">
-        <is>
-          <t>SI</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
@@ -5131,21 +5106,21 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>7930029</v>
+        <v>22534702</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>OCAMPO</t>
+          <t>ANACHURI</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ELIO JAVIER</t>
+          <t>PASCUAL</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Mayores de 65 años</t>
+          <t>De 45 a 65 años</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -5160,30 +5135,30 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hepatitis virales</t>
+          <t>Banco de Sangre</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
+          <t>02. Caso sospechoso en banco de sangre</t>
         </is>
       </c>
       <c r="I51">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="J51">
-        <v>2024</v>
+        <v>2019</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2024-36</t>
+          <t>2019-26</t>
         </is>
       </c>
       <c r="L51" s="2">
-        <v>45565</v>
+        <v>43739</v>
       </c>
       <c r="M51" s="3">
-        <v>45537</v>
+        <v>43644</v>
       </c>
       <c r="N51" t="inlineStr">
         <is>
@@ -5192,37 +5167,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>Crónica</t>
-        </is>
-      </c>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q51" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="R51" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="T51" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U51" t="inlineStr">
-        <is>
-          <t>SI</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
@@ -5233,16 +5178,16 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>18420802</v>
+        <v>22475930</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>AYALA</t>
+          <t>MORAN</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>CARLA PATRICIA</t>
+          <t>LAURA MABEL</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -5262,44 +5207,69 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hepatitis virales</t>
+          <t>Banco de Sangre</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Caso descartado Hepatitis B</t>
+          <t>07. Hepatitis B Resuelta - Infección Pasada</t>
         </is>
       </c>
       <c r="I52">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="J52">
         <v>2025</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-28</t>
         </is>
       </c>
       <c r="L52" s="2">
         <v>45876</v>
       </c>
       <c r="M52" s="3">
-        <v>45670</v>
+        <v>45846</v>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>*SIN DATO* (*SIN DATO*)</t>
+          <t>USHUAIA</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>Descartado</t>
+          <t>Resuelta</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>No corresponde</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
@@ -5310,21 +5280,21 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>13861790</v>
+        <v>27908220</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CAMERA</t>
+          <t>BAZAN</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>OMAR MIGUEL</t>
+          <t>JUAN FRANCO SANTIAGO</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>De 45 a 65 años</t>
+          <t>De 35 a 44 años</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -5344,29 +5314,29 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>12. Virus Hepatitis B</t>
+          <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
         </is>
       </c>
       <c r="I53">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="J53">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2021-31</t>
+          <t>2023-45</t>
         </is>
       </c>
       <c r="L53" s="2">
-        <v>44701</v>
+        <v>45244</v>
       </c>
       <c r="M53" s="3">
-        <v>44410</v>
+        <v>45239</v>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>CIUDAD DE BUENOS AIRES</t>
+          <t>USHUAIA</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -5376,12 +5346,12 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>HIV</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
@@ -5396,7 +5366,7 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -5412,21 +5382,21 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>30702578</v>
+        <v>94289655</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>LAREO</t>
+          <t>CAMPOS VARGAS</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>MARINA PAULA</t>
+          <t>FIDELIA</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>De 35 a 44 años</t>
+          <t>De 45 a 65 años</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -5441,30 +5411,30 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Banco de Sangre</t>
+          <t>Hepatitis virales</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>01. Caso probable en banco de sangre</t>
+          <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
         </is>
       </c>
       <c r="I54">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J54">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2020-18</t>
+          <t>2019-23</t>
         </is>
       </c>
       <c r="L54" s="2">
-        <v>44082</v>
+        <v>46139</v>
       </c>
       <c r="M54" s="3">
-        <v>43951</v>
+        <v>43621</v>
       </c>
       <c r="N54" t="inlineStr">
         <is>
@@ -5473,7 +5443,37 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Crónica</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>SI</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
@@ -5484,16 +5484,16 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>22534702</v>
+        <v>17656573</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ANACHURI</t>
+          <t>HEREDIA</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>PASCUAL</t>
+          <t>SERGIO OSCAR</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -5513,30 +5513,30 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Banco de Sangre</t>
+          <t>Hepatitis virales</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>02. Caso sospechoso en banco de sangre</t>
+          <t>12. Virus Hepatitis B</t>
         </is>
       </c>
       <c r="I55">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="J55">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2019-26</t>
+          <t>2020-07</t>
         </is>
       </c>
       <c r="L55" s="2">
-        <v>43739</v>
+        <v>43892</v>
       </c>
       <c r="M55" s="3">
-        <v>43644</v>
+        <v>43872</v>
       </c>
       <c r="N55" t="inlineStr">
         <is>
@@ -5556,16 +5556,16 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>22475930</v>
+        <v>20799126</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>MORAN</t>
+          <t>LLAMPA</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>LAURA MABEL</t>
+          <t>ROSALIA SABINA</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -5585,30 +5585,30 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Banco de Sangre</t>
+          <t>Hepatitis virales</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>07. Hepatitis B Resuelta - Infección Pasada</t>
+          <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
         </is>
       </c>
       <c r="I56">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="J56">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2025-28</t>
+          <t>2022-45</t>
         </is>
       </c>
       <c r="L56" s="2">
-        <v>45876</v>
+        <v>44932</v>
       </c>
       <c r="M56" s="3">
-        <v>45846</v>
+        <v>44873</v>
       </c>
       <c r="N56" t="inlineStr">
         <is>
@@ -5617,7 +5617,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>Resuelta</t>
+          <t>Crónica</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -5658,26 +5658,26 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>27908220</v>
+        <v>10816969</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>BAZAN</t>
+          <t>PRETO</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>JUAN FRANCO SANTIAGO</t>
+          <t>CATALINA</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>De 35 a 44 años</t>
+          <t>Mayores de 65 años</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -5692,25 +5692,25 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
+          <t>04. Caso CONFIRMADO de Infección por VHB</t>
         </is>
       </c>
       <c r="I57">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="J57">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2023-45</t>
+          <t>2025-38</t>
         </is>
       </c>
       <c r="L57" s="2">
-        <v>45244</v>
+        <v>45925</v>
       </c>
       <c r="M57" s="3">
-        <v>45239</v>
+        <v>45919</v>
       </c>
       <c r="N57" t="inlineStr">
         <is>
@@ -5729,7 +5729,7 @@
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
@@ -5749,32 +5749,32 @@
       </c>
       <c r="U57" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
           <t>SI</t>
-        </is>
-      </c>
-      <c r="V57" t="inlineStr">
-        <is>
-          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58">
-        <v>94289655</v>
+        <v>95045940</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>CAMPOS VARGAS</t>
+          <t>MERUVIA ROBLES</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>FIDELIA</t>
+          <t>HERLINDA</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>De 45 a 65 años</t>
+          <t>De 25 a 34 años</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -5798,21 +5798,21 @@
         </is>
       </c>
       <c r="I58">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="J58">
         <v>2019</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2019-23</t>
+          <t>2019-02</t>
         </is>
       </c>
       <c r="L58" s="2">
-        <v>46139</v>
+        <v>43524</v>
       </c>
       <c r="M58" s="3">
-        <v>43621</v>
+        <v>43472</v>
       </c>
       <c r="N58" t="inlineStr">
         <is>
@@ -5826,32 +5826,32 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
@@ -5862,16 +5862,16 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>17656573</v>
+        <v>20159193</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>HEREDIA</t>
+          <t>MOLINA</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>SERGIO OSCAR</t>
+          <t>VICENTE DURVAL</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -5896,25 +5896,25 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>12. Virus Hepatitis B</t>
+          <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
         </is>
       </c>
       <c r="I59">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J59">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2020-07</t>
+          <t>2019-08</t>
         </is>
       </c>
       <c r="L59" s="2">
-        <v>43892</v>
+        <v>45240</v>
       </c>
       <c r="M59" s="3">
-        <v>43872</v>
+        <v>43514</v>
       </c>
       <c r="N59" t="inlineStr">
         <is>
@@ -5923,7 +5923,37 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Crónica</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
@@ -5934,16 +5964,16 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>20799126</v>
+        <v>14405748</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>LLAMPA</t>
+          <t>BAZAN</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>ROSALIA SABINA</t>
+          <t>ANA MARIA</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -5972,25 +6002,25 @@
         </is>
       </c>
       <c r="I60">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="J60">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2022-45</t>
+          <t>2020-30</t>
         </is>
       </c>
       <c r="L60" s="2">
-        <v>44932</v>
+        <v>44176</v>
       </c>
       <c r="M60" s="3">
-        <v>44873</v>
+        <v>44032</v>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>USHUAIA</t>
+          <t>RIO GRANDE</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -6000,32 +6030,32 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
@@ -6036,26 +6066,26 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>10816969</v>
+        <v>12956640</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>PRETO</t>
+          <t>RUSCH</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>CATALINA</t>
+          <t>GERMAN ALFREDO</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Mayores de 65 años</t>
+          <t>De 45 a 65 años</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -6070,29 +6100,29 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>04. Caso CONFIRMADO de Infección por VHB</t>
+          <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
         </is>
       </c>
       <c r="I61">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="J61">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2025-38</t>
+          <t>2023-47</t>
         </is>
       </c>
       <c r="L61" s="2">
-        <v>45925</v>
+        <v>45295</v>
       </c>
       <c r="M61" s="3">
-        <v>45919</v>
+        <v>45252</v>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>USHUAIA</t>
+          <t>TOLHUIN</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -6102,62 +6132,62 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="R61" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="S61" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="T61" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U61" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62">
-        <v>95045940</v>
+        <v>27353554</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>MERUVIA ROBLES</t>
+          <t>LEON</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>HERLINDA</t>
+          <t>RAMON DE LA CRUZ</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>De 25 a 34 años</t>
+          <t>De 45 a 65 años</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -6172,25 +6202,25 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
+          <t>06. Caso CONFIRMADO de Infección Aguda por VHB</t>
         </is>
       </c>
       <c r="I62">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="J62">
         <v>2019</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2019-02</t>
+          <t>2019-40</t>
         </is>
       </c>
       <c r="L62" s="2">
-        <v>43524</v>
+        <v>46139</v>
       </c>
       <c r="M62" s="3">
-        <v>43472</v>
+        <v>43738</v>
       </c>
       <c r="N62" t="inlineStr">
         <is>
@@ -6199,7 +6229,7 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>Crónica</t>
+          <t>Aguda</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -6224,12 +6254,12 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
@@ -6240,21 +6270,21 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>17372956</v>
+        <v>40000129</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>PEÑALOZA</t>
+          <t>NAVIA CASTELLON</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>LUIS ALBERTO</t>
+          <t>GUSTAVO ENZO</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>De 45 a 65 años</t>
+          <t>De 20 a 24 años</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -6274,64 +6304,39 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
+          <t>Caso descartado Hepatitis B</t>
         </is>
       </c>
       <c r="I63">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="J63">
-        <v>2006</v>
+        <v>2019</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2006-46</t>
+          <t>2019-31</t>
         </is>
       </c>
       <c r="L63" s="2">
-        <v>45244</v>
+        <v>43689</v>
       </c>
       <c r="M63" s="3">
-        <v>39035</v>
+        <v>43677</v>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>RIO GRANDE</t>
+          <t>USHUAIA</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>Crónica</t>
-        </is>
-      </c>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q63" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="R63" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="S63" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="T63" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>Descartado</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>No corresponde</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
@@ -6342,21 +6347,21 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>20159193</v>
+        <v>12145481</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MOLINA</t>
+          <t>FERREYRA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>VICENTE DURVAL</t>
+          <t>RICARDO MANUEL</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>De 45 a 65 años</t>
+          <t>Mayores de 65 años</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -6380,21 +6385,21 @@
         </is>
       </c>
       <c r="I64">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="J64">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2019-08</t>
+          <t>2022-47</t>
         </is>
       </c>
       <c r="L64" s="2">
-        <v>45240</v>
+        <v>44693</v>
       </c>
       <c r="M64" s="3">
-        <v>43514</v>
+        <v>44889</v>
       </c>
       <c r="N64" t="inlineStr">
         <is>
@@ -6413,7 +6418,7 @@
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
@@ -6444,21 +6449,21 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>14405748</v>
+        <v>36733857</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>BAZAN</t>
+          <t>ORTIZ</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>ANA MARIA</t>
+          <t>NATALIA ALEJANDRA</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>De 45 a 65 años</t>
+          <t>De 25 a 34 años</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -6473,30 +6478,30 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hepatitis virales</t>
+          <t>Banco de Sangre</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
+          <t>09. Caso CONFIRMADO de Infección OCULTA por VHB</t>
         </is>
       </c>
       <c r="I65">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="J65">
-        <v>2020</v>
+        <v>2025</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2020-30</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="L65" s="2">
-        <v>44176</v>
+        <v>45733</v>
       </c>
       <c r="M65" s="3">
-        <v>44032</v>
+        <v>45677</v>
       </c>
       <c r="N65" t="inlineStr">
         <is>
@@ -6505,37 +6510,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>Crónica</t>
-        </is>
-      </c>
-      <c r="P65" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="Q65" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="R65" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="S65" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="T65" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="U65" t="inlineStr">
-        <is>
-          <t>SI</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
@@ -6546,16 +6521,16 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>12956640</v>
+        <v>13814814</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>RUSCH</t>
+          <t>ANDERSEN</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>GERMAN ALFREDO</t>
+          <t>JOSE DAVID</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -6584,21 +6559,21 @@
         </is>
       </c>
       <c r="I66">
-        <v>47</v>
+        <v>12</v>
       </c>
       <c r="J66">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2023-47</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="L66" s="2">
-        <v>45295</v>
+        <v>45370</v>
       </c>
       <c r="M66" s="3">
-        <v>45252</v>
+        <v>45370</v>
       </c>
       <c r="N66" t="inlineStr">
         <is>
@@ -6648,16 +6623,16 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>27353554</v>
+        <v>16538420</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>LEON</t>
+          <t>CALISAYA</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>RAMON DE LA CRUZ</t>
+          <t>ILDA</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -6667,7 +6642,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -6682,34 +6657,34 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>06. Caso CONFIRMADO de Infección Aguda por VHB</t>
+          <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
         </is>
       </c>
       <c r="I67">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="J67">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2019-40</t>
+          <t>2022-35</t>
         </is>
       </c>
       <c r="L67" s="2">
-        <v>46139</v>
+        <v>44855</v>
       </c>
       <c r="M67" s="3">
-        <v>43738</v>
+        <v>44805</v>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>USHUAIA</t>
+          <t>SALTA</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>Aguda</t>
+          <t>Crónica</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -6734,7 +6709,7 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
@@ -6743,461 +6718,6 @@
         </is>
       </c>
       <c r="V67" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68">
-        <v>40000129</v>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>NAVIA CASTELLON</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>GUSTAVO ENZO</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>De 20 a 24 años</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Hepatitis B</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>Hepatitis virales</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Caso descartado Hepatitis B</t>
-        </is>
-      </c>
-      <c r="I68">
-        <v>31</v>
-      </c>
-      <c r="J68">
-        <v>2019</v>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>2019-31</t>
-        </is>
-      </c>
-      <c r="L68" s="2">
-        <v>43689</v>
-      </c>
-      <c r="M68" s="3">
-        <v>43677</v>
-      </c>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>USHUAIA</t>
-        </is>
-      </c>
-      <c r="O68" t="inlineStr">
-        <is>
-          <t>Descartado</t>
-        </is>
-      </c>
-      <c r="U68" t="inlineStr">
-        <is>
-          <t>No corresponde</t>
-        </is>
-      </c>
-      <c r="V68" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69">
-        <v>12145481</v>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>FERREYRA</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>RICARDO MANUEL</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>Mayores de 65 años</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Hepatitis B</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>Hepatitis virales</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
-        </is>
-      </c>
-      <c r="I69">
-        <v>47</v>
-      </c>
-      <c r="J69">
-        <v>2022</v>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>2022-47</t>
-        </is>
-      </c>
-      <c r="L69" s="2">
-        <v>44693</v>
-      </c>
-      <c r="M69" s="3">
-        <v>44889</v>
-      </c>
-      <c r="N69" t="inlineStr">
-        <is>
-          <t>USHUAIA</t>
-        </is>
-      </c>
-      <c r="O69" t="inlineStr">
-        <is>
-          <t>Crónica</t>
-        </is>
-      </c>
-      <c r="P69" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q69" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="R69" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="S69" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="T69" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U69" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="V69" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70">
-        <v>36733857</v>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>ORTIZ</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>NATALIA ALEJANDRA</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>De 25 a 34 años</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Hepatitis B</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>Banco de Sangre</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>09. Caso CONFIRMADO de Infección OCULTA por VHB</t>
-        </is>
-      </c>
-      <c r="I70">
-        <v>4</v>
-      </c>
-      <c r="J70">
-        <v>2025</v>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>2025-04</t>
-        </is>
-      </c>
-      <c r="L70" s="2">
-        <v>45733</v>
-      </c>
-      <c r="M70" s="3">
-        <v>45677</v>
-      </c>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>RIO GRANDE</t>
-        </is>
-      </c>
-      <c r="O70" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="V70" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71">
-        <v>13814814</v>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>ANDERSEN</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>JOSE DAVID</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>De 45 a 65 años</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Hepatitis B</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>Hepatitis virales</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
-        </is>
-      </c>
-      <c r="I71">
-        <v>12</v>
-      </c>
-      <c r="J71">
-        <v>2024</v>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>2024-12</t>
-        </is>
-      </c>
-      <c r="L71" s="2">
-        <v>45370</v>
-      </c>
-      <c r="M71" s="3">
-        <v>45370</v>
-      </c>
-      <c r="N71" t="inlineStr">
-        <is>
-          <t>TOLHUIN</t>
-        </is>
-      </c>
-      <c r="O71" t="inlineStr">
-        <is>
-          <t>Crónica</t>
-        </is>
-      </c>
-      <c r="P71" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="Q71" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="R71" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="S71" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="T71" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="U71" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="V71" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72">
-        <v>16538420</v>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>CALISAYA</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>ILDA</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>De 45 a 65 años</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>Hepatitis B</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>Hepatitis virales</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
-        </is>
-      </c>
-      <c r="I72">
-        <v>35</v>
-      </c>
-      <c r="J72">
-        <v>2022</v>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>2022-35</t>
-        </is>
-      </c>
-      <c r="L72" s="2">
-        <v>44855</v>
-      </c>
-      <c r="M72" s="3">
-        <v>44805</v>
-      </c>
-      <c r="N72" t="inlineStr">
-        <is>
-          <t>SALTA</t>
-        </is>
-      </c>
-      <c r="O72" t="inlineStr">
-        <is>
-          <t>Crónica</t>
-        </is>
-      </c>
-      <c r="P72" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q72" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="R72" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="S72" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="T72" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U72" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="V72" t="inlineStr">
         <is>
           <t>NO</t>
         </is>

--- a/Salidas/data_B_completa.xlsx
+++ b/Salidas/data_B_completa.xlsx
@@ -856,26 +856,26 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>18597623</v>
+        <v>30675706</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NUÑEZ</t>
+          <t>VILLALOBOS</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>JOSE JESUS</t>
+          <t>EVA MARIA</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>De 45 a 65 años</t>
+          <t>De 35 a 44 años</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -885,69 +885,39 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatitis virales</t>
+          <t>Banco de Sangre</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>12. Virus Hepatitis B</t>
+          <t>09. Caso CONFIRMADO de Infección OCULTA por VHB</t>
         </is>
       </c>
       <c r="I6">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="J6">
-        <v>2019</v>
+        <v>2025</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2019-07</t>
+          <t>2025-38</t>
         </is>
       </c>
       <c r="L6" s="2">
-        <v>43511</v>
+        <v>45936</v>
       </c>
       <c r="M6" s="3">
-        <v>43508</v>
+        <v>45918</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>USHUAIA</t>
+          <t>RIO GRANDE</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Crónica</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>SI</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -958,16 +928,16 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>25633171</v>
+        <v>18597623</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>VERA OYARZO</t>
+          <t>NUÑEZ</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>RUBEN MARCELO</t>
+          <t>JOSE JESUS</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -992,25 +962,25 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
+          <t>12. Virus Hepatitis B</t>
         </is>
       </c>
       <c r="I7">
-        <v>50</v>
+        <v>7</v>
       </c>
       <c r="J7">
-        <v>2025</v>
+        <v>2019</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2025-50</t>
+          <t>2019-07</t>
         </is>
       </c>
       <c r="L7" s="2">
-        <v>46001</v>
+        <v>43511</v>
       </c>
       <c r="M7" s="3">
-        <v>46001</v>
+        <v>43508</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -1024,32 +994,32 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1060,21 +1030,21 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>10619060</v>
+        <v>25633171</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>VERA OYARZO</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>EDGARDO RUBEN</t>
+          <t>RUBEN MARCELO</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Mayores de 65 años</t>
+          <t>De 45 a 65 años</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1098,25 +1068,25 @@
         </is>
       </c>
       <c r="I8">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="J8">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2021-23</t>
+          <t>2025-50</t>
         </is>
       </c>
       <c r="L8" s="2">
-        <v>44365</v>
+        <v>46001</v>
       </c>
       <c r="M8" s="3">
-        <v>44357</v>
+        <v>46001</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>TOLHUIN</t>
+          <t>USHUAIA</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1131,7 +1101,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1162,26 +1132,26 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>30675706</v>
+        <v>10619060</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>VILLALOBOS</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>EVA MARIA</t>
+          <t>EDGARDO RUBEN</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>De 35 a 44 años</t>
+          <t>Mayores de 65 años</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1191,39 +1161,69 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Banco de Sangre</t>
+          <t>Hepatitis virales</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>09. Caso CONFIRMADO de Infección OCULTA por VHB</t>
+          <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
         </is>
       </c>
       <c r="I9">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="J9">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2025-38</t>
+          <t>2021-23</t>
         </is>
       </c>
       <c r="L9" s="2">
-        <v>45936</v>
+        <v>44365</v>
       </c>
       <c r="M9" s="3">
-        <v>45918</v>
+        <v>44357</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>RIO GRANDE</t>
+          <t>TOLHUIN</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Crónica</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1923,16 +1923,16 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>26421454</v>
+        <v>31761053</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>QUIROZ</t>
+          <t>SOSA</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>LILIANA ROXANA</t>
+          <t>SANDRA VIVIANA</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1961,25 +1961,25 @@
         </is>
       </c>
       <c r="I17">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="J17">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2022-21</t>
+          <t>2023-35</t>
         </is>
       </c>
       <c r="L17" s="2">
-        <v>44708</v>
+        <v>45169</v>
       </c>
       <c r="M17" s="3">
-        <v>44705</v>
+        <v>45169</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>USHUAIA</t>
+          <t>TOLHUIN</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -2025,16 +2025,16 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>31761053</v>
+        <v>26421454</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SOSA</t>
+          <t>QUIROZ</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>SANDRA VIVIANA</t>
+          <t>LILIANA ROXANA</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2063,25 +2063,25 @@
         </is>
       </c>
       <c r="I18">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="J18">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2023-35</t>
+          <t>2022-21</t>
         </is>
       </c>
       <c r="L18" s="2">
-        <v>45169</v>
+        <v>44708</v>
       </c>
       <c r="M18" s="3">
-        <v>45169</v>
+        <v>44705</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>TOLHUIN</t>
+          <t>USHUAIA</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -2229,26 +2229,26 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>25633109</v>
+        <v>41058767</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MOTTER</t>
+          <t>GONZALEZ MOLINA</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>DIEGO IGNACIO</t>
+          <t>LOURDES MARIANELA</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>De 35 a 44 años</t>
+          <t>De 20 a 24 años</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2263,25 +2263,25 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
+          <t>Caso descartado Hepatitis B</t>
         </is>
       </c>
       <c r="I20">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="J20">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2020-45</t>
+          <t>2019-31</t>
         </is>
       </c>
       <c r="L20" s="2">
-        <v>44221</v>
+        <v>43689</v>
       </c>
       <c r="M20" s="3">
-        <v>44140</v>
+        <v>43677</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -2290,37 +2290,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Crónica</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -2331,16 +2301,16 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>22193794</v>
+        <v>17396287</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NIEVA</t>
+          <t>LAMA</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ENRIQUE ALBERTO</t>
+          <t>MIGUEL ANGEL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2365,25 +2335,25 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>04. Caso CONFIRMADO de Infección por VHB</t>
+          <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
         </is>
       </c>
       <c r="I21">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J21">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2022-30</t>
+          <t>2018-27</t>
         </is>
       </c>
       <c r="L21" s="2">
-        <v>46116</v>
+        <v>43424</v>
       </c>
       <c r="M21" s="3">
-        <v>44770</v>
+        <v>43286</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -2392,7 +2362,32 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Aguda</t>
+          <t>Crónica</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2402,32 +2397,32 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>41058767</v>
+        <v>22193794</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>GONZALEZ MOLINA</t>
+          <t>NIEVA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>LOURDES MARIANELA</t>
+          <t>ENRIQUE ALBERTO</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>De 20 a 24 años</t>
+          <t>De 45 a 65 años</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2442,25 +2437,25 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Caso descartado Hepatitis B</t>
+          <t>04. Caso CONFIRMADO de Infección por VHB</t>
         </is>
       </c>
       <c r="I22">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J22">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2019-31</t>
+          <t>2022-30</t>
         </is>
       </c>
       <c r="L22" s="2">
-        <v>43689</v>
+        <v>46116</v>
       </c>
       <c r="M22" s="3">
-        <v>43677</v>
+        <v>44770</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -2469,32 +2464,37 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Aguda</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>SI</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <v>17396287</v>
+        <v>25633109</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>MOTTER</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>MIGUEL ANGEL</t>
+          <t>DIEGO IGNACIO</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>De 45 a 65 años</t>
+          <t>De 35 a 44 años</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2518,21 +2518,21 @@
         </is>
       </c>
       <c r="I23">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="J23">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2018-27</t>
+          <t>2020-45</t>
         </is>
       </c>
       <c r="L23" s="2">
-        <v>43424</v>
+        <v>44221</v>
       </c>
       <c r="M23" s="3">
-        <v>43286</v>
+        <v>44140</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2571,7 +2571,7 @@
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -2684,26 +2684,26 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>28227396</v>
+        <v>14898515</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>FIGEROA</t>
+          <t>SALAS</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>VICTORIA ELENA</t>
+          <t>EVARISTO SILVANO</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>De 35 a 44 años</t>
+          <t>De 45 a 65 años</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2713,39 +2713,39 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Banco de Sangre</t>
+          <t>Hepatitis virales</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>07. Hepatitis B Resuelta - Infección Pasada</t>
+          <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
         </is>
       </c>
       <c r="I25">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="J25">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2019-28</t>
+          <t>2018-20</t>
         </is>
       </c>
       <c r="L25" s="2">
-        <v>43668</v>
+        <v>43243</v>
       </c>
       <c r="M25" s="3">
-        <v>43658</v>
+        <v>43237</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>RIO GRANDE</t>
+          <t>USHUAIA</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Resuelta</t>
+          <t>Crónica</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -2786,26 +2786,26 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>14898515</v>
+        <v>28227396</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SALAS</t>
+          <t>FIGEROA</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>EVARISTO SILVANO</t>
+          <t>VICTORIA ELENA</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>De 45 a 65 años</t>
+          <t>De 35 a 44 años</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2815,39 +2815,39 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatitis virales</t>
+          <t>Banco de Sangre</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
+          <t>07. Hepatitis B Resuelta - Infección Pasada</t>
         </is>
       </c>
       <c r="I26">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="J26">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2018-20</t>
+          <t>2019-28</t>
         </is>
       </c>
       <c r="L26" s="2">
-        <v>43243</v>
+        <v>43668</v>
       </c>
       <c r="M26" s="3">
-        <v>43237</v>
+        <v>43658</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>USHUAIA</t>
+          <t>RIO GRANDE</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Crónica</t>
+          <t>Resuelta</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3194,16 +3194,16 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>28008546</v>
+        <v>27908220</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SENILLIANI MELCHIOR</t>
+          <t>BAZAN</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CECILIA</t>
+          <t>JUAN FRANCO SANTIAGO</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -3232,21 +3232,21 @@
         </is>
       </c>
       <c r="I30">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="J30">
-        <v>2019</v>
+        <v>2023</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2019-33</t>
+          <t>2023-45</t>
         </is>
       </c>
       <c r="L30" s="2">
-        <v>43692</v>
+        <v>45244</v>
       </c>
       <c r="M30" s="3">
-        <v>43692</v>
+        <v>45239</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
@@ -3285,7 +3285,7 @@
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
@@ -3296,21 +3296,21 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>27834459</v>
+        <v>94289655</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ALCOBA</t>
+          <t>CAMPOS VARGAS</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>LUISA AUDELINA</t>
+          <t>FIDELIA</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>De 35 a 44 años</t>
+          <t>De 45 a 65 años</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3325,39 +3325,69 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Banco de Sangre</t>
+          <t>Hepatitis virales</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>01. Caso probable en banco de sangre</t>
+          <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
         </is>
       </c>
       <c r="I31">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="J31">
         <v>2019</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2019-49</t>
+          <t>2019-23</t>
         </is>
       </c>
       <c r="L31" s="2">
-        <v>43851</v>
+        <v>46139</v>
       </c>
       <c r="M31" s="3">
-        <v>43804</v>
+        <v>43621</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>RIO GRANDE</t>
+          <t>USHUAIA</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Crónica</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>SI</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
@@ -3368,21 +3398,21 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>26930068</v>
+        <v>17656573</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t>HEREDIA</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>SILVIO ALFREDO</t>
+          <t>SERGIO OSCAR</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>De 35 a 44 años</t>
+          <t>De 45 a 65 años</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3397,34 +3427,34 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Banco de Sangre</t>
+          <t>Hepatitis virales</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>02. Caso sospechoso en banco de sangre</t>
+          <t>12. Virus Hepatitis B</t>
         </is>
       </c>
       <c r="I32">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="J32">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2019-14</t>
+          <t>2020-07</t>
         </is>
       </c>
       <c r="L32" s="2">
-        <v>43598</v>
+        <v>43892</v>
       </c>
       <c r="M32" s="3">
-        <v>43556</v>
+        <v>43872</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>RIO GRANDE</t>
+          <t>USHUAIA</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -3440,16 +3470,16 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>13454523</v>
+        <v>20799126</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>PELLEGRINI</t>
+          <t>LLAMPA</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>EDGARDO ENZO</t>
+          <t>ROSALIA SABINA</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3459,7 +3489,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -3478,25 +3508,25 @@
         </is>
       </c>
       <c r="I33">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="J33">
         <v>2022</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2022-51</t>
+          <t>2022-45</t>
         </is>
       </c>
       <c r="L33" s="2">
-        <v>44928</v>
+        <v>44932</v>
       </c>
       <c r="M33" s="3">
-        <v>44917</v>
+        <v>44873</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>*sin dato*</t>
+          <t>USHUAIA</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -3511,27 +3541,27 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
@@ -3542,21 +3572,21 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>19092851</v>
+        <v>10816969</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>PEREZ LUNA RAFAJLOVSKI</t>
+          <t>PRETO</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>PARASHKEVA</t>
+          <t>CATALINA</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>De 35 a 44 años</t>
+          <t>Mayores de 65 años</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3576,29 +3606,29 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>12. Virus Hepatitis B</t>
+          <t>04. Caso CONFIRMADO de Infección por VHB</t>
         </is>
       </c>
       <c r="I34">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="J34">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2023-35</t>
+          <t>2025-38</t>
         </is>
       </c>
       <c r="L34" s="2">
-        <v>45183</v>
+        <v>45925</v>
       </c>
       <c r="M34" s="3">
-        <v>45169</v>
+        <v>45919</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>RIO GRANDE</t>
+          <t>USHUAIA</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -3608,62 +3638,62 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
           <t>SI</t>
-        </is>
-      </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35">
-        <v>29293499</v>
+        <v>95045940</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>PEREA</t>
+          <t>MERUVIA ROBLES</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>MARTIN ALFREDO</t>
+          <t>HERLINDA</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>De 35 a 44 años</t>
+          <t>De 25 a 34 años</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -3673,30 +3703,30 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Banco de Sangre</t>
+          <t>Hepatitis virales</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>07. Hepatitis B Resuelta - Infección Pasada</t>
+          <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
         </is>
       </c>
       <c r="I35">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="J35">
         <v>2019</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2019-24</t>
+          <t>2019-02</t>
         </is>
       </c>
       <c r="L35" s="2">
-        <v>43739</v>
+        <v>43524</v>
       </c>
       <c r="M35" s="3">
-        <v>43626</v>
+        <v>43472</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
@@ -3705,7 +3735,37 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Crónica</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -3716,26 +3776,26 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>95894978</v>
+        <v>20159193</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ROMERO QUIROGA</t>
+          <t>MOLINA</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CINTHIA SOLEDAD</t>
+          <t>VICENTE DURVAL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>De 20 a 24 años</t>
+          <t>De 45 a 65 años</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -3750,25 +3810,25 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>12. Virus Hepatitis B</t>
+          <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
         </is>
       </c>
       <c r="I36">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J36">
         <v>2019</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2019-02</t>
+          <t>2019-08</t>
         </is>
       </c>
       <c r="L36" s="2">
-        <v>43511</v>
+        <v>45240</v>
       </c>
       <c r="M36" s="3">
-        <v>43472</v>
+        <v>43514</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
@@ -3782,32 +3842,32 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
@@ -3818,16 +3878,16 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>14450682</v>
+        <v>12956640</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>GRAMAJO</t>
+          <t>RUSCH</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>NORMANDO</t>
+          <t>GERMAN ALFREDO</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -3847,44 +3907,69 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Banco de Sangre</t>
+          <t>Hepatitis virales</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Caso descartado Hepatitis B</t>
+          <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
         </is>
       </c>
       <c r="I37">
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="J37">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2023-47</t>
         </is>
       </c>
       <c r="L37" s="2">
-        <v>45414</v>
+        <v>45295</v>
       </c>
       <c r="M37" s="3">
-        <v>45315</v>
+        <v>45252</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>USHUAIA</t>
+          <t>TOLHUIN</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Descartado</t>
+          <t>Crónica</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>No corresponde</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
@@ -3895,16 +3980,16 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>20256616</v>
+        <v>27353554</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CARMONA</t>
+          <t>LEON</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>NORBERTO ALEJANDRO</t>
+          <t>RAMON DE LA CRUZ</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -3924,30 +4009,30 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Banco de Sangre</t>
+          <t>Hepatitis virales</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>02. Caso sospechoso en banco de sangre</t>
+          <t>06. Caso CONFIRMADO de Infección Aguda por VHB</t>
         </is>
       </c>
       <c r="I38">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="J38">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2020-14</t>
+          <t>2019-40</t>
         </is>
       </c>
       <c r="L38" s="2">
-        <v>44082</v>
+        <v>46139</v>
       </c>
       <c r="M38" s="3">
-        <v>43922</v>
+        <v>43738</v>
       </c>
       <c r="N38" t="inlineStr">
         <is>
@@ -3956,7 +4041,37 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Aguda</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>SI</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
@@ -3967,21 +4082,21 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>23140885</v>
+        <v>12145481</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>PORTAL</t>
+          <t>FERREYRA</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>HUGO CESAR</t>
+          <t>RICARDO MANUEL</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>De 45 a 65 años</t>
+          <t>Mayores de 65 años</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -4005,21 +4120,21 @@
         </is>
       </c>
       <c r="I39">
-        <v>10</v>
+        <v>47</v>
       </c>
       <c r="J39">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2023-10</t>
+          <t>2022-47</t>
         </is>
       </c>
       <c r="L39" s="2">
-        <v>45244</v>
+        <v>44693</v>
       </c>
       <c r="M39" s="3">
-        <v>44991</v>
+        <v>44889</v>
       </c>
       <c r="N39" t="inlineStr">
         <is>
@@ -4058,7 +4173,7 @@
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
@@ -4069,21 +4184,21 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>29372354</v>
+        <v>40000129</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>GUANDARILLO</t>
+          <t>NAVIA CASTELLON</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ABEL MARCELO</t>
+          <t>GUSTAVO ENZO</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>De 35 a 44 años</t>
+          <t>De 20 a 24 años</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -4103,64 +4218,39 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>07. Hepatitis B Resuelta - Infección Pasada</t>
+          <t>Caso descartado Hepatitis B</t>
         </is>
       </c>
       <c r="I40">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="J40">
-        <v>2024</v>
+        <v>2019</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2024-17</t>
+          <t>2019-31</t>
         </is>
       </c>
       <c r="L40" s="2">
-        <v>45441</v>
+        <v>43689</v>
       </c>
       <c r="M40" s="3">
-        <v>45407</v>
+        <v>43677</v>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>RIO GRANDE</t>
+          <t>USHUAIA</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Resuelta</t>
-        </is>
-      </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="R40" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>Descartado</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>No corresponde</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
@@ -4171,16 +4261,16 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>16150973</v>
+        <v>14405748</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>VARGAS</t>
+          <t>BAZAN</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ALDO WALTER</t>
+          <t>ANA MARIA</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -4190,7 +4280,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -4200,30 +4290,30 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Banco de Sangre</t>
+          <t>Hepatitis virales</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>01. Caso probable en banco de sangre</t>
+          <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
         </is>
       </c>
       <c r="I41">
         <v>30</v>
       </c>
       <c r="J41">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2019-30</t>
+          <t>2020-30</t>
         </is>
       </c>
       <c r="L41" s="2">
-        <v>43675</v>
+        <v>44176</v>
       </c>
       <c r="M41" s="3">
-        <v>43672</v>
+        <v>44032</v>
       </c>
       <c r="N41" t="inlineStr">
         <is>
@@ -4232,7 +4322,37 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Crónica</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>SI</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
@@ -4243,26 +4363,26 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>30144181</v>
+        <v>36733857</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>DAVIDSON</t>
+          <t>ORTIZ</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ANDRES SILVIO DE LA CRUZ</t>
+          <t>NATALIA ALEJANDRA</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>De 35 a 44 años</t>
+          <t>De 25 a 34 años</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -4272,69 +4392,39 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hepatitis virales</t>
+          <t>Banco de Sangre</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>07. Hepatitis B Resuelta - Infección Pasada</t>
+          <t>09. Caso CONFIRMADO de Infección OCULTA por VHB</t>
         </is>
       </c>
       <c r="I42">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="J42">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2024-44</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="L42" s="2">
-        <v>45595</v>
+        <v>45733</v>
       </c>
       <c r="M42" s="3">
-        <v>45593</v>
+        <v>45677</v>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>USHUAIA</t>
+          <t>RIO GRANDE</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Aguda y resuelta</t>
-        </is>
-      </c>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="R42" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U42" t="inlineStr">
-        <is>
-          <t>No corresponde</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
@@ -4345,21 +4435,21 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>26710844</v>
+        <v>13814814</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>FLEITAS</t>
+          <t>ANDERSEN</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>CARLOS FELIPE</t>
+          <t>JOSE DAVID</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>De 35 a 44 años</t>
+          <t>De 45 a 65 años</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -4379,25 +4469,25 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>07. Hepatitis B Resuelta - Infección Pasada</t>
+          <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
         </is>
       </c>
       <c r="I43">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="J43">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2023-28</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="L43" s="2">
-        <v>45122</v>
+        <v>45370</v>
       </c>
       <c r="M43" s="3">
-        <v>45118</v>
+        <v>45370</v>
       </c>
       <c r="N43" t="inlineStr">
         <is>
@@ -4411,27 +4501,27 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -4447,16 +4537,16 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>24557964</v>
+        <v>27834459</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>ALCOBA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>OSVALDO CRISTIAN</t>
+          <t>LUISA AUDELINA</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -4466,7 +4556,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -4476,69 +4566,39 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hepatitis virales</t>
+          <t>Banco de Sangre</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>06. Caso CONFIRMADO de Infección Aguda por VHB</t>
+          <t>01. Caso probable en banco de sangre</t>
         </is>
       </c>
       <c r="I44">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="J44">
         <v>2019</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2019-35</t>
+          <t>2019-49</t>
         </is>
       </c>
       <c r="L44" s="2">
-        <v>43707</v>
+        <v>43851</v>
       </c>
       <c r="M44" s="3">
-        <v>43703</v>
+        <v>43804</v>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>USHUAIA</t>
+          <t>RIO GRANDE</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Aguda</t>
-        </is>
-      </c>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="R44" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t>SI</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
@@ -4549,26 +4609,26 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>38776020</v>
+        <v>28008546</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>GODOY</t>
+          <t>SENILLIANI MELCHIOR</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>DANIEL ALBERTO</t>
+          <t>CECILIA</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>De 25 a 34 años</t>
+          <t>De 35 a 44 años</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -4583,64 +4643,64 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>06. Caso CONFIRMADO de Infección Aguda por VHB</t>
+          <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
         </is>
       </c>
       <c r="I45">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J45">
         <v>2019</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2019-34</t>
+          <t>2019-33</t>
         </is>
       </c>
       <c r="L45" s="2">
-        <v>43714</v>
+        <v>43692</v>
       </c>
       <c r="M45" s="3">
-        <v>43697</v>
+        <v>43692</v>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>RIO GALLEGOS</t>
+          <t>USHUAIA</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>Aguda</t>
+          <t>Crónica</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
@@ -4651,16 +4711,16 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>14492074</v>
+        <v>13454523</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ESTIGARRIBIA ACOSTA</t>
+          <t>PELLEGRINI</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>CLAUDIO</t>
+          <t>EDGARDO ENZO</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -4689,25 +4749,25 @@
         </is>
       </c>
       <c r="I46">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="J46">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2025-18</t>
+          <t>2022-51</t>
         </is>
       </c>
       <c r="L46" s="2">
-        <v>45777</v>
+        <v>44928</v>
       </c>
       <c r="M46" s="3">
-        <v>45777</v>
+        <v>44917</v>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>TOLHUIN</t>
+          <t>*sin dato*</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -4722,22 +4782,22 @@
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -4753,21 +4813,21 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>7930029</v>
+        <v>26930068</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>OCAMPO</t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ELIO JAVIER</t>
+          <t>SILVIO ALFREDO</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Mayores de 65 años</t>
+          <t>De 35 a 44 años</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -4782,69 +4842,39 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hepatitis virales</t>
+          <t>Banco de Sangre</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
+          <t>02. Caso sospechoso en banco de sangre</t>
         </is>
       </c>
       <c r="I47">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="J47">
-        <v>2024</v>
+        <v>2019</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2024-36</t>
+          <t>2019-14</t>
         </is>
       </c>
       <c r="L47" s="2">
-        <v>45565</v>
+        <v>43598</v>
       </c>
       <c r="M47" s="3">
-        <v>45537</v>
+        <v>43556</v>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>USHUAIA</t>
+          <t>RIO GRANDE</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Crónica</t>
-        </is>
-      </c>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="R47" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="T47" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U47" t="inlineStr">
-        <is>
-          <t>SI</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
@@ -4855,21 +4885,21 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>18420802</v>
+        <v>19092851</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>AYALA</t>
+          <t>PEREZ LUNA RAFAJLOVSKI</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CARLA PATRICIA</t>
+          <t>PARASHKEVA</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>De 45 a 65 años</t>
+          <t>De 35 a 44 años</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -4889,39 +4919,64 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Caso descartado Hepatitis B</t>
+          <t>12. Virus Hepatitis B</t>
         </is>
       </c>
       <c r="I48">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="J48">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2023-35</t>
         </is>
       </c>
       <c r="L48" s="2">
-        <v>45876</v>
+        <v>45183</v>
       </c>
       <c r="M48" s="3">
-        <v>45670</v>
+        <v>45169</v>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>*SIN DATO* (*SIN DATO*)</t>
+          <t>RIO GRANDE</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>Descartado</t>
+          <t>Crónica</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>No corresponde</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
@@ -4932,26 +4987,26 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>13861790</v>
+        <v>95894978</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CAMERA</t>
+          <t>ROMERO QUIROGA</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>OMAR MIGUEL</t>
+          <t>CINTHIA SOLEDAD</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>De 45 a 65 años</t>
+          <t>De 20 a 24 años</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -4970,25 +5025,25 @@
         </is>
       </c>
       <c r="I49">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="J49">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2021-31</t>
+          <t>2019-02</t>
         </is>
       </c>
       <c r="L49" s="2">
-        <v>44701</v>
+        <v>43511</v>
       </c>
       <c r="M49" s="3">
-        <v>44410</v>
+        <v>43472</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>CIUDAD DE BUENOS AIRES</t>
+          <t>USHUAIA</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -4998,22 +5053,22 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>HIV</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
@@ -5034,16 +5089,16 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>30702578</v>
+        <v>29293499</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>LAREO</t>
+          <t>PEREA</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>MARINA PAULA</t>
+          <t>MARTIN ALFREDO</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -5053,7 +5108,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -5068,25 +5123,25 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>01. Caso probable en banco de sangre</t>
+          <t>07. Hepatitis B Resuelta - Infección Pasada</t>
         </is>
       </c>
       <c r="I50">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J50">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2020-18</t>
+          <t>2019-24</t>
         </is>
       </c>
       <c r="L50" s="2">
-        <v>44082</v>
+        <v>43739</v>
       </c>
       <c r="M50" s="3">
-        <v>43951</v>
+        <v>43626</v>
       </c>
       <c r="N50" t="inlineStr">
         <is>
@@ -5106,16 +5161,16 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>22534702</v>
+        <v>20256616</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ANACHURI</t>
+          <t>CARMONA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>PASCUAL</t>
+          <t>NORBERTO ALEJANDRO</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -5144,21 +5199,21 @@
         </is>
       </c>
       <c r="I51">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="J51">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2019-26</t>
+          <t>2020-14</t>
         </is>
       </c>
       <c r="L51" s="2">
-        <v>43739</v>
+        <v>44082</v>
       </c>
       <c r="M51" s="3">
-        <v>43644</v>
+        <v>43922</v>
       </c>
       <c r="N51" t="inlineStr">
         <is>
@@ -5178,16 +5233,16 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>22475930</v>
+        <v>14450682</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>MORAN</t>
+          <t>GRAMAJO</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>LAURA MABEL</t>
+          <t>NORMANDO</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -5197,7 +5252,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -5212,25 +5267,25 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>07. Hepatitis B Resuelta - Infección Pasada</t>
+          <t>Caso descartado Hepatitis B</t>
         </is>
       </c>
       <c r="I52">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="J52">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2025-28</t>
+          <t>2024-04</t>
         </is>
       </c>
       <c r="L52" s="2">
-        <v>45876</v>
+        <v>45414</v>
       </c>
       <c r="M52" s="3">
-        <v>45846</v>
+        <v>45315</v>
       </c>
       <c r="N52" t="inlineStr">
         <is>
@@ -5239,37 +5294,12 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>Resuelta</t>
-        </is>
-      </c>
-      <c r="P52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="R52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="T52" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>Descartado</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>No corresponde</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
@@ -5280,21 +5310,21 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>27908220</v>
+        <v>23140885</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>BAZAN</t>
+          <t>PORTAL</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>JUAN FRANCO SANTIAGO</t>
+          <t>HUGO CESAR</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>De 35 a 44 años</t>
+          <t>De 45 a 65 años</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -5318,21 +5348,21 @@
         </is>
       </c>
       <c r="I53">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="J53">
         <v>2023</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2023-45</t>
+          <t>2023-10</t>
         </is>
       </c>
       <c r="L53" s="2">
         <v>45244</v>
       </c>
       <c r="M53" s="3">
-        <v>45239</v>
+        <v>44991</v>
       </c>
       <c r="N53" t="inlineStr">
         <is>
@@ -5382,16 +5412,16 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>94289655</v>
+        <v>16150973</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CAMPOS VARGAS</t>
+          <t>VARGAS</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>FIDELIA</t>
+          <t>ALDO WALTER</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -5401,7 +5431,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -5411,69 +5441,39 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hepatitis virales</t>
+          <t>Banco de Sangre</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
+          <t>01. Caso probable en banco de sangre</t>
         </is>
       </c>
       <c r="I54">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J54">
         <v>2019</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2019-23</t>
+          <t>2019-30</t>
         </is>
       </c>
       <c r="L54" s="2">
-        <v>46139</v>
+        <v>43675</v>
       </c>
       <c r="M54" s="3">
-        <v>43621</v>
+        <v>43672</v>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>USHUAIA</t>
+          <t>RIO GRANDE</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>Crónica</t>
-        </is>
-      </c>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="Q54" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="R54" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="T54" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="U54" t="inlineStr">
-        <is>
-          <t>SI</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
@@ -5484,21 +5484,21 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>17656573</v>
+        <v>29372354</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>HEREDIA</t>
+          <t>GUANDARILLO</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>SERGIO OSCAR</t>
+          <t>ABEL MARCELO</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>De 45 a 65 años</t>
+          <t>De 35 a 44 años</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -5518,34 +5518,64 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>12. Virus Hepatitis B</t>
+          <t>07. Hepatitis B Resuelta - Infección Pasada</t>
         </is>
       </c>
       <c r="I55">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="J55">
-        <v>2020</v>
+        <v>2024</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2020-07</t>
+          <t>2024-17</t>
         </is>
       </c>
       <c r="L55" s="2">
-        <v>43892</v>
+        <v>45441</v>
       </c>
       <c r="M55" s="3">
-        <v>43872</v>
+        <v>45407</v>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>USHUAIA</t>
+          <t>RIO GRANDE</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Resuelta</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
@@ -5556,26 +5586,26 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>20799126</v>
+        <v>24557964</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>LLAMPA</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ROSALIA SABINA</t>
+          <t>OSVALDO CRISTIAN</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>De 45 a 65 años</t>
+          <t>De 35 a 44 años</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -5590,25 +5620,25 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
+          <t>06. Caso CONFIRMADO de Infección Aguda por VHB</t>
         </is>
       </c>
       <c r="I56">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="J56">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2022-45</t>
+          <t>2019-35</t>
         </is>
       </c>
       <c r="L56" s="2">
-        <v>44932</v>
+        <v>43707</v>
       </c>
       <c r="M56" s="3">
-        <v>44873</v>
+        <v>43703</v>
       </c>
       <c r="N56" t="inlineStr">
         <is>
@@ -5617,7 +5647,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>Crónica</t>
+          <t>Aguda</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -5627,27 +5657,27 @@
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
@@ -5658,26 +5688,26 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>10816969</v>
+        <v>26710844</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>PRETO</t>
+          <t>FLEITAS</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>CATALINA</t>
+          <t>CARLOS FELIPE</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Mayores de 65 años</t>
+          <t>De 35 a 44 años</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -5692,29 +5722,29 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>04. Caso CONFIRMADO de Infección por VHB</t>
+          <t>07. Hepatitis B Resuelta - Infección Pasada</t>
         </is>
       </c>
       <c r="I57">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="J57">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2025-38</t>
+          <t>2023-28</t>
         </is>
       </c>
       <c r="L57" s="2">
-        <v>45925</v>
+        <v>45122</v>
       </c>
       <c r="M57" s="3">
-        <v>45919</v>
+        <v>45118</v>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>USHUAIA</t>
+          <t>TOLHUIN</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -5729,57 +5759,57 @@
       </c>
       <c r="Q57" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="R57" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="T57" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U57" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58">
-        <v>95045940</v>
+        <v>30144181</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>MERUVIA ROBLES</t>
+          <t>DAVIDSON</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>HERLINDA</t>
+          <t>ANDRES SILVIO DE LA CRUZ</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>De 25 a 34 años</t>
+          <t>De 35 a 44 años</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -5794,25 +5824,25 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
+          <t>07. Hepatitis B Resuelta - Infección Pasada</t>
         </is>
       </c>
       <c r="I58">
-        <v>2</v>
+        <v>44</v>
       </c>
       <c r="J58">
-        <v>2019</v>
+        <v>2024</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2019-02</t>
+          <t>2024-44</t>
         </is>
       </c>
       <c r="L58" s="2">
-        <v>43524</v>
+        <v>45595</v>
       </c>
       <c r="M58" s="3">
-        <v>43472</v>
+        <v>45593</v>
       </c>
       <c r="N58" t="inlineStr">
         <is>
@@ -5821,7 +5851,7 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>Crónica</t>
+          <t>Aguda y resuelta</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -5851,7 +5881,7 @@
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>No corresponde</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
@@ -5862,21 +5892,21 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>20159193</v>
+        <v>38776020</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>MOLINA</t>
+          <t>GODOY</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>VICENTE DURVAL</t>
+          <t>DANIEL ALBERTO</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>De 45 a 65 años</t>
+          <t>De 25 a 34 años</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -5896,64 +5926,64 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
+          <t>06. Caso CONFIRMADO de Infección Aguda por VHB</t>
         </is>
       </c>
       <c r="I59">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="J59">
         <v>2019</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2019-08</t>
+          <t>2019-34</t>
         </is>
       </c>
       <c r="L59" s="2">
-        <v>45240</v>
+        <v>43714</v>
       </c>
       <c r="M59" s="3">
-        <v>43514</v>
+        <v>43697</v>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>USHUAIA</t>
+          <t>RIO GALLEGOS</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Crónica</t>
+          <t>Aguda</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
           <t>SI</t>
-        </is>
-      </c>
-      <c r="R59" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="T59" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U59" t="inlineStr">
-        <is>
-          <t>NO</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
@@ -5964,16 +5994,16 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>14405748</v>
+        <v>14492074</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>BAZAN</t>
+          <t>ESTIGARRIBIA ACOSTA</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>ANA MARIA</t>
+          <t>CLAUDIO</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -5983,7 +6013,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -6002,25 +6032,25 @@
         </is>
       </c>
       <c r="I60">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="J60">
-        <v>2020</v>
+        <v>2025</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2020-30</t>
+          <t>2025-18</t>
         </is>
       </c>
       <c r="L60" s="2">
-        <v>44176</v>
+        <v>45777</v>
       </c>
       <c r="M60" s="3">
-        <v>44032</v>
+        <v>45777</v>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>RIO GRANDE</t>
+          <t>TOLHUIN</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -6030,27 +6060,27 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -6066,16 +6096,16 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>12956640</v>
+        <v>13861790</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>RUSCH</t>
+          <t>CAMERA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>GERMAN ALFREDO</t>
+          <t>OMAR MIGUEL</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -6100,29 +6130,29 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
+          <t>12. Virus Hepatitis B</t>
         </is>
       </c>
       <c r="I61">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="J61">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2023-47</t>
+          <t>2021-31</t>
         </is>
       </c>
       <c r="L61" s="2">
-        <v>45295</v>
+        <v>44701</v>
       </c>
       <c r="M61" s="3">
-        <v>45252</v>
+        <v>44410</v>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>TOLHUIN</t>
+          <t>CIUDAD DE BUENOS AIRES</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -6132,22 +6162,22 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>HIV</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
@@ -6168,21 +6198,21 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>27353554</v>
+        <v>7930029</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>LEON</t>
+          <t>OCAMPO</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>RAMON DE LA CRUZ</t>
+          <t>ELIO JAVIER</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>De 45 a 65 años</t>
+          <t>Mayores de 65 años</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -6202,25 +6232,25 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>06. Caso CONFIRMADO de Infección Aguda por VHB</t>
+          <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
         </is>
       </c>
       <c r="I62">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J62">
-        <v>2019</v>
+        <v>2024</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2019-40</t>
+          <t>2024-36</t>
         </is>
       </c>
       <c r="L62" s="2">
-        <v>46139</v>
+        <v>45565</v>
       </c>
       <c r="M62" s="3">
-        <v>43738</v>
+        <v>45537</v>
       </c>
       <c r="N62" t="inlineStr">
         <is>
@@ -6229,7 +6259,7 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>Aguda</t>
+          <t>Crónica</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -6239,7 +6269,7 @@
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
@@ -6254,7 +6284,7 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -6270,26 +6300,26 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>40000129</v>
+        <v>18420802</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>NAVIA CASTELLON</t>
+          <t>AYALA</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>GUSTAVO ENZO</t>
+          <t>CARLA PATRICIA</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>De 20 a 24 años</t>
+          <t>De 45 a 65 años</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -6308,25 +6338,25 @@
         </is>
       </c>
       <c r="I63">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="J63">
-        <v>2019</v>
+        <v>2025</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2019-31</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="L63" s="2">
-        <v>43689</v>
+        <v>45876</v>
       </c>
       <c r="M63" s="3">
-        <v>43677</v>
+        <v>45670</v>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>USHUAIA</t>
+          <t>*SIN DATO* (*SIN DATO*)</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
@@ -6347,26 +6377,26 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>12145481</v>
+        <v>30702578</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>FERREYRA</t>
+          <t>LAREO</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>RICARDO MANUEL</t>
+          <t>MARINA PAULA</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Mayores de 65 años</t>
+          <t>De 35 a 44 años</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -6376,30 +6406,30 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hepatitis virales</t>
+          <t>Banco de Sangre</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
+          <t>01. Caso probable en banco de sangre</t>
         </is>
       </c>
       <c r="I64">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="J64">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2022-47</t>
+          <t>2020-18</t>
         </is>
       </c>
       <c r="L64" s="2">
-        <v>44693</v>
+        <v>44082</v>
       </c>
       <c r="M64" s="3">
-        <v>44889</v>
+        <v>43951</v>
       </c>
       <c r="N64" t="inlineStr">
         <is>
@@ -6408,37 +6438,7 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>Crónica</t>
-        </is>
-      </c>
-      <c r="P64" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q64" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="R64" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="S64" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="T64" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U64" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
@@ -6449,21 +6449,21 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>36733857</v>
+        <v>22475930</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>ORTIZ</t>
+          <t>MORAN</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>NATALIA ALEJANDRA</t>
+          <t>LAURA MABEL</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>De 25 a 34 años</t>
+          <t>De 45 a 65 años</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -6483,34 +6483,64 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>09. Caso CONFIRMADO de Infección OCULTA por VHB</t>
+          <t>07. Hepatitis B Resuelta - Infección Pasada</t>
         </is>
       </c>
       <c r="I65">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="J65">
         <v>2025</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2025-28</t>
         </is>
       </c>
       <c r="L65" s="2">
-        <v>45733</v>
+        <v>45876</v>
       </c>
       <c r="M65" s="3">
-        <v>45677</v>
+        <v>45846</v>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>RIO GRANDE</t>
+          <t>USHUAIA</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Resuelta</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
@@ -6521,16 +6551,16 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>13814814</v>
+        <v>22534702</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>ANDERSEN</t>
+          <t>ANACHURI</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>JOSE DAVID</t>
+          <t>PASCUAL</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -6550,69 +6580,39 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hepatitis virales</t>
+          <t>Banco de Sangre</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>05. Caso CONFIRMADO de Infección Crónica por VHB</t>
+          <t>02. Caso sospechoso en banco de sangre</t>
         </is>
       </c>
       <c r="I66">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="J66">
-        <v>2024</v>
+        <v>2019</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2019-26</t>
         </is>
       </c>
       <c r="L66" s="2">
-        <v>45370</v>
+        <v>43739</v>
       </c>
       <c r="M66" s="3">
-        <v>45370</v>
+        <v>43644</v>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>TOLHUIN</t>
+          <t>USHUAIA</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>Crónica</t>
-        </is>
-      </c>
-      <c r="P66" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="Q66" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="R66" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="S66" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="T66" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="U66" t="inlineStr">
-        <is>
-          <t>SI</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
